--- a/fournisseurs/Table_fournisseurs_consolidee.xlsx
+++ b/fournisseurs/Table_fournisseurs_consolidee.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Fournisseurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fournisseurs'!$A$3:$M$239</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fournisseurs'!$A$3:$M$247</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M239"/>
+  <dimension ref="A1:M247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source : Annuaire_FRN.xlsx (onglets « annuaire FRN contrats » et « annuaire FRN espaces verts »). Une ligne dédiée par fournisseur, ses contacts rangés juste en dessous. Pôle non renseigné dans la source → « SGX Réseau ».</t>
+          <t>Source : Annuaire_FRN.xlsx (onglets « annuaire FRN contrats » et « annuaire FRN espaces verts »), complétée des fournisseurs transmis hors annuaire. Une ligne dédiée par fournisseur, ses contacts rangés juste en dessous. Pôle non renseigné → « SGX Réseau ».</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="M138" s="6" t="inlineStr"/>
     </row>
-    <row r="139" ht="28.8" customHeight="1">
+    <row r="139" ht="67.5" customHeight="1">
       <c r="A139" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
@@ -5049,141 +5049,149 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>LE MOAL PAYSAGE</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>FSLE0225</t>
-        </is>
-      </c>
-      <c r="D139" s="4" t="inlineStr">
-        <is>
-          <t>LE MOAL PAYSAGE</t>
-        </is>
-      </c>
+          <t>KINTESSIA</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr"/>
+      <c r="D139" s="4" t="inlineStr"/>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>ESPACES VERTS / PAYSAGISTE</t>
-        </is>
-      </c>
-      <c r="F139" s="4" t="inlineStr"/>
-      <c r="G139" s="4" t="inlineStr">
-        <is>
-          <t>CARHAIX EST</t>
-        </is>
-      </c>
+          <t>MÉNAGE</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>PARIS RP ; SUD EST</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr"/>
       <c r="H139" s="4" t="inlineStr"/>
       <c r="I139" s="4" t="inlineStr"/>
       <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr"/>
       <c r="L139" s="4" t="inlineStr"/>
-      <c r="M139" s="4" t="inlineStr"/>
-    </row>
-    <row r="140" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A140" s="6" t="inlineStr"/>
-      <c r="B140" s="6" t="inlineStr"/>
-      <c r="C140" s="6" t="inlineStr"/>
-      <c r="D140" s="6" t="inlineStr"/>
-      <c r="E140" s="6" t="inlineStr"/>
-      <c r="F140" s="6" t="inlineStr"/>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="6" t="inlineStr"/>
-      <c r="I140" s="6" t="inlineStr">
+      <c r="M139" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE SECTEURS PARIS RP ET SUD-EST ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="28.8" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>LE MOAL PAYSAGE</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>FSLE0225</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>LE MOAL PAYSAGE</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>ESPACES VERTS / PAYSAGISTE</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr"/>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>CARHAIX EST</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr"/>
+      <c r="I140" s="4" t="inlineStr"/>
+      <c r="J140" s="4" t="inlineStr"/>
+      <c r="K140" s="4" t="inlineStr"/>
+      <c r="L140" s="4" t="inlineStr"/>
+      <c r="M140" s="4" t="inlineStr"/>
+    </row>
+    <row r="141" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A141" s="6" t="inlineStr"/>
+      <c r="B141" s="6" t="inlineStr"/>
+      <c r="C141" s="6" t="inlineStr"/>
+      <c r="D141" s="6" t="inlineStr"/>
+      <c r="E141" s="6" t="inlineStr"/>
+      <c r="F141" s="6" t="inlineStr"/>
+      <c r="G141" s="6" t="inlineStr"/>
+      <c r="H141" s="6" t="inlineStr"/>
+      <c r="I141" s="6" t="inlineStr">
         <is>
           <t>SYLVAIN LE MOAL</t>
         </is>
       </c>
-      <c r="J140" s="6" t="inlineStr">
+      <c r="J141" s="6" t="inlineStr">
         <is>
           <t>GÉRANT</t>
         </is>
       </c>
-      <c r="K140" s="6" t="inlineStr">
+      <c r="K141" s="6" t="inlineStr">
         <is>
           <t>02 98 93 99 10 / 06 59 59 98 12</t>
         </is>
       </c>
-      <c r="L140" s="6" t="inlineStr">
+      <c r="L141" s="6" t="inlineStr">
         <is>
           <t>lemoalpaysage@hotmail.com</t>
         </is>
       </c>
-      <c r="M140" s="6" t="inlineStr"/>
-    </row>
-    <row r="141" ht="15.9" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="M141" s="6" t="inlineStr"/>
+    </row>
+    <row r="142" ht="15.9" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B142" s="5" t="inlineStr">
         <is>
           <t>LECOQ</t>
         </is>
       </c>
-      <c r="C141" s="5" t="inlineStr">
+      <c r="C142" s="5" t="inlineStr">
         <is>
           <t>FSLE0087</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr">
         <is>
           <t>LECOQ SAS</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
+      <c r="E142" s="4" t="inlineStr">
         <is>
           <t>CLIMATICIEN</t>
         </is>
       </c>
-      <c r="F141" s="4" t="inlineStr">
+      <c r="F142" s="4" t="inlineStr">
         <is>
           <t>SUD OUEST</t>
         </is>
       </c>
-      <c r="G141" s="4" t="inlineStr">
+      <c r="G142" s="4" t="inlineStr">
         <is>
           <t>BORDEAUX GAMBETTA</t>
         </is>
       </c>
-      <c r="H141" s="4" t="inlineStr">
+      <c r="H142" s="4" t="inlineStr">
         <is>
           <t>05 56 16 85 05</t>
         </is>
       </c>
-      <c r="I141" s="4" t="inlineStr"/>
-      <c r="J141" s="4" t="inlineStr"/>
-      <c r="K141" s="4" t="inlineStr"/>
-      <c r="L141" s="4" t="inlineStr"/>
-      <c r="M141" s="4" t="inlineStr"/>
-    </row>
-    <row r="142" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A142" s="6" t="inlineStr"/>
-      <c r="B142" s="6" t="inlineStr"/>
-      <c r="C142" s="6" t="inlineStr"/>
-      <c r="D142" s="6" t="inlineStr"/>
-      <c r="E142" s="6" t="inlineStr"/>
-      <c r="F142" s="6" t="inlineStr"/>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr"/>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>SERVICE MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="J142" s="6" t="inlineStr"/>
-      <c r="K142" s="6" t="inlineStr">
-        <is>
-          <t>05 56 16 85 05</t>
-        </is>
-      </c>
-      <c r="L142" s="6" t="inlineStr">
-        <is>
-          <t>maintenance@lecoq-sa.fr</t>
-        </is>
-      </c>
-      <c r="M142" s="6" t="inlineStr"/>
+      <c r="I142" s="4" t="inlineStr"/>
+      <c r="J142" s="4" t="inlineStr"/>
+      <c r="K142" s="4" t="inlineStr"/>
+      <c r="L142" s="4" t="inlineStr"/>
+      <c r="M142" s="4" t="inlineStr"/>
     </row>
     <row r="143" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A143" s="6" t="inlineStr"/>
@@ -5196,22 +5204,18 @@
       <c r="H143" s="6" t="inlineStr"/>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>KARINE ARENAS</t>
-        </is>
-      </c>
-      <c r="J143" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANTE MAINTENANCE</t>
-        </is>
-      </c>
+          <t>SERVICE MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr"/>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>05 56 16 85 00</t>
+          <t>05 56 16 85 05</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr">
         <is>
-          <t>k.arenas@lecoq-sa.fr</t>
+          <t>maintenance@lecoq-sa.fr</t>
         </is>
       </c>
       <c r="M143" s="6" t="inlineStr"/>
@@ -5227,14 +5231,22 @@
       <c r="H144" s="6" t="inlineStr"/>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>FABIENNE LARTIGAU</t>
-        </is>
-      </c>
-      <c r="J144" s="6" t="inlineStr"/>
-      <c r="K144" s="6" t="inlineStr"/>
+          <t>KARINE ARENAS</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>ASSISTANTE MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>05 56 16 85 00</t>
+        </is>
+      </c>
       <c r="L144" s="6" t="inlineStr">
         <is>
-          <t>f.lartigau@lecoq-sa.fr</t>
+          <t>k.arenas@lecoq-sa.fr</t>
         </is>
       </c>
       <c r="M144" s="6" t="inlineStr"/>
@@ -5250,206 +5262,194 @@
       <c r="H145" s="6" t="inlineStr"/>
       <c r="I145" s="6" t="inlineStr">
         <is>
+          <t>FABIENNE LARTIGAU</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr"/>
+      <c r="K145" s="6" t="inlineStr"/>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>f.lartigau@lecoq-sa.fr</t>
+        </is>
+      </c>
+      <c r="M145" s="6" t="inlineStr"/>
+    </row>
+    <row r="146" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A146" s="6" t="inlineStr"/>
+      <c r="B146" s="6" t="inlineStr"/>
+      <c r="C146" s="6" t="inlineStr"/>
+      <c r="D146" s="6" t="inlineStr"/>
+      <c r="E146" s="6" t="inlineStr"/>
+      <c r="F146" s="6" t="inlineStr"/>
+      <c r="G146" s="6" t="inlineStr"/>
+      <c r="H146" s="6" t="inlineStr"/>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
           <t>STÉPHANE MASCUNAN</t>
         </is>
       </c>
-      <c r="J145" s="6" t="inlineStr"/>
-      <c r="K145" s="6" t="inlineStr">
+      <c r="J146" s="6" t="inlineStr"/>
+      <c r="K146" s="6" t="inlineStr">
         <is>
           <t>06 08 55 77 74</t>
         </is>
       </c>
-      <c r="L145" s="6" t="inlineStr">
+      <c r="L146" s="6" t="inlineStr">
         <is>
           <t>s.mascunan@lecoq-sa.fr</t>
         </is>
       </c>
-      <c r="M145" s="6" t="inlineStr"/>
-    </row>
-    <row r="146" ht="28.8" customHeight="1">
-      <c r="A146" s="4" t="inlineStr">
+      <c r="M146" s="6" t="inlineStr"/>
+    </row>
+    <row r="147" ht="28.8" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="B147" s="5" t="inlineStr">
         <is>
           <t>LOIRE AUTOMATISMES SERVICES</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="C147" s="5" t="inlineStr">
         <is>
           <t>FSLO0069</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D147" s="4" t="inlineStr">
         <is>
           <t>LOIRE AUTOMATISMES SERVIC</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
+      <c r="E147" s="4" t="inlineStr">
         <is>
           <t>PORTE AUTOMATIQUE</t>
         </is>
       </c>
-      <c r="F146" s="4" t="inlineStr">
+      <c r="F147" s="4" t="inlineStr">
         <is>
           <t>OUEST</t>
         </is>
       </c>
-      <c r="G146" s="4" t="inlineStr">
+      <c r="G147" s="4" t="inlineStr">
         <is>
           <t>LA ROCHE SUR YON 2</t>
         </is>
       </c>
-      <c r="H146" s="4" t="inlineStr"/>
-      <c r="I146" s="4" t="inlineStr"/>
-      <c r="J146" s="4" t="inlineStr"/>
-      <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="4" t="inlineStr"/>
-      <c r="M146" s="4" t="inlineStr"/>
-    </row>
-    <row r="147" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A147" s="6" t="inlineStr"/>
-      <c r="B147" s="6" t="inlineStr"/>
-      <c r="C147" s="6" t="inlineStr"/>
-      <c r="D147" s="6" t="inlineStr"/>
-      <c r="E147" s="6" t="inlineStr"/>
-      <c r="F147" s="6" t="inlineStr"/>
-      <c r="G147" s="6" t="inlineStr"/>
-      <c r="H147" s="6" t="inlineStr"/>
-      <c r="I147" s="6" t="inlineStr">
+      <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr"/>
+      <c r="J147" s="4" t="inlineStr"/>
+      <c r="K147" s="4" t="inlineStr"/>
+      <c r="L147" s="4" t="inlineStr"/>
+      <c r="M147" s="4" t="inlineStr"/>
+    </row>
+    <row r="148" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A148" s="6" t="inlineStr"/>
+      <c r="B148" s="6" t="inlineStr"/>
+      <c r="C148" s="6" t="inlineStr"/>
+      <c r="D148" s="6" t="inlineStr"/>
+      <c r="E148" s="6" t="inlineStr"/>
+      <c r="F148" s="6" t="inlineStr"/>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="6" t="inlineStr"/>
+      <c r="I148" s="6" t="inlineStr">
         <is>
           <t>FABRICE COUNILLE</t>
         </is>
       </c>
-      <c r="J147" s="6" t="inlineStr"/>
-      <c r="K147" s="6" t="inlineStr">
+      <c r="J148" s="6" t="inlineStr"/>
+      <c r="K148" s="6" t="inlineStr">
         <is>
           <t>09 84 10 10 78 / 06 84 87 44 39</t>
         </is>
       </c>
-      <c r="L147" s="6" t="inlineStr">
+      <c r="L148" s="6" t="inlineStr">
         <is>
           <t>contact@loire-automatismes-services.fr</t>
         </is>
       </c>
-      <c r="M147" s="6" t="inlineStr"/>
-    </row>
-    <row r="148" ht="15.9" customHeight="1">
-      <c r="A148" s="4" t="inlineStr">
+      <c r="M148" s="6" t="inlineStr"/>
+    </row>
+    <row r="149" ht="67.5" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
         </is>
       </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>LUSTRAL</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr"/>
+      <c r="D149" s="4" t="inlineStr"/>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>MÉNAGE</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>EST ; NORD</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr"/>
+      <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" s="4" t="inlineStr"/>
+      <c r="J149" s="4" t="inlineStr"/>
+      <c r="K149" s="4" t="inlineStr"/>
+      <c r="L149" s="4" t="inlineStr"/>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE SECTEURS EST ET NORD ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="15.9" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
         <is>
           <t>MATHIS&amp;PHILIP</t>
         </is>
       </c>
-      <c r="C148" s="5" t="inlineStr">
+      <c r="C150" s="5" t="inlineStr">
         <is>
           <t>FSMA0109</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="D150" s="4" t="inlineStr">
         <is>
           <t>MATHIS &amp; PHILIP</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
+      <c r="E150" s="4" t="inlineStr">
         <is>
           <t>CHAUFFAGISTE</t>
         </is>
       </c>
-      <c r="F148" s="4" t="inlineStr">
+      <c r="F150" s="4" t="inlineStr">
         <is>
           <t>EST</t>
         </is>
       </c>
-      <c r="G148" s="4" t="inlineStr">
+      <c r="G150" s="4" t="inlineStr">
         <is>
           <t>VITTEL</t>
         </is>
       </c>
-      <c r="H148" s="4" t="inlineStr"/>
-      <c r="I148" s="4" t="inlineStr"/>
-      <c r="J148" s="4" t="inlineStr"/>
-      <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="4" t="inlineStr"/>
-      <c r="M148" s="4" t="inlineStr"/>
-    </row>
-    <row r="149" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A149" s="6" t="inlineStr"/>
-      <c r="B149" s="6" t="inlineStr"/>
-      <c r="C149" s="6" t="inlineStr"/>
-      <c r="D149" s="6" t="inlineStr"/>
-      <c r="E149" s="6" t="inlineStr"/>
-      <c r="F149" s="6" t="inlineStr"/>
-      <c r="G149" s="6" t="inlineStr"/>
-      <c r="H149" s="6" t="inlineStr"/>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>ISABELLE ANTOINE</t>
-        </is>
-      </c>
-      <c r="J149" s="6" t="inlineStr"/>
-      <c r="K149" s="6" t="inlineStr">
-        <is>
-          <t>03 29 08 01 02</t>
-        </is>
-      </c>
-      <c r="L149" s="6" t="inlineStr">
-        <is>
-          <t>i.antoine@mathisetphilip.com</t>
-        </is>
-      </c>
-      <c r="M149" s="6" t="inlineStr"/>
-    </row>
-    <row r="150" ht="67.5" customHeight="1">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="inlineStr">
-        <is>
-          <t>MTE LOGISTIC</t>
-        </is>
-      </c>
-      <c r="C150" s="5" t="inlineStr"/>
-      <c r="D150" s="4" t="inlineStr"/>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>RIDEAU METALLIQUE ; MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>EST ; SUD OUEST</t>
-        </is>
-      </c>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>CHALON 2 ; BERGERAC, CHALON 2</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>04 74 45 56 46</t>
-        </is>
-      </c>
+      <c r="H150" s="4" t="inlineStr"/>
       <c r="I150" s="4" t="inlineStr"/>
       <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr"/>
       <c r="L150" s="4" t="inlineStr"/>
-      <c r="M150" s="4" t="inlineStr">
-        <is>
-          <t>SAISI 2 FOIS DANS LES SOURCES (« ANNUAIRE FRN CONTRATS » (RIDEAU METALLIQUE) + « ANNUAIRE FRN CONTRATS » (MAINTENANCE)) : LIGNES FUSIONNÉES, DOMAINES CUMULÉS ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="M150" s="4" t="inlineStr"/>
+    </row>
+    <row r="151" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A151" s="6" t="inlineStr"/>
       <c r="B151" s="6" t="inlineStr"/>
       <c r="C151" s="6" t="inlineStr"/>
@@ -5460,46 +5460,66 @@
       <c r="H151" s="6" t="inlineStr"/>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>PATRICIA RAMAKERS</t>
-        </is>
-      </c>
-      <c r="J151" s="6" t="inlineStr">
-        <is>
-          <t>MANAGER</t>
-        </is>
-      </c>
-      <c r="K151" s="6" t="inlineStr"/>
+          <t>ISABELLE ANTOINE</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="inlineStr"/>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>03 29 08 01 02</t>
+        </is>
+      </c>
       <c r="L151" s="6" t="inlineStr">
         <is>
-          <t>patricia.ramakers@mtelogistic.com</t>
+          <t>i.antoine@mathisetphilip.com</t>
         </is>
       </c>
       <c r="M151" s="6" t="inlineStr"/>
     </row>
-    <row r="152" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A152" s="6" t="inlineStr"/>
-      <c r="B152" s="6" t="inlineStr"/>
-      <c r="C152" s="6" t="inlineStr"/>
-      <c r="D152" s="6" t="inlineStr"/>
-      <c r="E152" s="6" t="inlineStr"/>
-      <c r="F152" s="6" t="inlineStr"/>
-      <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="6" t="inlineStr"/>
-      <c r="I152" s="6" t="inlineStr">
-        <is>
-          <t>AURORE NAPOLITANO</t>
-        </is>
-      </c>
-      <c r="J152" s="6" t="inlineStr"/>
-      <c r="K152" s="6" t="inlineStr"/>
-      <c r="L152" s="6" t="inlineStr">
-        <is>
-          <t>aurore.napolitano@mtelogistic.com</t>
-        </is>
-      </c>
-      <c r="M152" s="6" t="inlineStr"/>
-    </row>
-    <row r="153" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="152" ht="67.5" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>MTE LOGISTIC</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr"/>
+      <c r="D152" s="4" t="inlineStr"/>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>RIDEAU METALLIQUE ; MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>EST ; SUD OUEST</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>CHALON 2 ; BERGERAC, CHALON 2</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>04 74 45 56 46</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr"/>
+      <c r="J152" s="4" t="inlineStr"/>
+      <c r="K152" s="4" t="inlineStr"/>
+      <c r="L152" s="4" t="inlineStr"/>
+      <c r="M152" s="4" t="inlineStr">
+        <is>
+          <t>SAISI 2 FOIS DANS LES SOURCES (« ANNUAIRE FRN CONTRATS » (RIDEAU METALLIQUE) + « ANNUAIRE FRN CONTRATS » (MAINTENANCE)) : LIGNES FUSIONNÉES, DOMAINES CUMULÉS ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A153" s="6" t="inlineStr"/>
       <c r="B153" s="6" t="inlineStr"/>
       <c r="C153" s="6" t="inlineStr"/>
@@ -5510,54 +5530,46 @@
       <c r="H153" s="6" t="inlineStr"/>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>CONTACT SAV DÉPANNAGES</t>
-        </is>
-      </c>
-      <c r="J153" s="6" t="inlineStr"/>
-      <c r="K153" s="6" t="inlineStr">
-        <is>
-          <t>04 74 45 56 46</t>
-        </is>
-      </c>
+          <t>PATRICIA RAMAKERS</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="inlineStr">
+        <is>
+          <t>MANAGER</t>
+        </is>
+      </c>
+      <c r="K153" s="6" t="inlineStr"/>
       <c r="L153" s="6" t="inlineStr">
         <is>
-          <t>contact@mtelogistic.com</t>
+          <t>patricia.ramakers@mtelogistic.com</t>
         </is>
       </c>
       <c r="M153" s="6" t="inlineStr"/>
     </row>
-    <row r="154" outlineLevel="1" ht="41.7" customHeight="1">
+    <row r="154" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A154" s="6" t="inlineStr"/>
       <c r="B154" s="6" t="inlineStr"/>
       <c r="C154" s="6" t="inlineStr"/>
       <c r="D154" s="6" t="inlineStr"/>
       <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="6" t="inlineStr">
-        <is>
-          <t>SUD OUEST</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr">
-        <is>
-          <t>BERGERAC, CHALON 2</t>
-        </is>
-      </c>
+      <c r="F154" s="6" t="inlineStr"/>
+      <c r="G154" s="6" t="inlineStr"/>
       <c r="H154" s="6" t="inlineStr"/>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>BOÎTE GÉNÉRIQUE (À METTRE EN COPIE SYSTÉMATIQUE ET DESTINATAIRE)</t>
+          <t>AURORE NAPOLITANO</t>
         </is>
       </c>
       <c r="J154" s="6" t="inlineStr"/>
       <c r="K154" s="6" t="inlineStr"/>
       <c r="L154" s="6" t="inlineStr">
         <is>
-          <t>contact@mtelogistic.com</t>
+          <t>aurore.napolitano@mtelogistic.com</t>
         </is>
       </c>
       <c r="M154" s="6" t="inlineStr"/>
     </row>
-    <row r="155" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="155" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A155" s="6" t="inlineStr"/>
       <c r="B155" s="6" t="inlineStr"/>
       <c r="C155" s="6" t="inlineStr"/>
@@ -5568,45 +5580,49 @@
       <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>CYRIELLE GENTON</t>
+          <t>CONTACT SAV DÉPANNAGES</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr"/>
-      <c r="K155" s="6" t="inlineStr"/>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>04 74 45 56 46</t>
+        </is>
+      </c>
       <c r="L155" s="6" t="inlineStr">
         <is>
-          <t>cyrielle.genton@mtelogistic.com</t>
+          <t>contact@mtelogistic.com</t>
         </is>
       </c>
       <c r="M155" s="6" t="inlineStr"/>
     </row>
-    <row r="156" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="156" outlineLevel="1" ht="41.7" customHeight="1">
       <c r="A156" s="6" t="inlineStr"/>
       <c r="B156" s="6" t="inlineStr"/>
       <c r="C156" s="6" t="inlineStr"/>
       <c r="D156" s="6" t="inlineStr"/>
       <c r="E156" s="6" t="inlineStr"/>
-      <c r="F156" s="6" t="inlineStr"/>
-      <c r="G156" s="6" t="inlineStr"/>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>SUD OUEST</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>BERGERAC, CHALON 2</t>
+        </is>
+      </c>
       <c r="H156" s="6" t="inlineStr"/>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>ALINE ROSSET</t>
-        </is>
-      </c>
-      <c r="J156" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANTE COMMERCIALE</t>
-        </is>
-      </c>
-      <c r="K156" s="6" t="inlineStr">
-        <is>
-          <t>04 74 45 56 46 / 06 70 65 57 43</t>
-        </is>
-      </c>
+          <t>BOÎTE GÉNÉRIQUE (À METTRE EN COPIE SYSTÉMATIQUE ET DESTINATAIRE)</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="inlineStr"/>
+      <c r="K156" s="6" t="inlineStr"/>
       <c r="L156" s="6" t="inlineStr">
         <is>
-          <t>aline.rosset@mtelogistic.com</t>
+          <t>contact@mtelogistic.com</t>
         </is>
       </c>
       <c r="M156" s="6" t="inlineStr"/>
@@ -5622,70 +5638,50 @@
       <c r="H157" s="6" t="inlineStr"/>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>PATRICIA RAMAKERS</t>
-        </is>
-      </c>
-      <c r="J157" s="6" t="inlineStr">
-        <is>
-          <t>DIRIGEANTE</t>
-        </is>
-      </c>
-      <c r="K157" s="6" t="inlineStr">
-        <is>
-          <t>04 74 45 56 46 / 06 48 44 91 44</t>
-        </is>
-      </c>
+          <t>CYRIELLE GENTON</t>
+        </is>
+      </c>
+      <c r="J157" s="6" t="inlineStr"/>
+      <c r="K157" s="6" t="inlineStr"/>
       <c r="L157" s="6" t="inlineStr">
         <is>
-          <t>patricia.ramakers@mtelogistic.com</t>
+          <t>cyrielle.genton@mtelogistic.com</t>
         </is>
       </c>
       <c r="M157" s="6" t="inlineStr"/>
     </row>
-    <row r="158" ht="15.9" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B158" s="5" t="inlineStr">
-        <is>
-          <t>NISSE FRERES</t>
-        </is>
-      </c>
-      <c r="C158" s="5" t="inlineStr">
-        <is>
-          <t>FSNI0015</t>
-        </is>
-      </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>NISSE FRERES</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>CHAUFFAGISTE</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>EST</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>SARREBOURG</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr"/>
-      <c r="I158" s="4" t="inlineStr"/>
-      <c r="J158" s="4" t="inlineStr"/>
-      <c r="K158" s="4" t="inlineStr"/>
-      <c r="L158" s="4" t="inlineStr"/>
-      <c r="M158" s="4" t="inlineStr"/>
-    </row>
-    <row r="159" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="158" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A158" s="6" t="inlineStr"/>
+      <c r="B158" s="6" t="inlineStr"/>
+      <c r="C158" s="6" t="inlineStr"/>
+      <c r="D158" s="6" t="inlineStr"/>
+      <c r="E158" s="6" t="inlineStr"/>
+      <c r="F158" s="6" t="inlineStr"/>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="6" t="inlineStr"/>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>ALINE ROSSET</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="inlineStr">
+        <is>
+          <t>ASSISTANTE COMMERCIALE</t>
+        </is>
+      </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>04 74 45 56 46 / 06 70 65 57 43</t>
+        </is>
+      </c>
+      <c r="L158" s="6" t="inlineStr">
+        <is>
+          <t>aline.rosset@mtelogistic.com</t>
+        </is>
+      </c>
+      <c r="M158" s="6" t="inlineStr"/>
+    </row>
+    <row r="159" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A159" s="6" t="inlineStr"/>
       <c r="B159" s="6" t="inlineStr"/>
       <c r="C159" s="6" t="inlineStr"/>
@@ -5696,27 +5692,27 @@
       <c r="H159" s="6" t="inlineStr"/>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>JEAN-BERNARD KUHL</t>
+          <t>PATRICIA RAMAKERS</t>
         </is>
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>GÉRANT</t>
+          <t>DIRIGEANTE</t>
         </is>
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>03 87 03 17 15</t>
+          <t>04 74 45 56 46 / 06 48 44 91 44</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr">
         <is>
-          <t>info@nisse.fr</t>
+          <t>patricia.ramakers@mtelogistic.com</t>
         </is>
       </c>
       <c r="M159" s="6" t="inlineStr"/>
     </row>
-    <row r="160" ht="41.7" customHeight="1">
+    <row r="160" ht="67.5" customHeight="1">
       <c r="A160" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
@@ -5724,104 +5720,108 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>OLEA SERVICES</t>
-        </is>
-      </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>FSOL0006</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="inlineStr">
-        <is>
-          <t>OLEA SERVICES</t>
-        </is>
-      </c>
+          <t>NETIJY</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr"/>
+      <c r="D160" s="4" t="inlineStr"/>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>RIDEAU METALLIQUE ; BARRIERES AUTO PARKING</t>
+          <t>MÉNAGE</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>MARSEILLE SÉBASTOPOL ; BOURG EN BRESSE 2</t>
-        </is>
-      </c>
-      <c r="H160" s="4" t="inlineStr">
-        <is>
-          <t>02 49 62 09 24</t>
-        </is>
-      </c>
+          <t>OUEST ; SUD OUEST</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr"/>
+      <c r="H160" s="4" t="inlineStr"/>
       <c r="I160" s="4" t="inlineStr"/>
       <c r="J160" s="4" t="inlineStr"/>
       <c r="K160" s="4" t="inlineStr"/>
       <c r="L160" s="4" t="inlineStr"/>
-      <c r="M160" s="4" t="inlineStr"/>
-    </row>
-    <row r="161" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A161" s="6" t="inlineStr"/>
-      <c r="B161" s="6" t="inlineStr"/>
-      <c r="C161" s="6" t="inlineStr"/>
-      <c r="D161" s="6" t="inlineStr"/>
-      <c r="E161" s="6" t="inlineStr"/>
-      <c r="F161" s="6" t="inlineStr"/>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="6" t="inlineStr"/>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="J161" s="6" t="inlineStr">
-        <is>
-          <t>PRÉCISER SITE, LOCALISATION, SI DÉPANNAGE OU DEVIS</t>
-        </is>
-      </c>
-      <c r="K161" s="6" t="inlineStr">
-        <is>
-          <t>02 49 62 09 24</t>
-        </is>
-      </c>
-      <c r="L161" s="6" t="inlineStr">
-        <is>
-          <t>oleasav@olea-services.com</t>
-        </is>
-      </c>
-      <c r="M161" s="6" t="inlineStr"/>
-    </row>
-    <row r="162" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="M160" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE SECTEURS OUEST ET SUD-OUEST ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="15.9" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>NISSE FRERES</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>FSNI0015</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>NISSE FRERES</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>SARREBOURG</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr"/>
+      <c r="K161" s="4" t="inlineStr"/>
+      <c r="L161" s="4" t="inlineStr"/>
+      <c r="M161" s="4" t="inlineStr"/>
+    </row>
+    <row r="162" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A162" s="6" t="inlineStr"/>
       <c r="B162" s="6" t="inlineStr"/>
       <c r="C162" s="6" t="inlineStr"/>
       <c r="D162" s="6" t="inlineStr"/>
       <c r="E162" s="6" t="inlineStr"/>
       <c r="F162" s="6" t="inlineStr"/>
-      <c r="G162" s="6" t="inlineStr">
-        <is>
-          <t>BOURG EN BRESSE 2</t>
-        </is>
-      </c>
+      <c r="G162" s="6" t="inlineStr"/>
       <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>NICOLAS THEOT</t>
+          <t>JEAN-BERNARD KUHL</t>
         </is>
       </c>
       <c r="J162" s="6" t="inlineStr">
         <is>
-          <t>RESPONSABLE SERVICE CLIENTS &amp; PARTENARIATS</t>
-        </is>
-      </c>
-      <c r="K162" s="6" t="inlineStr"/>
-      <c r="L162" s="6" t="inlineStr"/>
+          <t>GÉRANT</t>
+        </is>
+      </c>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>03 87 03 17 15</t>
+        </is>
+      </c>
+      <c r="L162" s="6" t="inlineStr">
+        <is>
+          <t>info@nisse.fr</t>
+        </is>
+      </c>
       <c r="M162" s="6" t="inlineStr"/>
     </row>
-    <row r="163" ht="15.9" customHeight="1">
+    <row r="163" ht="41.7" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
@@ -5829,37 +5829,37 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>PELTIER EURL (GROUPE CHAM)</t>
+          <t>OLEA SERVICES</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>FSPE0031</t>
+          <t>FSOL0006</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>PELTIER EURL</t>
+          <t>OLEA SERVICES</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>CHAUFFAGISTE</t>
+          <t>RIDEAU METALLIQUE ; BARRIERES AUTO PARKING</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>SUD OUEST</t>
+          <t>SUD EST</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>SAINT JEAN DE LUZ</t>
+          <t>MARSEILLE SÉBASTOPOL ; BOURG EN BRESSE 2</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>05 59 54 01 32</t>
+          <t>02 49 62 09 24</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr"/>
@@ -5868,7 +5868,7 @@
       <c r="L163" s="4" t="inlineStr"/>
       <c r="M163" s="4" t="inlineStr"/>
     </row>
-    <row r="164" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="164" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A164" s="6" t="inlineStr"/>
       <c r="B164" s="6" t="inlineStr"/>
       <c r="C164" s="6" t="inlineStr"/>
@@ -5882,92 +5882,84 @@
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J164" s="6" t="inlineStr"/>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t>PRÉCISER SITE, LOCALISATION, SI DÉPANNAGE OU DEVIS</t>
+        </is>
+      </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>05 59 54 01 32</t>
+          <t>02 49 62 09 24</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr">
         <is>
-          <t>contact@peltier64.fr</t>
+          <t>oleasav@olea-services.com</t>
         </is>
       </c>
       <c r="M164" s="6" t="inlineStr"/>
     </row>
-    <row r="165" ht="54.6" customHeight="1">
-      <c r="A165" s="4" t="inlineStr">
+    <row r="165" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A165" s="6" t="inlineStr"/>
+      <c r="B165" s="6" t="inlineStr"/>
+      <c r="C165" s="6" t="inlineStr"/>
+      <c r="D165" s="6" t="inlineStr"/>
+      <c r="E165" s="6" t="inlineStr"/>
+      <c r="F165" s="6" t="inlineStr"/>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>BOURG EN BRESSE 2</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="inlineStr"/>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>NICOLAS THEOT</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>RESPONSABLE SERVICE CLIENTS &amp; PARTENARIATS</t>
+        </is>
+      </c>
+      <c r="K165" s="6" t="inlineStr"/>
+      <c r="L165" s="6" t="inlineStr"/>
+      <c r="M165" s="6" t="inlineStr"/>
+    </row>
+    <row r="166" ht="54.6" customHeight="1">
+      <c r="A166" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
         </is>
       </c>
-      <c r="B165" s="5" t="inlineStr">
-        <is>
-          <t>PORTALP</t>
-        </is>
-      </c>
-      <c r="C165" s="5" t="inlineStr">
-        <is>
-          <t>FSPO0011</t>
-        </is>
-      </c>
-      <c r="D165" s="4" t="inlineStr">
-        <is>
-          <t>PORTALP</t>
-        </is>
-      </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>PORTE AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="F165" s="4" t="inlineStr">
-        <is>
-          <t>FRANCE</t>
-        </is>
-      </c>
-      <c r="G165" s="4" t="inlineStr">
-        <is>
-          <t>PORTE : AUBAGNE, AUXERRE / PORTE+RIDEAU : VITRY LE FRANÇOIS, CHÂTEAUBRIANT</t>
-        </is>
-      </c>
-      <c r="H165" s="4" t="inlineStr">
-        <is>
-          <t>08 00 50 02 00</t>
-        </is>
-      </c>
-      <c r="I165" s="4" t="inlineStr"/>
-      <c r="J165" s="4" t="inlineStr"/>
-      <c r="K165" s="4" t="inlineStr"/>
-      <c r="L165" s="4" t="inlineStr"/>
-      <c r="M165" s="4" t="inlineStr"/>
-    </row>
-    <row r="166" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A166" s="6" t="inlineStr"/>
-      <c r="B166" s="6" t="inlineStr"/>
-      <c r="C166" s="6" t="inlineStr"/>
-      <c r="D166" s="6" t="inlineStr"/>
-      <c r="E166" s="6" t="inlineStr"/>
-      <c r="F166" s="6" t="inlineStr"/>
-      <c r="G166" s="6" t="inlineStr"/>
-      <c r="H166" s="6" t="inlineStr"/>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>PLATEFORME</t>
-        </is>
-      </c>
-      <c r="J166" s="6" t="inlineStr"/>
-      <c r="K166" s="6" t="inlineStr">
-        <is>
-          <t>08 00 50 02 00</t>
-        </is>
-      </c>
-      <c r="L166" s="6" t="inlineStr">
-        <is>
-          <t>callcenterportalp@portalp.fr</t>
-        </is>
-      </c>
-      <c r="M166" s="6" t="inlineStr"/>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>OOVOOM FLEET</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr"/>
+      <c r="D166" s="4" t="inlineStr"/>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>GESTION DE FLOTTE</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr"/>
+      <c r="G166" s="4" t="inlineStr"/>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>01 80 82 44 44</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr"/>
+      <c r="J166" s="4" t="inlineStr"/>
+      <c r="K166" s="4" t="inlineStr"/>
+      <c r="L166" s="4" t="inlineStr"/>
+      <c r="M166" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; 59 BOULEVARD EXELMANS, 75016 PARIS ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
+        </is>
+      </c>
     </row>
     <row r="167" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A167" s="6" t="inlineStr"/>
@@ -5980,42 +5972,66 @@
       <c r="H167" s="6" t="inlineStr"/>
       <c r="I167" s="6" t="inlineStr">
         <is>
-          <t>SAV FRANCE</t>
+          <t>SANDRA BIBAS</t>
         </is>
       </c>
       <c r="J167" s="6" t="inlineStr"/>
-      <c r="K167" s="6" t="inlineStr"/>
-      <c r="L167" s="6" t="inlineStr">
-        <is>
-          <t>sav.france@portalp.com</t>
-        </is>
-      </c>
+      <c r="K167" s="6" t="inlineStr">
+        <is>
+          <t>06 88 39 35 03</t>
+        </is>
+      </c>
+      <c r="L167" s="6" t="inlineStr"/>
       <c r="M167" s="6" t="inlineStr"/>
     </row>
-    <row r="168" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A168" s="6" t="inlineStr"/>
-      <c r="B168" s="6" t="inlineStr"/>
-      <c r="C168" s="6" t="inlineStr"/>
-      <c r="D168" s="6" t="inlineStr"/>
-      <c r="E168" s="6" t="inlineStr"/>
-      <c r="F168" s="6" t="inlineStr"/>
-      <c r="G168" s="6" t="inlineStr"/>
-      <c r="H168" s="6" t="inlineStr"/>
-      <c r="I168" s="6" t="inlineStr">
-        <is>
-          <t>AGENCE CHAMPAGNE ARDENNE (VITRY-LE-FRANÇOIS)</t>
-        </is>
-      </c>
-      <c r="J168" s="6" t="inlineStr"/>
-      <c r="K168" s="6" t="inlineStr">
-        <is>
-          <t>03 26 97 25 40</t>
-        </is>
-      </c>
-      <c r="L168" s="6" t="inlineStr"/>
-      <c r="M168" s="6" t="inlineStr"/>
-    </row>
-    <row r="169" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="168" ht="15.9" customHeight="1">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>PELTIER EURL (GROUPE CHAM)</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>FSPE0031</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>PELTIER EURL</t>
+        </is>
+      </c>
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
+        <is>
+          <t>SUD OUEST</t>
+        </is>
+      </c>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>SAINT JEAN DE LUZ</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>05 59 54 01 32</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr"/>
+      <c r="J168" s="4" t="inlineStr"/>
+      <c r="K168" s="4" t="inlineStr"/>
+      <c r="L168" s="4" t="inlineStr"/>
+      <c r="M168" s="4" t="inlineStr"/>
+    </row>
+    <row r="169" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A169" s="6" t="inlineStr"/>
       <c r="B169" s="6" t="inlineStr"/>
       <c r="C169" s="6" t="inlineStr"/>
@@ -6026,56 +6042,52 @@
       <c r="H169" s="6" t="inlineStr"/>
       <c r="I169" s="6" t="inlineStr">
         <is>
-          <t>EMILIE BEGHIN</t>
-        </is>
-      </c>
-      <c r="J169" s="6" t="inlineStr">
-        <is>
-          <t>CHARGÉE D'AFFAIRES CHAMPAGNE ARDENNES</t>
-        </is>
-      </c>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="J169" s="6" t="inlineStr"/>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>06 58 06 94 73</t>
+          <t>05 59 54 01 32</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr">
         <is>
-          <t>e.beghin@portalp.com</t>
+          <t>contact@peltier64.fr</t>
         </is>
       </c>
       <c r="M169" s="6" t="inlineStr"/>
     </row>
-    <row r="170" outlineLevel="1" ht="41.7" customHeight="1">
-      <c r="A170" s="6" t="inlineStr"/>
-      <c r="B170" s="6" t="inlineStr"/>
-      <c r="C170" s="6" t="inlineStr"/>
-      <c r="D170" s="6" t="inlineStr"/>
-      <c r="E170" s="6" t="inlineStr"/>
-      <c r="F170" s="6" t="inlineStr"/>
-      <c r="G170" s="6" t="inlineStr"/>
-      <c r="H170" s="6" t="inlineStr"/>
-      <c r="I170" s="6" t="inlineStr">
-        <is>
-          <t>HÉLÈNE SERRE (AGENCE À AZAY LE BRULE 79, CTRE CHÂTEAUBRIANT)</t>
-        </is>
-      </c>
-      <c r="J170" s="6" t="inlineStr">
-        <is>
-          <t>CHARGÉE DE CLIENTÈLE</t>
-        </is>
-      </c>
-      <c r="K170" s="6" t="inlineStr">
-        <is>
-          <t>05 49 77 59 07 / 07 63 63 66 53</t>
-        </is>
-      </c>
-      <c r="L170" s="6" t="inlineStr">
-        <is>
-          <t>hserre@portalp.com</t>
-        </is>
-      </c>
-      <c r="M170" s="6" t="inlineStr"/>
+    <row r="170" ht="54.6" customHeight="1">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>PÉNÉLOPE GROUPE</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr"/>
+      <c r="D170" s="4" t="inlineStr"/>
+      <c r="E170" s="4" t="inlineStr"/>
+      <c r="F170" s="4" t="inlineStr"/>
+      <c r="G170" s="4" t="inlineStr"/>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>01 42 09 10 00</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr"/>
+      <c r="J170" s="4" t="inlineStr"/>
+      <c r="K170" s="4" t="inlineStr"/>
+      <c r="L170" s="4" t="inlineStr"/>
+      <c r="M170" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; 52 RUE TAITBOUT, PARIS ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; DOMAINE D’ACTIVITÉ À PRÉCISER</t>
+        </is>
+      </c>
     </row>
     <row r="171" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A171" s="6" t="inlineStr"/>
@@ -6088,48 +6100,68 @@
       <c r="H171" s="6" t="inlineStr"/>
       <c r="I171" s="6" t="inlineStr">
         <is>
-          <t>AGENCE BORDEAUX (BAYONNE ST ESPRIT)</t>
+          <t>O. KOJCIC</t>
         </is>
       </c>
       <c r="J171" s="6" t="inlineStr"/>
-      <c r="K171" s="6" t="inlineStr">
-        <is>
-          <t>05 56 13 47 41</t>
-        </is>
-      </c>
-      <c r="L171" s="6" t="inlineStr"/>
-      <c r="M171" s="6" t="inlineStr"/>
-    </row>
-    <row r="172" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A172" s="6" t="inlineStr"/>
-      <c r="B172" s="6" t="inlineStr"/>
-      <c r="C172" s="6" t="inlineStr"/>
-      <c r="D172" s="6" t="inlineStr"/>
-      <c r="E172" s="6" t="inlineStr"/>
-      <c r="F172" s="6" t="inlineStr"/>
-      <c r="G172" s="6" t="inlineStr"/>
-      <c r="H172" s="6" t="inlineStr"/>
-      <c r="I172" s="6" t="inlineStr">
-        <is>
-          <t>SANDRA BRUNETEAU (BAYONNE ST ESPRIT)</t>
-        </is>
-      </c>
-      <c r="J172" s="6" t="inlineStr">
-        <is>
-          <t>CHARGÉE DE CLIENTÈLE (AGENCE BORDEAUX MÉRIGNAC)</t>
-        </is>
-      </c>
-      <c r="K172" s="6" t="inlineStr">
-        <is>
-          <t>05 56 13 47 46 / 06 68 96 54 40</t>
-        </is>
-      </c>
-      <c r="L172" s="6" t="inlineStr">
-        <is>
-          <t>sbruneteau@portalp.com</t>
-        </is>
-      </c>
-      <c r="M172" s="6" t="inlineStr"/>
+      <c r="K171" s="6" t="inlineStr"/>
+      <c r="L171" s="6" t="inlineStr">
+        <is>
+          <t>o.kojcic@penelope.fr</t>
+        </is>
+      </c>
+      <c r="M171" s="6" t="inlineStr">
+        <is>
+          <t>NOM DÉDUIT DE L'ADRESSE COURRIEL, À CONFIRMER</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="54.6" customHeight="1">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>PORTALP</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>FSPO0011</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>PORTALP</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>PORTE AUTOMATIQUE</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr">
+        <is>
+          <t>FRANCE</t>
+        </is>
+      </c>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>PORTE : AUBAGNE, AUXERRE / PORTE+RIDEAU : VITRY LE FRANÇOIS, CHÂTEAUBRIANT</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>08 00 50 02 00</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr"/>
+      <c r="J172" s="4" t="inlineStr"/>
+      <c r="K172" s="4" t="inlineStr"/>
+      <c r="L172" s="4" t="inlineStr"/>
+      <c r="M172" s="4" t="inlineStr"/>
     </row>
     <row r="173" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A173" s="6" t="inlineStr"/>
@@ -6142,70 +6174,46 @@
       <c r="H173" s="6" t="inlineStr"/>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t>ANTOINE ZEUD</t>
-        </is>
-      </c>
-      <c r="J173" s="6" t="inlineStr">
-        <is>
-          <t>CHARGÉ D'AFFAIRES BORDEAUX</t>
-        </is>
-      </c>
+          <t>PLATEFORME</t>
+        </is>
+      </c>
+      <c r="J173" s="6" t="inlineStr"/>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>06 66 33 41 58</t>
-        </is>
-      </c>
-      <c r="L173" s="6" t="inlineStr"/>
+          <t>08 00 50 02 00</t>
+        </is>
+      </c>
+      <c r="L173" s="6" t="inlineStr">
+        <is>
+          <t>callcenterportalp@portalp.fr</t>
+        </is>
+      </c>
       <c r="M173" s="6" t="inlineStr"/>
     </row>
-    <row r="174" ht="15.9" customHeight="1">
-      <c r="A174" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B174" s="5" t="inlineStr">
-        <is>
-          <t>PROXI GAZ ABITIBI</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="inlineStr">
-        <is>
-          <t>FSPR0042</t>
-        </is>
-      </c>
-      <c r="D174" s="4" t="inlineStr">
-        <is>
-          <t>PROXI GAZ SERVICE</t>
-        </is>
-      </c>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>CHAUFFAGISTE</t>
-        </is>
-      </c>
-      <c r="F174" s="4" t="inlineStr">
-        <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G174" s="4" t="inlineStr">
-        <is>
-          <t>LYON VENDÔME</t>
-        </is>
-      </c>
-      <c r="H174" s="4" t="inlineStr">
-        <is>
-          <t>04 78 17 20 13</t>
-        </is>
-      </c>
-      <c r="I174" s="4" t="inlineStr"/>
-      <c r="J174" s="4" t="inlineStr"/>
-      <c r="K174" s="4" t="inlineStr"/>
-      <c r="L174" s="4" t="inlineStr"/>
-      <c r="M174" s="4" t="inlineStr"/>
-    </row>
-    <row r="175" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="174" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A174" s="6" t="inlineStr"/>
+      <c r="B174" s="6" t="inlineStr"/>
+      <c r="C174" s="6" t="inlineStr"/>
+      <c r="D174" s="6" t="inlineStr"/>
+      <c r="E174" s="6" t="inlineStr"/>
+      <c r="F174" s="6" t="inlineStr"/>
+      <c r="G174" s="6" t="inlineStr"/>
+      <c r="H174" s="6" t="inlineStr"/>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>SAV FRANCE</t>
+        </is>
+      </c>
+      <c r="J174" s="6" t="inlineStr"/>
+      <c r="K174" s="6" t="inlineStr"/>
+      <c r="L174" s="6" t="inlineStr">
+        <is>
+          <t>sav.france@portalp.com</t>
+        </is>
+      </c>
+      <c r="M174" s="6" t="inlineStr"/>
+    </row>
+    <row r="175" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A175" s="6" t="inlineStr"/>
       <c r="B175" s="6" t="inlineStr"/>
       <c r="C175" s="6" t="inlineStr"/>
@@ -6216,23 +6224,19 @@
       <c r="H175" s="6" t="inlineStr"/>
       <c r="I175" s="6" t="inlineStr">
         <is>
-          <t>STANDARD</t>
+          <t>AGENCE CHAMPAGNE ARDENNE (VITRY-LE-FRANÇOIS)</t>
         </is>
       </c>
       <c r="J175" s="6" t="inlineStr"/>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>04 78 17 20 13</t>
-        </is>
-      </c>
-      <c r="L175" s="6" t="inlineStr">
-        <is>
-          <t>contact@proxigazservice.fr</t>
-        </is>
-      </c>
+          <t>03 26 97 25 40</t>
+        </is>
+      </c>
+      <c r="L175" s="6" t="inlineStr"/>
       <c r="M175" s="6" t="inlineStr"/>
     </row>
-    <row r="176" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="176" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A176" s="6" t="inlineStr"/>
       <c r="B176" s="6" t="inlineStr"/>
       <c r="C176" s="6" t="inlineStr"/>
@@ -6243,70 +6247,58 @@
       <c r="H176" s="6" t="inlineStr"/>
       <c r="I176" s="6" t="inlineStr">
         <is>
-          <t>NATHALIE</t>
+          <t>EMILIE BEGHIN</t>
         </is>
       </c>
       <c r="J176" s="6" t="inlineStr">
         <is>
-          <t>SAV ABITIBI</t>
+          <t>CHARGÉE D'AFFAIRES CHAMPAGNE ARDENNES</t>
         </is>
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>04 78 37 42 72</t>
+          <t>06 58 06 94 73</t>
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr">
         <is>
-          <t>sav@abitibi.fr</t>
+          <t>e.beghin@portalp.com</t>
         </is>
       </c>
       <c r="M176" s="6" t="inlineStr"/>
     </row>
-    <row r="177" ht="15.9" customHeight="1">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
-        <is>
-          <t>RATAUD ASSAINISSEMENT</t>
-        </is>
-      </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>V000112</t>
-        </is>
-      </c>
-      <c r="D177" s="4" t="inlineStr">
-        <is>
-          <t>ASSAINISSEMENTS RATAUD</t>
-        </is>
-      </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>CANALISATIONS EU</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>OUEST</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="inlineStr">
-        <is>
-          <t>ST GILLES CROIX DE VIE</t>
-        </is>
-      </c>
-      <c r="H177" s="4" t="inlineStr"/>
-      <c r="I177" s="4" t="inlineStr"/>
-      <c r="J177" s="4" t="inlineStr"/>
-      <c r="K177" s="4" t="inlineStr"/>
-      <c r="L177" s="4" t="inlineStr"/>
-      <c r="M177" s="4" t="inlineStr"/>
-    </row>
-    <row r="178" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="177" outlineLevel="1" ht="41.7" customHeight="1">
+      <c r="A177" s="6" t="inlineStr"/>
+      <c r="B177" s="6" t="inlineStr"/>
+      <c r="C177" s="6" t="inlineStr"/>
+      <c r="D177" s="6" t="inlineStr"/>
+      <c r="E177" s="6" t="inlineStr"/>
+      <c r="F177" s="6" t="inlineStr"/>
+      <c r="G177" s="6" t="inlineStr"/>
+      <c r="H177" s="6" t="inlineStr"/>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>HÉLÈNE SERRE (AGENCE À AZAY LE BRULE 79, CTRE CHÂTEAUBRIANT)</t>
+        </is>
+      </c>
+      <c r="J177" s="6" t="inlineStr">
+        <is>
+          <t>CHARGÉE DE CLIENTÈLE</t>
+        </is>
+      </c>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t>05 49 77 59 07 / 07 63 63 66 53</t>
+        </is>
+      </c>
+      <c r="L177" s="6" t="inlineStr">
+        <is>
+          <t>hserre@portalp.com</t>
+        </is>
+      </c>
+      <c r="M177" s="6" t="inlineStr"/>
+    </row>
+    <row r="178" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A178" s="6" t="inlineStr"/>
       <c r="B178" s="6" t="inlineStr"/>
       <c r="C178" s="6" t="inlineStr"/>
@@ -6317,70 +6309,50 @@
       <c r="H178" s="6" t="inlineStr"/>
       <c r="I178" s="6" t="inlineStr">
         <is>
-          <t>JULIE RATAUD</t>
+          <t>AGENCE BORDEAUX (BAYONNE ST ESPRIT)</t>
         </is>
       </c>
       <c r="J178" s="6" t="inlineStr"/>
       <c r="K178" s="6" t="inlineStr">
         <is>
-          <t>02 51 55 86 44</t>
-        </is>
-      </c>
-      <c r="L178" s="6" t="inlineStr">
-        <is>
-          <t>sarlrataud@gmail.com</t>
-        </is>
-      </c>
+          <t>05 56 13 47 41</t>
+        </is>
+      </c>
+      <c r="L178" s="6" t="inlineStr"/>
       <c r="M178" s="6" t="inlineStr"/>
     </row>
-    <row r="179" ht="41.7" customHeight="1">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
-        <is>
-          <t>RECORD</t>
-        </is>
-      </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>FSRE0051</t>
-        </is>
-      </c>
-      <c r="D179" s="4" t="inlineStr">
-        <is>
-          <t>RECORD PORTES AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>PORTE AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="F179" s="4" t="inlineStr">
-        <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G179" s="4" t="inlineStr">
-        <is>
-          <t>BRIEY, BRON, CHALON2, CLAMECY, JONZAC, ST RÉMY, VALENCIENNES LUÇON</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr">
-        <is>
-          <t>08 09 10 01 22</t>
-        </is>
-      </c>
-      <c r="I179" s="4" t="inlineStr"/>
-      <c r="J179" s="4" t="inlineStr"/>
-      <c r="K179" s="4" t="inlineStr"/>
-      <c r="L179" s="4" t="inlineStr"/>
-      <c r="M179" s="4" t="inlineStr"/>
-    </row>
-    <row r="180" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="179" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A179" s="6" t="inlineStr"/>
+      <c r="B179" s="6" t="inlineStr"/>
+      <c r="C179" s="6" t="inlineStr"/>
+      <c r="D179" s="6" t="inlineStr"/>
+      <c r="E179" s="6" t="inlineStr"/>
+      <c r="F179" s="6" t="inlineStr"/>
+      <c r="G179" s="6" t="inlineStr"/>
+      <c r="H179" s="6" t="inlineStr"/>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>SANDRA BRUNETEAU (BAYONNE ST ESPRIT)</t>
+        </is>
+      </c>
+      <c r="J179" s="6" t="inlineStr">
+        <is>
+          <t>CHARGÉE DE CLIENTÈLE (AGENCE BORDEAUX MÉRIGNAC)</t>
+        </is>
+      </c>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t>05 56 13 47 46 / 06 68 96 54 40</t>
+        </is>
+      </c>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>sbruneteau@portalp.com</t>
+        </is>
+      </c>
+      <c r="M179" s="6" t="inlineStr"/>
+    </row>
+    <row r="180" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A180" s="6" t="inlineStr"/>
       <c r="B180" s="6" t="inlineStr"/>
       <c r="C180" s="6" t="inlineStr"/>
@@ -6391,58 +6363,70 @@
       <c r="H180" s="6" t="inlineStr"/>
       <c r="I180" s="6" t="inlineStr">
         <is>
-          <t>SERVICE FRONT OFFICE</t>
+          <t>ANTOINE ZEUD</t>
         </is>
       </c>
       <c r="J180" s="6" t="inlineStr">
         <is>
-          <t>RENSEIGNEMENT VISITES D'ENTRETIEN ET DÉPANNAGES</t>
+          <t>CHARGÉ D'AFFAIRES BORDEAUX</t>
         </is>
       </c>
       <c r="K180" s="6" t="inlineStr">
         <is>
-          <t>08 09 10 01 22</t>
-        </is>
-      </c>
-      <c r="L180" s="6" t="inlineStr">
-        <is>
-          <t>maintenance.sudest@record.fr</t>
-        </is>
-      </c>
+          <t>06 66 33 41 58</t>
+        </is>
+      </c>
+      <c r="L180" s="6" t="inlineStr"/>
       <c r="M180" s="6" t="inlineStr"/>
     </row>
-    <row r="181" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A181" s="6" t="inlineStr"/>
-      <c r="B181" s="6" t="inlineStr"/>
-      <c r="C181" s="6" t="inlineStr"/>
-      <c r="D181" s="6" t="inlineStr"/>
-      <c r="E181" s="6" t="inlineStr"/>
-      <c r="F181" s="6" t="inlineStr"/>
-      <c r="G181" s="6" t="inlineStr"/>
-      <c r="H181" s="6" t="inlineStr"/>
-      <c r="I181" s="6" t="inlineStr">
-        <is>
-          <t>SERVICE BACK OFFICE</t>
-        </is>
-      </c>
-      <c r="J181" s="6" t="inlineStr">
-        <is>
-          <t>QUESTIONS FACTURATION, DEVIS, CONTRAT</t>
-        </is>
-      </c>
-      <c r="K181" s="6" t="inlineStr">
-        <is>
-          <t>09 79 98 08 60</t>
-        </is>
-      </c>
-      <c r="L181" s="6" t="inlineStr">
-        <is>
-          <t>maintenance.sudest@record.fr</t>
-        </is>
-      </c>
-      <c r="M181" s="6" t="inlineStr"/>
-    </row>
-    <row r="182" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="181" ht="15.9" customHeight="1">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>PROXI GAZ ABITIBI</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>FSPR0042</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>PROXI GAZ SERVICE</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F181" s="4" t="inlineStr">
+        <is>
+          <t>SUD EST</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>LYON VENDÔME</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>04 78 17 20 13</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr"/>
+      <c r="J181" s="4" t="inlineStr"/>
+      <c r="K181" s="4" t="inlineStr"/>
+      <c r="L181" s="4" t="inlineStr"/>
+      <c r="M181" s="4" t="inlineStr"/>
+    </row>
+    <row r="182" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A182" s="6" t="inlineStr"/>
       <c r="B182" s="6" t="inlineStr"/>
       <c r="C182" s="6" t="inlineStr"/>
@@ -6453,22 +6437,18 @@
       <c r="H182" s="6" t="inlineStr"/>
       <c r="I182" s="6" t="inlineStr">
         <is>
-          <t>PÔLE CONTRATS SUD EST</t>
-        </is>
-      </c>
-      <c r="J182" s="6" t="inlineStr">
-        <is>
-          <t>CONTRATS</t>
-        </is>
-      </c>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="J182" s="6" t="inlineStr"/>
       <c r="K182" s="6" t="inlineStr">
         <is>
-          <t>04 79 52 09 73</t>
+          <t>04 78 17 20 13</t>
         </is>
       </c>
       <c r="L182" s="6" t="inlineStr">
         <is>
-          <t>contrats.maintenance.sudest@record.fr</t>
+          <t>contact@proxigazservice.fr</t>
         </is>
       </c>
       <c r="M182" s="6" t="inlineStr"/>
@@ -6484,54 +6464,70 @@
       <c r="H183" s="6" t="inlineStr"/>
       <c r="I183" s="6" t="inlineStr">
         <is>
-          <t>FLORENT RIVAILLIER</t>
+          <t>NATHALIE</t>
         </is>
       </c>
       <c r="J183" s="6" t="inlineStr">
         <is>
-          <t>INTERLOCUTEUR CONTRAT CLAMECY</t>
+          <t>SAV ABITIBI</t>
         </is>
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>09 79 98 08 60</t>
+          <t>04 78 37 42 72</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr">
         <is>
-          <t>maintenance.sudest@record.fr</t>
+          <t>sav@abitibi.fr</t>
         </is>
       </c>
       <c r="M183" s="6" t="inlineStr"/>
     </row>
-    <row r="184" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A184" s="6" t="inlineStr"/>
-      <c r="B184" s="6" t="inlineStr"/>
-      <c r="C184" s="6" t="inlineStr"/>
-      <c r="D184" s="6" t="inlineStr"/>
-      <c r="E184" s="6" t="inlineStr"/>
-      <c r="F184" s="6" t="inlineStr"/>
-      <c r="G184" s="6" t="inlineStr"/>
-      <c r="H184" s="6" t="inlineStr"/>
-      <c r="I184" s="6" t="inlineStr">
-        <is>
-          <t>ISABELLE VALLET</t>
-        </is>
-      </c>
-      <c r="J184" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANTE MAINTENANCE (BRON)</t>
-        </is>
-      </c>
-      <c r="K184" s="6" t="inlineStr">
-        <is>
-          <t>09 79 98 09 93</t>
-        </is>
-      </c>
-      <c r="L184" s="6" t="inlineStr"/>
-      <c r="M184" s="6" t="inlineStr"/>
-    </row>
-    <row r="185" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="184" ht="15.9" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>RATAUD ASSAINISSEMENT</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>V000112</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>ASSAINISSEMENTS RATAUD</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>CANALISATIONS EU</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>OUEST</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>ST GILLES CROIX DE VIE</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr"/>
+      <c r="I184" s="4" t="inlineStr"/>
+      <c r="J184" s="4" t="inlineStr"/>
+      <c r="K184" s="4" t="inlineStr"/>
+      <c r="L184" s="4" t="inlineStr"/>
+      <c r="M184" s="4" t="inlineStr"/>
+    </row>
+    <row r="185" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A185" s="6" t="inlineStr"/>
       <c r="B185" s="6" t="inlineStr"/>
       <c r="C185" s="6" t="inlineStr"/>
@@ -6542,52 +6538,68 @@
       <c r="H185" s="6" t="inlineStr"/>
       <c r="I185" s="6" t="inlineStr">
         <is>
-          <t>JULIETTE BOURBON</t>
-        </is>
-      </c>
-      <c r="J185" s="6" t="inlineStr">
-        <is>
-          <t>COMMERCIALE SÉDENTAIRE MAINTENANCE SUD-EST</t>
-        </is>
-      </c>
+          <t>JULIE RATAUD</t>
+        </is>
+      </c>
+      <c r="J185" s="6" t="inlineStr"/>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>04 79 52 09 76</t>
+          <t>02 51 55 86 44</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr">
         <is>
-          <t>juliette.bourbon@record.fr</t>
+          <t>sarlrataud@gmail.com</t>
         </is>
       </c>
       <c r="M185" s="6" t="inlineStr"/>
     </row>
-    <row r="186" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A186" s="6" t="inlineStr"/>
-      <c r="B186" s="6" t="inlineStr"/>
-      <c r="C186" s="6" t="inlineStr"/>
-      <c r="D186" s="6" t="inlineStr"/>
-      <c r="E186" s="6" t="inlineStr"/>
-      <c r="F186" s="6" t="inlineStr"/>
-      <c r="G186" s="6" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr"/>
-      <c r="I186" s="6" t="inlineStr">
-        <is>
-          <t>MAINTENANCE OUEST</t>
-        </is>
-      </c>
-      <c r="J186" s="6" t="inlineStr"/>
-      <c r="K186" s="6" t="inlineStr">
+    <row r="186" ht="41.7" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>RECORD</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>FSRE0051</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>RECORD PORTES AUTOMATIQUE</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="inlineStr">
+        <is>
+          <t>PORTE AUTOMATIQUE</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>SUD EST</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>BRIEY, BRON, CHALON2, CLAMECY, JONZAC, ST RÉMY, VALENCIENNES LUÇON</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
         <is>
           <t>08 09 10 01 22</t>
         </is>
       </c>
-      <c r="L186" s="6" t="inlineStr">
-        <is>
-          <t>maintenance.ouest@record.fr</t>
-        </is>
-      </c>
-      <c r="M186" s="6" t="inlineStr"/>
+      <c r="I186" s="4" t="inlineStr"/>
+      <c r="J186" s="4" t="inlineStr"/>
+      <c r="K186" s="4" t="inlineStr"/>
+      <c r="L186" s="4" t="inlineStr"/>
+      <c r="M186" s="4" t="inlineStr"/>
     </row>
     <row r="187" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A187" s="6" t="inlineStr"/>
@@ -6600,14 +6612,22 @@
       <c r="H187" s="6" t="inlineStr"/>
       <c r="I187" s="6" t="inlineStr">
         <is>
-          <t>PÔLE CONTRATS OUEST</t>
-        </is>
-      </c>
-      <c r="J187" s="6" t="inlineStr"/>
-      <c r="K187" s="6" t="inlineStr"/>
+          <t>SERVICE FRONT OFFICE</t>
+        </is>
+      </c>
+      <c r="J187" s="6" t="inlineStr">
+        <is>
+          <t>RENSEIGNEMENT VISITES D'ENTRETIEN ET DÉPANNAGES</t>
+        </is>
+      </c>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>08 09 10 01 22</t>
+        </is>
+      </c>
       <c r="L187" s="6" t="inlineStr">
         <is>
-          <t>contrats.maintenanceouest@record.fr</t>
+          <t>maintenance.sudest@record.fr</t>
         </is>
       </c>
       <c r="M187" s="6" t="inlineStr"/>
@@ -6623,64 +6643,56 @@
       <c r="H188" s="6" t="inlineStr"/>
       <c r="I188" s="6" t="inlineStr">
         <is>
-          <t>AURÉLIE GUIRCHOUN</t>
+          <t>SERVICE BACK OFFICE</t>
         </is>
       </c>
       <c r="J188" s="6" t="inlineStr">
         <is>
-          <t>COMMERCIALE SÉDENTAIRE MAINTENANCE OUEST</t>
+          <t>QUESTIONS FACTURATION, DEVIS, CONTRAT</t>
         </is>
       </c>
       <c r="K188" s="6" t="inlineStr">
         <is>
-          <t>09 79 98 08 74</t>
+          <t>09 79 98 08 60</t>
         </is>
       </c>
       <c r="L188" s="6" t="inlineStr">
         <is>
-          <t>aurelie.guirchoun@record.fr</t>
+          <t>maintenance.sudest@record.fr</t>
         </is>
       </c>
       <c r="M188" s="6" t="inlineStr"/>
     </row>
-    <row r="189" ht="15.9" customHeight="1">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
-        <is>
-          <t>REMI GIRARD</t>
-        </is>
-      </c>
-      <c r="C189" s="5" t="inlineStr">
-        <is>
-          <t>FSRE0151</t>
-        </is>
-      </c>
-      <c r="D189" s="4" t="inlineStr">
-        <is>
-          <t>REMI GIRARD</t>
-        </is>
-      </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>NUISIBLES</t>
-        </is>
-      </c>
-      <c r="F189" s="4" t="inlineStr"/>
-      <c r="G189" s="4" t="inlineStr">
-        <is>
-          <t>CHAMPAGNOLE</t>
-        </is>
-      </c>
-      <c r="H189" s="4" t="inlineStr"/>
-      <c r="I189" s="4" t="inlineStr"/>
-      <c r="J189" s="4" t="inlineStr"/>
-      <c r="K189" s="4" t="inlineStr"/>
-      <c r="L189" s="4" t="inlineStr"/>
-      <c r="M189" s="4" t="inlineStr"/>
+    <row r="189" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A189" s="6" t="inlineStr"/>
+      <c r="B189" s="6" t="inlineStr"/>
+      <c r="C189" s="6" t="inlineStr"/>
+      <c r="D189" s="6" t="inlineStr"/>
+      <c r="E189" s="6" t="inlineStr"/>
+      <c r="F189" s="6" t="inlineStr"/>
+      <c r="G189" s="6" t="inlineStr"/>
+      <c r="H189" s="6" t="inlineStr"/>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>PÔLE CONTRATS SUD EST</t>
+        </is>
+      </c>
+      <c r="J189" s="6" t="inlineStr">
+        <is>
+          <t>CONTRATS</t>
+        </is>
+      </c>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t>04 79 52 09 73</t>
+        </is>
+      </c>
+      <c r="L189" s="6" t="inlineStr">
+        <is>
+          <t>contrats.maintenance.sudest@record.fr</t>
+        </is>
+      </c>
+      <c r="M189" s="6" t="inlineStr"/>
     </row>
     <row r="190" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A190" s="6" t="inlineStr"/>
@@ -6693,68 +6705,52 @@
       <c r="H190" s="6" t="inlineStr"/>
       <c r="I190" s="6" t="inlineStr">
         <is>
-          <t>RÉMI GIRARD</t>
-        </is>
-      </c>
-      <c r="J190" s="6" t="inlineStr"/>
+          <t>FLORENT RIVAILLIER</t>
+        </is>
+      </c>
+      <c r="J190" s="6" t="inlineStr">
+        <is>
+          <t>INTERLOCUTEUR CONTRAT CLAMECY</t>
+        </is>
+      </c>
       <c r="K190" s="6" t="inlineStr">
         <is>
-          <t>06 02 23 02 87</t>
+          <t>09 79 98 08 60</t>
         </is>
       </c>
       <c r="L190" s="6" t="inlineStr">
         <is>
-          <t>rem14117@gmail.com</t>
+          <t>maintenance.sudest@record.fr</t>
         </is>
       </c>
       <c r="M190" s="6" t="inlineStr"/>
     </row>
-    <row r="191" ht="28.8" customHeight="1">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B191" s="5" t="inlineStr">
-        <is>
-          <t>SCARAVELLI &amp; FILS, INZA GROUPE</t>
-        </is>
-      </c>
-      <c r="C191" s="5" t="inlineStr">
-        <is>
-          <t>FSSC0096</t>
-        </is>
-      </c>
-      <c r="D191" s="4" t="inlineStr">
-        <is>
-          <t>SCARAVELLI ET FILS</t>
-        </is>
-      </c>
-      <c r="E191" s="4" t="inlineStr">
-        <is>
-          <t>CHAUFFAGISTE</t>
-        </is>
-      </c>
-      <c r="F191" s="4" t="inlineStr">
-        <is>
-          <t>SUD OUEST</t>
-        </is>
-      </c>
-      <c r="G191" s="4" t="inlineStr">
-        <is>
-          <t>NÉRAC</t>
-        </is>
-      </c>
-      <c r="H191" s="4" t="inlineStr">
-        <is>
-          <t>06 12 13 28 85</t>
-        </is>
-      </c>
-      <c r="I191" s="4" t="inlineStr"/>
-      <c r="J191" s="4" t="inlineStr"/>
-      <c r="K191" s="4" t="inlineStr"/>
-      <c r="L191" s="4" t="inlineStr"/>
-      <c r="M191" s="4" t="inlineStr"/>
+    <row r="191" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A191" s="6" t="inlineStr"/>
+      <c r="B191" s="6" t="inlineStr"/>
+      <c r="C191" s="6" t="inlineStr"/>
+      <c r="D191" s="6" t="inlineStr"/>
+      <c r="E191" s="6" t="inlineStr"/>
+      <c r="F191" s="6" t="inlineStr"/>
+      <c r="G191" s="6" t="inlineStr"/>
+      <c r="H191" s="6" t="inlineStr"/>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>ISABELLE VALLET</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr">
+        <is>
+          <t>ASSISTANTE MAINTENANCE (BRON)</t>
+        </is>
+      </c>
+      <c r="K191" s="6" t="inlineStr">
+        <is>
+          <t>09 79 98 09 93</t>
+        </is>
+      </c>
+      <c r="L191" s="6" t="inlineStr"/>
+      <c r="M191" s="6" t="inlineStr"/>
     </row>
     <row r="192" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A192" s="6" t="inlineStr"/>
@@ -6767,70 +6763,54 @@
       <c r="H192" s="6" t="inlineStr"/>
       <c r="I192" s="6" t="inlineStr">
         <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="J192" s="6" t="inlineStr"/>
+          <t>JULIETTE BOURBON</t>
+        </is>
+      </c>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCIALE SÉDENTAIRE MAINTENANCE SUD-EST</t>
+        </is>
+      </c>
       <c r="K192" s="6" t="inlineStr">
         <is>
-          <t>06 12 13 28 85</t>
+          <t>04 79 52 09 76</t>
         </is>
       </c>
       <c r="L192" s="6" t="inlineStr">
         <is>
-          <t>scaravelli.chauffagiste@orange.fr</t>
+          <t>juliette.bourbon@record.fr</t>
         </is>
       </c>
       <c r="M192" s="6" t="inlineStr"/>
     </row>
-    <row r="193" ht="28.8" customHeight="1">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B193" s="5" t="inlineStr">
-        <is>
-          <t>SOCIETE NOUVELLE H. CONRAUX</t>
-        </is>
-      </c>
-      <c r="C193" s="5" t="inlineStr">
-        <is>
-          <t>FSCO0034</t>
-        </is>
-      </c>
-      <c r="D193" s="4" t="inlineStr">
-        <is>
-          <t>CONRAUX H SAS</t>
-        </is>
-      </c>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>CHAUFFAGISTE</t>
-        </is>
-      </c>
-      <c r="F193" s="4" t="inlineStr">
-        <is>
-          <t>EST</t>
-        </is>
-      </c>
-      <c r="G193" s="4" t="inlineStr">
-        <is>
-          <t>REIMS PARIS</t>
-        </is>
-      </c>
-      <c r="H193" s="4" t="inlineStr">
-        <is>
-          <t>03 26 65 40 40</t>
-        </is>
-      </c>
-      <c r="I193" s="4" t="inlineStr"/>
-      <c r="J193" s="4" t="inlineStr"/>
-      <c r="K193" s="4" t="inlineStr"/>
-      <c r="L193" s="4" t="inlineStr"/>
-      <c r="M193" s="4" t="inlineStr"/>
-    </row>
-    <row r="194" outlineLevel="1" ht="41.7" customHeight="1">
+    <row r="193" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A193" s="6" t="inlineStr"/>
+      <c r="B193" s="6" t="inlineStr"/>
+      <c r="C193" s="6" t="inlineStr"/>
+      <c r="D193" s="6" t="inlineStr"/>
+      <c r="E193" s="6" t="inlineStr"/>
+      <c r="F193" s="6" t="inlineStr"/>
+      <c r="G193" s="6" t="inlineStr"/>
+      <c r="H193" s="6" t="inlineStr"/>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>MAINTENANCE OUEST</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr"/>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>08 09 10 01 22</t>
+        </is>
+      </c>
+      <c r="L193" s="6" t="inlineStr">
+        <is>
+          <t>maintenance.ouest@record.fr</t>
+        </is>
+      </c>
+      <c r="M193" s="6" t="inlineStr"/>
+    </row>
+    <row r="194" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A194" s="6" t="inlineStr"/>
       <c r="B194" s="6" t="inlineStr"/>
       <c r="C194" s="6" t="inlineStr"/>
@@ -6841,27 +6821,19 @@
       <c r="H194" s="6" t="inlineStr"/>
       <c r="I194" s="6" t="inlineStr">
         <is>
-          <t>SAV</t>
+          <t>PÔLE CONTRATS OUEST</t>
         </is>
       </c>
       <c r="J194" s="6" t="inlineStr"/>
-      <c r="K194" s="6" t="inlineStr">
-        <is>
-          <t>03 26 65 40 40</t>
-        </is>
-      </c>
+      <c r="K194" s="6" t="inlineStr"/>
       <c r="L194" s="6" t="inlineStr">
         <is>
-          <t>sav.anquetil@anquetil.fr</t>
-        </is>
-      </c>
-      <c r="M194" s="6" t="inlineStr">
-        <is>
-          <t>STÉ NOUVELLE H. CONRAUX TRAVAILLE EN PARTENARIAT AVEC ANQUETIL, ÉGALEMENT FILIALE SPIE, POUR LA MAINTENANCE ; CHOIX 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" outlineLevel="1" ht="15.9" customHeight="1">
+          <t>contrats.maintenanceouest@record.fr</t>
+        </is>
+      </c>
+      <c r="M194" s="6" t="inlineStr"/>
+    </row>
+    <row r="195" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A195" s="6" t="inlineStr"/>
       <c r="B195" s="6" t="inlineStr"/>
       <c r="C195" s="6" t="inlineStr"/>
@@ -6872,48 +6844,64 @@
       <c r="H195" s="6" t="inlineStr"/>
       <c r="I195" s="6" t="inlineStr">
         <is>
-          <t>JORICK MAILLARD</t>
+          <t>AURÉLIE GUIRCHOUN</t>
         </is>
       </c>
       <c r="J195" s="6" t="inlineStr">
         <is>
-          <t>TECHNICIEN D'ETUDE</t>
+          <t>COMMERCIALE SÉDENTAIRE MAINTENANCE OUEST</t>
         </is>
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>06 15 62 53 79</t>
+          <t>09 79 98 08 74</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr">
         <is>
-          <t>jorick.maillard@spie.com</t>
+          <t>aurelie.guirchoun@record.fr</t>
         </is>
       </c>
       <c r="M195" s="6" t="inlineStr"/>
     </row>
-    <row r="196" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A196" s="6" t="inlineStr"/>
-      <c r="B196" s="6" t="inlineStr"/>
-      <c r="C196" s="6" t="inlineStr"/>
-      <c r="D196" s="6" t="inlineStr"/>
-      <c r="E196" s="6" t="inlineStr"/>
-      <c r="F196" s="6" t="inlineStr"/>
-      <c r="G196" s="6" t="inlineStr"/>
-      <c r="H196" s="6" t="inlineStr"/>
-      <c r="I196" s="6" t="inlineStr">
-        <is>
-          <t>KEVIN MOREAUX</t>
-        </is>
-      </c>
-      <c r="J196" s="6" t="inlineStr"/>
-      <c r="K196" s="6" t="inlineStr"/>
-      <c r="L196" s="6" t="inlineStr">
-        <is>
-          <t>kevin.moreaux@spie.com</t>
-        </is>
-      </c>
-      <c r="M196" s="6" t="inlineStr"/>
+    <row r="196" ht="15.9" customHeight="1">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>REMI GIRARD</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>FSRE0151</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>REMI GIRARD</t>
+        </is>
+      </c>
+      <c r="E196" s="4" t="inlineStr">
+        <is>
+          <t>NUISIBLES</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr"/>
+      <c r="G196" s="4" t="inlineStr">
+        <is>
+          <t>CHAMPAGNOLE</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr"/>
+      <c r="I196" s="4" t="inlineStr"/>
+      <c r="J196" s="4" t="inlineStr"/>
+      <c r="K196" s="4" t="inlineStr"/>
+      <c r="L196" s="4" t="inlineStr"/>
+      <c r="M196" s="4" t="inlineStr"/>
     </row>
     <row r="197" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A197" s="6" t="inlineStr"/>
@@ -6926,159 +6914,179 @@
       <c r="H197" s="6" t="inlineStr"/>
       <c r="I197" s="6" t="inlineStr">
         <is>
-          <t>DJAMILA BENSEGHIR</t>
+          <t>RÉMI GIRARD</t>
         </is>
       </c>
       <c r="J197" s="6" t="inlineStr"/>
-      <c r="K197" s="6" t="inlineStr"/>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t>06 02 23 02 87</t>
+        </is>
+      </c>
       <c r="L197" s="6" t="inlineStr">
         <is>
-          <t>djamila.benseghir@spie.com</t>
+          <t>rem14117@gmail.com</t>
         </is>
       </c>
       <c r="M197" s="6" t="inlineStr"/>
     </row>
-    <row r="198" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A198" s="6" t="inlineStr"/>
-      <c r="B198" s="6" t="inlineStr"/>
-      <c r="C198" s="6" t="inlineStr"/>
-      <c r="D198" s="6" t="inlineStr"/>
-      <c r="E198" s="6" t="inlineStr"/>
-      <c r="F198" s="6" t="inlineStr"/>
-      <c r="G198" s="6" t="inlineStr"/>
-      <c r="H198" s="6" t="inlineStr"/>
-      <c r="I198" s="6" t="inlineStr">
-        <is>
-          <t>ISABELLE BAILLARD</t>
-        </is>
-      </c>
-      <c r="J198" s="6" t="inlineStr">
-        <is>
-          <t>COMPTABLE</t>
-        </is>
-      </c>
-      <c r="K198" s="6" t="inlineStr">
-        <is>
-          <t>03 80 60 61 19</t>
-        </is>
-      </c>
-      <c r="L198" s="6" t="inlineStr">
-        <is>
-          <t>isabelle.baillard@spie.com</t>
-        </is>
-      </c>
-      <c r="M198" s="6" t="inlineStr"/>
-    </row>
-    <row r="199" ht="15.9" customHeight="1">
-      <c r="A199" s="4" t="inlineStr">
+    <row r="198" ht="28.8" customHeight="1">
+      <c r="A198" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
         </is>
       </c>
-      <c r="B199" s="5" t="inlineStr">
-        <is>
-          <t>SOFTICA</t>
-        </is>
-      </c>
-      <c r="C199" s="5" t="inlineStr">
-        <is>
-          <t>FSSO0157</t>
-        </is>
-      </c>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>SOFTICA</t>
-        </is>
-      </c>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>PORTE AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="F199" s="4" t="inlineStr">
-        <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G199" s="4" t="inlineStr">
-        <is>
-          <t>DRUMETTAZ, GRÉSY-SUR-AIX</t>
-        </is>
-      </c>
-      <c r="H199" s="4" t="inlineStr">
-        <is>
-          <t>04 79 63 14 89</t>
-        </is>
-      </c>
-      <c r="I199" s="4" t="inlineStr"/>
-      <c r="J199" s="4" t="inlineStr"/>
-      <c r="K199" s="4" t="inlineStr"/>
-      <c r="L199" s="4" t="inlineStr"/>
-      <c r="M199" s="4" t="inlineStr"/>
-    </row>
-    <row r="200" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A200" s="6" t="inlineStr"/>
-      <c r="B200" s="6" t="inlineStr"/>
-      <c r="C200" s="6" t="inlineStr"/>
-      <c r="D200" s="6" t="inlineStr"/>
-      <c r="E200" s="6" t="inlineStr"/>
-      <c r="F200" s="6" t="inlineStr"/>
-      <c r="G200" s="6" t="inlineStr"/>
-      <c r="H200" s="6" t="inlineStr"/>
-      <c r="I200" s="6" t="inlineStr">
-        <is>
-          <t>SAV, DÉPANNAGES</t>
-        </is>
-      </c>
-      <c r="J200" s="6" t="inlineStr"/>
-      <c r="K200" s="6" t="inlineStr">
-        <is>
-          <t>04 79 63 14 89</t>
-        </is>
-      </c>
-      <c r="L200" s="6" t="inlineStr">
-        <is>
-          <t>maintenance@softica.fr</t>
-        </is>
-      </c>
-      <c r="M200" s="6" t="inlineStr">
-        <is>
-          <t>AGENCE CHAMBÉRY - ALPES</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A201" s="6" t="inlineStr"/>
-      <c r="B201" s="6" t="inlineStr"/>
-      <c r="C201" s="6" t="inlineStr"/>
-      <c r="D201" s="6" t="inlineStr"/>
-      <c r="E201" s="6" t="inlineStr"/>
-      <c r="F201" s="6" t="inlineStr"/>
-      <c r="G201" s="6" t="inlineStr"/>
-      <c r="H201" s="6" t="inlineStr"/>
-      <c r="I201" s="6" t="inlineStr">
-        <is>
-          <t>DEMANDES D'INTERVENTION</t>
-        </is>
-      </c>
-      <c r="J201" s="6" t="inlineStr">
-        <is>
-          <t>À UTILISER POUR TOUTES LES DEMANDES MAINT, PRÉV</t>
-        </is>
-      </c>
-      <c r="K201" s="6" t="inlineStr">
-        <is>
-          <t>04 79 34 54 17</t>
-        </is>
-      </c>
-      <c r="L201" s="6" t="inlineStr">
-        <is>
-          <t>intervention@softica.fr</t>
-        </is>
-      </c>
-      <c r="M201" s="6" t="inlineStr"/>
-    </row>
-    <row r="202" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>SCARAVELLI &amp; FILS, INZA GROUPE</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>FSSC0096</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>SCARAVELLI ET FILS</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>SUD OUEST</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>NÉRAC</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>06 12 13 28 85</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr"/>
+      <c r="J198" s="4" t="inlineStr"/>
+      <c r="K198" s="4" t="inlineStr"/>
+      <c r="L198" s="4" t="inlineStr"/>
+      <c r="M198" s="4" t="inlineStr"/>
+    </row>
+    <row r="199" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A199" s="6" t="inlineStr"/>
+      <c r="B199" s="6" t="inlineStr"/>
+      <c r="C199" s="6" t="inlineStr"/>
+      <c r="D199" s="6" t="inlineStr"/>
+      <c r="E199" s="6" t="inlineStr"/>
+      <c r="F199" s="6" t="inlineStr"/>
+      <c r="G199" s="6" t="inlineStr"/>
+      <c r="H199" s="6" t="inlineStr"/>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="J199" s="6" t="inlineStr"/>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>06 12 13 28 85</t>
+        </is>
+      </c>
+      <c r="L199" s="6" t="inlineStr">
+        <is>
+          <t>scaravelli.chauffagiste@orange.fr</t>
+        </is>
+      </c>
+      <c r="M199" s="6" t="inlineStr"/>
+    </row>
+    <row r="200" ht="54.6" customHeight="1">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>SIÈGE</t>
+        </is>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>SNP</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr"/>
+      <c r="D200" s="4" t="inlineStr"/>
+      <c r="E200" s="4" t="inlineStr">
+        <is>
+          <t>MÉNAGE</t>
+        </is>
+      </c>
+      <c r="F200" s="4" t="inlineStr"/>
+      <c r="G200" s="4" t="inlineStr">
+        <is>
+          <t>SIÈGE</t>
+        </is>
+      </c>
+      <c r="H200" s="4" t="inlineStr"/>
+      <c r="I200" s="4" t="inlineStr"/>
+      <c r="J200" s="4" t="inlineStr"/>
+      <c r="K200" s="4" t="inlineStr"/>
+      <c r="L200" s="4" t="inlineStr"/>
+      <c r="M200" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE DU SIÈGE ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="28.8" customHeight="1">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>SOCIETE NOUVELLE H. CONRAUX</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>FSCO0034</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>CONRAUX H SAS</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F201" s="4" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr">
+        <is>
+          <t>REIMS PARIS</t>
+        </is>
+      </c>
+      <c r="H201" s="4" t="inlineStr">
+        <is>
+          <t>03 26 65 40 40</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="inlineStr"/>
+      <c r="J201" s="4" t="inlineStr"/>
+      <c r="K201" s="4" t="inlineStr"/>
+      <c r="L201" s="4" t="inlineStr"/>
+      <c r="M201" s="4" t="inlineStr"/>
+    </row>
+    <row r="202" outlineLevel="1" ht="41.7" customHeight="1">
       <c r="A202" s="6" t="inlineStr"/>
       <c r="B202" s="6" t="inlineStr"/>
       <c r="C202" s="6" t="inlineStr"/>
@@ -7089,78 +7097,58 @@
       <c r="H202" s="6" t="inlineStr"/>
       <c r="I202" s="6" t="inlineStr">
         <is>
-          <t>LAËTITIA MICHELLIER</t>
-        </is>
-      </c>
-      <c r="J202" s="6" t="inlineStr">
-        <is>
-          <t>COMMERCIALE SAV CONTRAT</t>
-        </is>
-      </c>
+          <t>SAV</t>
+        </is>
+      </c>
+      <c r="J202" s="6" t="inlineStr"/>
       <c r="K202" s="6" t="inlineStr">
         <is>
-          <t>04 79 63 78 35</t>
+          <t>03 26 65 40 40</t>
         </is>
       </c>
       <c r="L202" s="6" t="inlineStr">
         <is>
-          <t>lmichellier@softica.fr</t>
+          <t>sav.anquetil@anquetil.fr</t>
         </is>
       </c>
       <c r="M202" s="6" t="inlineStr">
         <is>
-          <t>SAVOIE HEXAPOLE, 55 IMPASSE DES IRIS 73420 MÉRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="203" ht="80.40000000000001" customHeight="1">
-      <c r="A203" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B203" s="5" t="inlineStr">
-        <is>
-          <t>SOPREMA (SOPRASSISTANCE)</t>
-        </is>
-      </c>
-      <c r="C203" s="5" t="inlineStr">
-        <is>
-          <t>FSSO0114</t>
-        </is>
-      </c>
-      <c r="D203" s="4" t="inlineStr">
-        <is>
-          <t>SOPRASSISTANCE</t>
-        </is>
-      </c>
-      <c r="E203" s="4" t="inlineStr">
-        <is>
-          <t>TOITURES, CHENEAUX</t>
-        </is>
-      </c>
-      <c r="F203" s="4" t="inlineStr">
-        <is>
-          <t>FRANCE</t>
-        </is>
-      </c>
-      <c r="G203" s="4" t="inlineStr">
-        <is>
-          <t>ST GERMAIN EN LAYE ; LISIEUX ; BREST PASTEUR ; ST GILLES CROIX DE VIE ET ; LA ROCHE SUR YON 2 ; VENDÉE ; ORANGE ; DOUAI ; LA MADELEINE</t>
-        </is>
-      </c>
-      <c r="H203" s="4" t="inlineStr">
-        <is>
-          <t>02 98 41 03 40</t>
-        </is>
-      </c>
-      <c r="I203" s="4" t="inlineStr"/>
-      <c r="J203" s="4" t="inlineStr"/>
-      <c r="K203" s="4" t="inlineStr"/>
-      <c r="L203" s="4" t="inlineStr"/>
-      <c r="M203" s="4" t="inlineStr"/>
-    </row>
-    <row r="204" outlineLevel="1" ht="28.8" customHeight="1">
+          <t>STÉ NOUVELLE H. CONRAUX TRAVAILLE EN PARTENARIAT AVEC ANQUETIL, ÉGALEMENT FILIALE SPIE, POUR LA MAINTENANCE ; CHOIX 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A203" s="6" t="inlineStr"/>
+      <c r="B203" s="6" t="inlineStr"/>
+      <c r="C203" s="6" t="inlineStr"/>
+      <c r="D203" s="6" t="inlineStr"/>
+      <c r="E203" s="6" t="inlineStr"/>
+      <c r="F203" s="6" t="inlineStr"/>
+      <c r="G203" s="6" t="inlineStr"/>
+      <c r="H203" s="6" t="inlineStr"/>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>JORICK MAILLARD</t>
+        </is>
+      </c>
+      <c r="J203" s="6" t="inlineStr">
+        <is>
+          <t>TECHNICIEN D'ETUDE</t>
+        </is>
+      </c>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>06 15 62 53 79</t>
+        </is>
+      </c>
+      <c r="L203" s="6" t="inlineStr">
+        <is>
+          <t>jorick.maillard@spie.com</t>
+        </is>
+      </c>
+      <c r="M203" s="6" t="inlineStr"/>
+    </row>
+    <row r="204" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A204" s="6" t="inlineStr"/>
       <c r="B204" s="6" t="inlineStr"/>
       <c r="C204" s="6" t="inlineStr"/>
@@ -7171,19 +7159,19 @@
       <c r="H204" s="6" t="inlineStr"/>
       <c r="I204" s="6" t="inlineStr">
         <is>
-          <t>ADRESSE GÉNÉRIQUE</t>
+          <t>KEVIN MOREAUX</t>
         </is>
       </c>
       <c r="J204" s="6" t="inlineStr"/>
       <c r="K204" s="6" t="inlineStr"/>
       <c r="L204" s="6" t="inlineStr">
         <is>
-          <t>contact@soprema-entreprises.fr</t>
+          <t>kevin.moreaux@spie.com</t>
         </is>
       </c>
       <c r="M204" s="6" t="inlineStr"/>
     </row>
-    <row r="205" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="205" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A205" s="6" t="inlineStr"/>
       <c r="B205" s="6" t="inlineStr"/>
       <c r="C205" s="6" t="inlineStr"/>
@@ -7194,25 +7182,17 @@
       <c r="H205" s="6" t="inlineStr"/>
       <c r="I205" s="6" t="inlineStr">
         <is>
-          <t>ANTHONY GAUDOIN</t>
+          <t>DJAMILA BENSEGHIR</t>
         </is>
       </c>
       <c r="J205" s="6" t="inlineStr"/>
-      <c r="K205" s="6" t="inlineStr">
-        <is>
-          <t>01 55 46 10 80 / 06 74 25 92 39</t>
-        </is>
-      </c>
+      <c r="K205" s="6" t="inlineStr"/>
       <c r="L205" s="6" t="inlineStr">
         <is>
-          <t>agaudoin@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M205" s="6" t="inlineStr">
-        <is>
-          <t>ZAC DES LOUVRESSES, 16 AV. DES LOUVRESSES 92230 GENNEVILLIERS</t>
-        </is>
-      </c>
+          <t>djamila.benseghir@spie.com</t>
+        </is>
+      </c>
+      <c r="M205" s="6" t="inlineStr"/>
     </row>
     <row r="206" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A206" s="6" t="inlineStr"/>
@@ -7225,52 +7205,72 @@
       <c r="H206" s="6" t="inlineStr"/>
       <c r="I206" s="6" t="inlineStr">
         <is>
-          <t>FLORENCE ESCUER</t>
+          <t>ISABELLE BAILLARD</t>
         </is>
       </c>
       <c r="J206" s="6" t="inlineStr">
         <is>
-          <t>ASSISTANTE</t>
+          <t>COMPTABLE</t>
         </is>
       </c>
       <c r="K206" s="6" t="inlineStr">
         <is>
-          <t>01 55 46 00 82</t>
+          <t>03 80 60 61 19</t>
         </is>
       </c>
       <c r="L206" s="6" t="inlineStr">
         <is>
-          <t>fescuer@soprema.fr</t>
+          <t>isabelle.baillard@spie.com</t>
         </is>
       </c>
       <c r="M206" s="6" t="inlineStr"/>
     </row>
-    <row r="207" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A207" s="6" t="inlineStr"/>
-      <c r="B207" s="6" t="inlineStr"/>
-      <c r="C207" s="6" t="inlineStr"/>
-      <c r="D207" s="6" t="inlineStr"/>
-      <c r="E207" s="6" t="inlineStr"/>
-      <c r="F207" s="6" t="inlineStr"/>
-      <c r="G207" s="6" t="inlineStr">
-        <is>
-          <t>LISIEUX</t>
-        </is>
-      </c>
-      <c r="H207" s="6" t="inlineStr"/>
-      <c r="I207" s="6" t="inlineStr">
-        <is>
-          <t>AGENCE VAL-DE-REUIL</t>
-        </is>
-      </c>
-      <c r="J207" s="6" t="inlineStr"/>
-      <c r="K207" s="6" t="inlineStr">
-        <is>
-          <t>02 32 40 22 98</t>
-        </is>
-      </c>
-      <c r="L207" s="6" t="inlineStr"/>
-      <c r="M207" s="6" t="inlineStr"/>
+    <row r="207" ht="15.9" customHeight="1">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>SOFTICA</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>FSSO0157</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>SOFTICA</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>PORTE AUTOMATIQUE</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>SUD EST</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>DRUMETTAZ, GRÉSY-SUR-AIX</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>04 79 63 14 89</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr"/>
+      <c r="J207" s="4" t="inlineStr"/>
+      <c r="K207" s="4" t="inlineStr"/>
+      <c r="L207" s="4" t="inlineStr"/>
+      <c r="M207" s="4" t="inlineStr"/>
     </row>
     <row r="208" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A208" s="6" t="inlineStr"/>
@@ -7279,25 +7279,29 @@
       <c r="D208" s="6" t="inlineStr"/>
       <c r="E208" s="6" t="inlineStr"/>
       <c r="F208" s="6" t="inlineStr"/>
-      <c r="G208" s="6" t="inlineStr">
-        <is>
-          <t>BREST PASTEUR</t>
-        </is>
-      </c>
+      <c r="G208" s="6" t="inlineStr"/>
       <c r="H208" s="6" t="inlineStr"/>
       <c r="I208" s="6" t="inlineStr">
         <is>
-          <t>STANDARD</t>
+          <t>SAV, DÉPANNAGES</t>
         </is>
       </c>
       <c r="J208" s="6" t="inlineStr"/>
       <c r="K208" s="6" t="inlineStr">
         <is>
-          <t>02 98 41 03 40</t>
-        </is>
-      </c>
-      <c r="L208" s="6" t="inlineStr"/>
-      <c r="M208" s="6" t="inlineStr"/>
+          <t>04 79 63 14 89</t>
+        </is>
+      </c>
+      <c r="L208" s="6" t="inlineStr">
+        <is>
+          <t>maintenance@softica.fr</t>
+        </is>
+      </c>
+      <c r="M208" s="6" t="inlineStr">
+        <is>
+          <t>AGENCE CHAMBÉRY - ALPES</t>
+        </is>
+      </c>
     </row>
     <row r="209" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A209" s="6" t="inlineStr"/>
@@ -7306,95 +7310,111 @@
       <c r="D209" s="6" t="inlineStr"/>
       <c r="E209" s="6" t="inlineStr"/>
       <c r="F209" s="6" t="inlineStr"/>
-      <c r="G209" s="6" t="inlineStr">
-        <is>
-          <t>BREST PASTEUR</t>
-        </is>
-      </c>
+      <c r="G209" s="6" t="inlineStr"/>
       <c r="H209" s="6" t="inlineStr"/>
       <c r="I209" s="6" t="inlineStr">
         <is>
-          <t>LUCILE PRIGENT</t>
+          <t>DEMANDES D'INTERVENTION</t>
         </is>
       </c>
       <c r="J209" s="6" t="inlineStr">
         <is>
-          <t>ASSISTANTE &amp; GESTIONNAIRE COMMUNICATION</t>
+          <t>À UTILISER POUR TOUTES LES DEMANDES MAINT, PRÉV</t>
         </is>
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>02 98 41 17 24</t>
+          <t>04 79 34 54 17</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr">
         <is>
-          <t>lprigent@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M209" s="6" t="inlineStr">
-        <is>
-          <t>PLOUDANIEL (29260)</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" outlineLevel="1" ht="15.9" customHeight="1">
+          <t>intervention@softica.fr</t>
+        </is>
+      </c>
+      <c r="M209" s="6" t="inlineStr"/>
+    </row>
+    <row r="210" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A210" s="6" t="inlineStr"/>
       <c r="B210" s="6" t="inlineStr"/>
       <c r="C210" s="6" t="inlineStr"/>
       <c r="D210" s="6" t="inlineStr"/>
       <c r="E210" s="6" t="inlineStr"/>
       <c r="F210" s="6" t="inlineStr"/>
-      <c r="G210" s="6" t="inlineStr">
-        <is>
-          <t>BREST PASTEUR</t>
-        </is>
-      </c>
+      <c r="G210" s="6" t="inlineStr"/>
       <c r="H210" s="6" t="inlineStr"/>
       <c r="I210" s="6" t="inlineStr">
         <is>
-          <t>SOLÈNE CORRE</t>
+          <t>LAËTITIA MICHELLIER</t>
         </is>
       </c>
       <c r="J210" s="6" t="inlineStr">
         <is>
-          <t>CONDUCTEUR DE TRAVAUX</t>
-        </is>
-      </c>
-      <c r="K210" s="6" t="inlineStr"/>
+          <t>COMMERCIALE SAV CONTRAT</t>
+        </is>
+      </c>
+      <c r="K210" s="6" t="inlineStr">
+        <is>
+          <t>04 79 63 78 35</t>
+        </is>
+      </c>
       <c r="L210" s="6" t="inlineStr">
         <is>
-          <t>scorre@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M210" s="6" t="inlineStr"/>
-    </row>
-    <row r="211" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A211" s="6" t="inlineStr"/>
-      <c r="B211" s="6" t="inlineStr"/>
-      <c r="C211" s="6" t="inlineStr"/>
-      <c r="D211" s="6" t="inlineStr"/>
-      <c r="E211" s="6" t="inlineStr"/>
-      <c r="F211" s="6" t="inlineStr"/>
-      <c r="G211" s="6" t="inlineStr">
-        <is>
-          <t>BREST PASTEUR</t>
-        </is>
-      </c>
-      <c r="H211" s="6" t="inlineStr"/>
-      <c r="I211" s="6" t="inlineStr">
-        <is>
-          <t>COURRIEL GÉNÉRIQUE AGENCE BREST</t>
-        </is>
-      </c>
-      <c r="J211" s="6" t="inlineStr"/>
-      <c r="K211" s="6" t="inlineStr"/>
-      <c r="L211" s="6" t="inlineStr">
-        <is>
-          <t>soprassistance-brest@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M211" s="6" t="inlineStr"/>
+          <t>lmichellier@softica.fr</t>
+        </is>
+      </c>
+      <c r="M210" s="6" t="inlineStr">
+        <is>
+          <t>SAVOIE HEXAPOLE, 55 IMPASSE DES IRIS 73420 MÉRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="80.40000000000001" customHeight="1">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>SOPREMA (SOPRASSISTANCE)</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>FSSO0114</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>SOPRASSISTANCE</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>TOITURES, CHENEAUX</t>
+        </is>
+      </c>
+      <c r="F211" s="4" t="inlineStr">
+        <is>
+          <t>FRANCE</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr">
+        <is>
+          <t>ST GERMAIN EN LAYE ; LISIEUX ; BREST PASTEUR ; ST GILLES CROIX DE VIE ET ; LA ROCHE SUR YON 2 ; VENDÉE ; ORANGE ; DOUAI ; LA MADELEINE</t>
+        </is>
+      </c>
+      <c r="H211" s="4" t="inlineStr">
+        <is>
+          <t>02 98 41 03 40</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="inlineStr"/>
+      <c r="J211" s="4" t="inlineStr"/>
+      <c r="K211" s="4" t="inlineStr"/>
+      <c r="L211" s="4" t="inlineStr"/>
+      <c r="M211" s="4" t="inlineStr"/>
     </row>
     <row r="212" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A212" s="6" t="inlineStr"/>
@@ -7403,26 +7423,18 @@
       <c r="D212" s="6" t="inlineStr"/>
       <c r="E212" s="6" t="inlineStr"/>
       <c r="F212" s="6" t="inlineStr"/>
-      <c r="G212" s="6" t="inlineStr">
-        <is>
-          <t>ST GILLES CROIX DE VIE ET</t>
-        </is>
-      </c>
+      <c r="G212" s="6" t="inlineStr"/>
       <c r="H212" s="6" t="inlineStr"/>
       <c r="I212" s="6" t="inlineStr">
         <is>
-          <t>ASSISTANTE D'AGENCE VENDÉE</t>
+          <t>ADRESSE GÉNÉRIQUE</t>
         </is>
       </c>
       <c r="J212" s="6" t="inlineStr"/>
-      <c r="K212" s="6" t="inlineStr">
-        <is>
-          <t>02 28 97 72 31</t>
-        </is>
-      </c>
+      <c r="K212" s="6" t="inlineStr"/>
       <c r="L212" s="6" t="inlineStr">
         <is>
-          <t>soprassistance-vendee@soprema.fr</t>
+          <t>contact@soprema-entreprises.fr</t>
         </is>
       </c>
       <c r="M212" s="6" t="inlineStr"/>
@@ -7434,74 +7446,62 @@
       <c r="D213" s="6" t="inlineStr"/>
       <c r="E213" s="6" t="inlineStr"/>
       <c r="F213" s="6" t="inlineStr"/>
-      <c r="G213" s="6" t="inlineStr">
-        <is>
-          <t>VENDÉE</t>
-        </is>
-      </c>
+      <c r="G213" s="6" t="inlineStr"/>
       <c r="H213" s="6" t="inlineStr"/>
       <c r="I213" s="6" t="inlineStr">
         <is>
-          <t>DAVID VINCENT</t>
-        </is>
-      </c>
-      <c r="J213" s="6" t="inlineStr">
-        <is>
-          <t>RESPONSABLE D'AGENCE VENDÉE</t>
-        </is>
-      </c>
+          <t>ANTHONY GAUDOIN</t>
+        </is>
+      </c>
+      <c r="J213" s="6" t="inlineStr"/>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>02 28 97 72 31 / 06 47 85 97 52</t>
+          <t>01 55 46 10 80 / 06 74 25 92 39</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr">
         <is>
-          <t>davincent@soprema.fr</t>
+          <t>agaudoin@soprema.fr</t>
         </is>
       </c>
       <c r="M213" s="6" t="inlineStr">
         <is>
-          <t>9 RUE AMPÈRE, BP3, 85170 LE POIRÉ-SUR-VIE</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" outlineLevel="1" ht="28.8" customHeight="1">
+          <t>ZAC DES LOUVRESSES, 16 AV. DES LOUVRESSES 92230 GENNEVILLIERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A214" s="6" t="inlineStr"/>
       <c r="B214" s="6" t="inlineStr"/>
       <c r="C214" s="6" t="inlineStr"/>
       <c r="D214" s="6" t="inlineStr"/>
       <c r="E214" s="6" t="inlineStr"/>
       <c r="F214" s="6" t="inlineStr"/>
-      <c r="G214" s="6" t="inlineStr">
-        <is>
-          <t>ORANGE</t>
-        </is>
-      </c>
+      <c r="G214" s="6" t="inlineStr"/>
       <c r="H214" s="6" t="inlineStr"/>
       <c r="I214" s="6" t="inlineStr">
         <is>
-          <t>OLIVIER BECKER</t>
-        </is>
-      </c>
-      <c r="J214" s="6" t="inlineStr"/>
+          <t>FLORENCE ESCUER</t>
+        </is>
+      </c>
+      <c r="J214" s="6" t="inlineStr">
+        <is>
+          <t>ASSISTANTE</t>
+        </is>
+      </c>
       <c r="K214" s="6" t="inlineStr">
         <is>
-          <t>04 90 14 89 27 / 06 87 56 73 32</t>
+          <t>01 55 46 00 82</t>
         </is>
       </c>
       <c r="L214" s="6" t="inlineStr">
         <is>
-          <t>obecker@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M214" s="6" t="inlineStr">
-        <is>
-          <t>125, RUE DES QUATRE GENDARMES D'OUVÉA 84000 AVIGNON</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" outlineLevel="1" ht="28.8" customHeight="1">
+          <t>fescuer@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M214" s="6" t="inlineStr"/>
+    </row>
+    <row r="215" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A215" s="6" t="inlineStr"/>
       <c r="B215" s="6" t="inlineStr"/>
       <c r="C215" s="6" t="inlineStr"/>
@@ -7510,33 +7510,25 @@
       <c r="F215" s="6" t="inlineStr"/>
       <c r="G215" s="6" t="inlineStr">
         <is>
-          <t>DOUAI</t>
+          <t>LISIEUX</t>
         </is>
       </c>
       <c r="H215" s="6" t="inlineStr"/>
       <c r="I215" s="6" t="inlineStr">
         <is>
-          <t>YOHAN FRERE</t>
+          <t>AGENCE VAL-DE-REUIL</t>
         </is>
       </c>
       <c r="J215" s="6" t="inlineStr"/>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>03 20 86 27 69 / 06 08 14 70 57</t>
-        </is>
-      </c>
-      <c r="L215" s="6" t="inlineStr">
-        <is>
-          <t>yfrere@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M215" s="6" t="inlineStr">
-        <is>
-          <t>208 RUE DES BOULEAUX 59860 BRUAY-SUR-L'ESCAUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" outlineLevel="1" ht="28.8" customHeight="1">
+          <t>02 32 40 22 98</t>
+        </is>
+      </c>
+      <c r="L215" s="6" t="inlineStr"/>
+      <c r="M215" s="6" t="inlineStr"/>
+    </row>
+    <row r="216" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A216" s="6" t="inlineStr"/>
       <c r="B216" s="6" t="inlineStr"/>
       <c r="C216" s="6" t="inlineStr"/>
@@ -7545,37 +7537,25 @@
       <c r="F216" s="6" t="inlineStr"/>
       <c r="G216" s="6" t="inlineStr">
         <is>
-          <t>LA MADELEINE</t>
+          <t>BREST PASTEUR</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr"/>
       <c r="I216" s="6" t="inlineStr">
         <is>
-          <t>ANTOINE FRANÇOIS</t>
-        </is>
-      </c>
-      <c r="J216" s="6" t="inlineStr">
-        <is>
-          <t>CONDUCTEUR DE TRAVAUX</t>
-        </is>
-      </c>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="J216" s="6" t="inlineStr"/>
       <c r="K216" s="6" t="inlineStr">
         <is>
-          <t>03 28 82 99 34 / 06 07 63 80 74</t>
-        </is>
-      </c>
-      <c r="L216" s="6" t="inlineStr">
-        <is>
-          <t>afrancois@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M216" s="6" t="inlineStr">
-        <is>
-          <t>851 RUE DU CHEMIN VERT FRETIN CRT 3 - BP104 59810 LESQUIN CEDEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" outlineLevel="1" ht="15.9" customHeight="1">
+          <t>02 98 41 03 40</t>
+        </is>
+      </c>
+      <c r="L216" s="6" t="inlineStr"/>
+      <c r="M216" s="6" t="inlineStr"/>
+    </row>
+    <row r="217" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A217" s="6" t="inlineStr"/>
       <c r="B217" s="6" t="inlineStr"/>
       <c r="C217" s="6" t="inlineStr"/>
@@ -7584,133 +7564,93 @@
       <c r="F217" s="6" t="inlineStr"/>
       <c r="G217" s="6" t="inlineStr">
         <is>
-          <t>LA MADELEINE</t>
+          <t>BREST PASTEUR</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr"/>
       <c r="I217" s="6" t="inlineStr">
         <is>
-          <t>CHARLES DELOBELLE</t>
+          <t>LUCILE PRIGENT</t>
         </is>
       </c>
       <c r="J217" s="6" t="inlineStr">
         <is>
-          <t>ASSISTANT</t>
+          <t>ASSISTANTE &amp; GESTIONNAIRE COMMUNICATION</t>
         </is>
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>03 28 82 99 31</t>
+          <t>02 98 41 17 24</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr">
         <is>
-          <t>cdelobelle@soprema.fr</t>
+          <t>lprigent@soprema.fr</t>
         </is>
       </c>
       <c r="M217" s="6" t="inlineStr">
         <is>
-          <t>SOPRASSISTANCE LILLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="15.9" customHeight="1">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B218" s="5" t="inlineStr">
-        <is>
-          <t>STAFF CLEAN 3D</t>
-        </is>
-      </c>
-      <c r="C218" s="5" t="inlineStr">
-        <is>
-          <t>FSST0123</t>
-        </is>
-      </c>
-      <c r="D218" s="4" t="inlineStr">
-        <is>
-          <t>STAFF CLEAN 3D</t>
-        </is>
-      </c>
-      <c r="E218" s="4" t="inlineStr">
-        <is>
-          <t>NUISIBLES</t>
-        </is>
-      </c>
-      <c r="F218" s="4" t="inlineStr">
-        <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G218" s="4" t="inlineStr">
-        <is>
-          <t>LA CIOTAT</t>
-        </is>
-      </c>
-      <c r="H218" s="4" t="inlineStr"/>
-      <c r="I218" s="4" t="inlineStr"/>
-      <c r="J218" s="4" t="inlineStr"/>
-      <c r="K218" s="4" t="inlineStr"/>
-      <c r="L218" s="4" t="inlineStr"/>
-      <c r="M218" s="4" t="inlineStr">
-        <is>
-          <t>AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="41.7" customHeight="1">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B219" s="5" t="inlineStr">
-        <is>
-          <t>TECH 9 ENERGIE</t>
-        </is>
-      </c>
-      <c r="C219" s="5" t="inlineStr">
-        <is>
-          <t>FSTE0082</t>
-        </is>
-      </c>
-      <c r="D219" s="4" t="inlineStr">
-        <is>
-          <t>TECH9 ENERGIE</t>
-        </is>
-      </c>
-      <c r="E219" s="4" t="inlineStr">
-        <is>
-          <t>CLIMATICIEN</t>
-        </is>
-      </c>
-      <c r="F219" s="4" t="inlineStr">
-        <is>
-          <t>SUD</t>
-        </is>
-      </c>
-      <c r="G219" s="4" t="inlineStr">
-        <is>
-          <t>CLIMATICIEN ; NOTRE CONTACT CHEZ GROUPTECH9</t>
-        </is>
-      </c>
-      <c r="H219" s="4" t="inlineStr">
-        <is>
-          <t>04 12 04 09 56</t>
-        </is>
-      </c>
-      <c r="I219" s="4" t="inlineStr"/>
-      <c r="J219" s="4" t="inlineStr"/>
-      <c r="K219" s="4" t="inlineStr"/>
-      <c r="L219" s="4" t="inlineStr"/>
-      <c r="M219" s="4" t="inlineStr">
-        <is>
-          <t>DOMAINE ABSENT DE LA SOURCE (« CLIMATICIEN » SAISI EN COLONNE CENTRE) : RÉTABLI LORS DE LA CONSOLIDATION</t>
-        </is>
-      </c>
+          <t>PLOUDANIEL (29260)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A218" s="6" t="inlineStr"/>
+      <c r="B218" s="6" t="inlineStr"/>
+      <c r="C218" s="6" t="inlineStr"/>
+      <c r="D218" s="6" t="inlineStr"/>
+      <c r="E218" s="6" t="inlineStr"/>
+      <c r="F218" s="6" t="inlineStr"/>
+      <c r="G218" s="6" t="inlineStr">
+        <is>
+          <t>BREST PASTEUR</t>
+        </is>
+      </c>
+      <c r="H218" s="6" t="inlineStr"/>
+      <c r="I218" s="6" t="inlineStr">
+        <is>
+          <t>SOLÈNE CORRE</t>
+        </is>
+      </c>
+      <c r="J218" s="6" t="inlineStr">
+        <is>
+          <t>CONDUCTEUR DE TRAVAUX</t>
+        </is>
+      </c>
+      <c r="K218" s="6" t="inlineStr"/>
+      <c r="L218" s="6" t="inlineStr">
+        <is>
+          <t>scorre@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M218" s="6" t="inlineStr"/>
+    </row>
+    <row r="219" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A219" s="6" t="inlineStr"/>
+      <c r="B219" s="6" t="inlineStr"/>
+      <c r="C219" s="6" t="inlineStr"/>
+      <c r="D219" s="6" t="inlineStr"/>
+      <c r="E219" s="6" t="inlineStr"/>
+      <c r="F219" s="6" t="inlineStr"/>
+      <c r="G219" s="6" t="inlineStr">
+        <is>
+          <t>BREST PASTEUR</t>
+        </is>
+      </c>
+      <c r="H219" s="6" t="inlineStr"/>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t>COURRIEL GÉNÉRIQUE AGENCE BREST</t>
+        </is>
+      </c>
+      <c r="J219" s="6" t="inlineStr"/>
+      <c r="K219" s="6" t="inlineStr"/>
+      <c r="L219" s="6" t="inlineStr">
+        <is>
+          <t>soprassistance-brest@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M219" s="6" t="inlineStr"/>
     </row>
     <row r="220" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A220" s="6" t="inlineStr"/>
@@ -7719,26 +7659,26 @@
       <c r="D220" s="6" t="inlineStr"/>
       <c r="E220" s="6" t="inlineStr"/>
       <c r="F220" s="6" t="inlineStr"/>
-      <c r="G220" s="6" t="inlineStr"/>
+      <c r="G220" s="6" t="inlineStr">
+        <is>
+          <t>ST GILLES CROIX DE VIE ET</t>
+        </is>
+      </c>
       <c r="H220" s="6" t="inlineStr"/>
       <c r="I220" s="6" t="inlineStr">
         <is>
-          <t>JEAN-PIERRE CAPPONI</t>
-        </is>
-      </c>
-      <c r="J220" s="6" t="inlineStr">
-        <is>
-          <t>DIRECTION</t>
-        </is>
-      </c>
+          <t>ASSISTANTE D'AGENCE VENDÉE</t>
+        </is>
+      </c>
+      <c r="J220" s="6" t="inlineStr"/>
       <c r="K220" s="6" t="inlineStr">
         <is>
-          <t>04 90 50 33 59 / 06 20 76 44 06</t>
+          <t>02 28 97 72 31</t>
         </is>
       </c>
       <c r="L220" s="6" t="inlineStr">
         <is>
-          <t>jp.capponi@grouptech9.fr</t>
+          <t>soprassistance-vendee@soprema.fr</t>
         </is>
       </c>
       <c r="M220" s="6" t="inlineStr"/>
@@ -7752,31 +7692,35 @@
       <c r="F221" s="6" t="inlineStr"/>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>NOTRE CONTACT CHEZ GROUPTECH9</t>
+          <t>VENDÉE</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr"/>
       <c r="I221" s="6" t="inlineStr">
         <is>
-          <t>CHRISTOPHE LECOINTE</t>
+          <t>DAVID VINCENT</t>
         </is>
       </c>
       <c r="J221" s="6" t="inlineStr">
         <is>
-          <t>RESPONSABLE D’AFFAIRES TECH9</t>
+          <t>RESPONSABLE D'AGENCE VENDÉE</t>
         </is>
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>07 57 50 11 70</t>
+          <t>02 28 97 72 31 / 06 47 85 97 52</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr">
         <is>
-          <t>c.lecointe@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M221" s="6" t="inlineStr"/>
+          <t>davincent@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M221" s="6" t="inlineStr">
+        <is>
+          <t>9 RUE AMPÈRE, BP3, 85170 LE POIRÉ-SUR-VIE</t>
+        </is>
+      </c>
     </row>
     <row r="222" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A222" s="6" t="inlineStr"/>
@@ -7785,75 +7729,107 @@
       <c r="D222" s="6" t="inlineStr"/>
       <c r="E222" s="6" t="inlineStr"/>
       <c r="F222" s="6" t="inlineStr"/>
-      <c r="G222" s="6" t="inlineStr"/>
+      <c r="G222" s="6" t="inlineStr">
+        <is>
+          <t>ORANGE</t>
+        </is>
+      </c>
       <c r="H222" s="6" t="inlineStr"/>
       <c r="I222" s="6" t="inlineStr">
         <is>
-          <t>MME V. ARCAMONE (GÈRE LA FACTURATION)</t>
-        </is>
-      </c>
-      <c r="J222" s="6" t="inlineStr">
-        <is>
-          <t>PRODUCTION (CHOIX 2)</t>
-        </is>
-      </c>
+          <t>OLIVIER BECKER</t>
+        </is>
+      </c>
+      <c r="J222" s="6" t="inlineStr"/>
       <c r="K222" s="6" t="inlineStr">
         <is>
-          <t>04 90 50 33 59</t>
+          <t>04 90 14 89 27 / 06 87 56 73 32</t>
         </is>
       </c>
       <c r="L222" s="6" t="inlineStr">
         <is>
-          <t>v.arcamone@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M222" s="6" t="inlineStr"/>
-    </row>
-    <row r="223" outlineLevel="1" ht="41.7" customHeight="1">
+          <t>obecker@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M222" s="6" t="inlineStr">
+        <is>
+          <t>125, RUE DES QUATRE GENDARMES D'OUVÉA 84000 AVIGNON</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A223" s="6" t="inlineStr"/>
       <c r="B223" s="6" t="inlineStr"/>
       <c r="C223" s="6" t="inlineStr"/>
       <c r="D223" s="6" t="inlineStr"/>
       <c r="E223" s="6" t="inlineStr"/>
       <c r="F223" s="6" t="inlineStr"/>
-      <c r="G223" s="6" t="inlineStr"/>
+      <c r="G223" s="6" t="inlineStr">
+        <is>
+          <t>DOUAI</t>
+        </is>
+      </c>
       <c r="H223" s="6" t="inlineStr"/>
       <c r="I223" s="6" t="inlineStr">
         <is>
-          <t>MME MARIELLE LUCCINI (À METTRE EN COPIE CC EN CAS ABS MME ARCAMONE)</t>
+          <t>YOHAN FRERE</t>
         </is>
       </c>
       <c r="J223" s="6" t="inlineStr"/>
-      <c r="K223" s="6" t="inlineStr"/>
+      <c r="K223" s="6" t="inlineStr">
+        <is>
+          <t>03 20 86 27 69 / 06 08 14 70 57</t>
+        </is>
+      </c>
       <c r="L223" s="6" t="inlineStr">
         <is>
-          <t>m.luccini@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M223" s="6" t="inlineStr"/>
-    </row>
-    <row r="224" outlineLevel="1" ht="41.7" customHeight="1">
+          <t>yfrere@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M223" s="6" t="inlineStr">
+        <is>
+          <t>208 RUE DES BOULEAUX 59860 BRUAY-SUR-L'ESCAUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A224" s="6" t="inlineStr"/>
       <c r="B224" s="6" t="inlineStr"/>
       <c r="C224" s="6" t="inlineStr"/>
       <c r="D224" s="6" t="inlineStr"/>
       <c r="E224" s="6" t="inlineStr"/>
       <c r="F224" s="6" t="inlineStr"/>
-      <c r="G224" s="6" t="inlineStr"/>
+      <c r="G224" s="6" t="inlineStr">
+        <is>
+          <t>LA MADELEINE</t>
+        </is>
+      </c>
       <c r="H224" s="6" t="inlineStr"/>
       <c r="I224" s="6" t="inlineStr">
         <is>
-          <t>M. VALENTIN FLEUREAU (EN CAS D'ABSENCE DE MME LUCCINI)</t>
-        </is>
-      </c>
-      <c r="J224" s="6" t="inlineStr"/>
-      <c r="K224" s="6" t="inlineStr"/>
+          <t>ANTOINE FRANÇOIS</t>
+        </is>
+      </c>
+      <c r="J224" s="6" t="inlineStr">
+        <is>
+          <t>CONDUCTEUR DE TRAVAUX</t>
+        </is>
+      </c>
+      <c r="K224" s="6" t="inlineStr">
+        <is>
+          <t>03 28 82 99 34 / 06 07 63 80 74</t>
+        </is>
+      </c>
       <c r="L224" s="6" t="inlineStr">
         <is>
-          <t>f.fleureau@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M224" s="6" t="inlineStr"/>
+          <t>afrancois@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M224" s="6" t="inlineStr">
+        <is>
+          <t>851 RUE DU CHEMIN VERT FRETIN CRT 3 - BP104 59810 LESQUIN CEDEX</t>
+        </is>
+      </c>
     </row>
     <row r="225" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A225" s="6" t="inlineStr"/>
@@ -7862,77 +7838,137 @@
       <c r="D225" s="6" t="inlineStr"/>
       <c r="E225" s="6" t="inlineStr"/>
       <c r="F225" s="6" t="inlineStr"/>
-      <c r="G225" s="6" t="inlineStr"/>
+      <c r="G225" s="6" t="inlineStr">
+        <is>
+          <t>LA MADELEINE</t>
+        </is>
+      </c>
       <c r="H225" s="6" t="inlineStr"/>
       <c r="I225" s="6" t="inlineStr">
         <is>
-          <t>OLIVIER PARTAGE</t>
+          <t>CHARLES DELOBELLE</t>
         </is>
       </c>
       <c r="J225" s="6" t="inlineStr">
         <is>
-          <t>GRANDS TRAVAUX</t>
+          <t>ASSISTANT</t>
         </is>
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>07 48 11 96 52</t>
+          <t>03 28 82 99 31</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr">
         <is>
-          <t>o.partage@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M225" s="6" t="inlineStr"/>
-    </row>
-    <row r="226" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A226" s="6" t="inlineStr"/>
-      <c r="B226" s="6" t="inlineStr"/>
-      <c r="C226" s="6" t="inlineStr"/>
-      <c r="D226" s="6" t="inlineStr"/>
-      <c r="E226" s="6" t="inlineStr"/>
-      <c r="F226" s="6" t="inlineStr"/>
-      <c r="G226" s="6" t="inlineStr"/>
-      <c r="H226" s="6" t="inlineStr"/>
-      <c r="I226" s="6" t="inlineStr"/>
-      <c r="J226" s="6" t="inlineStr"/>
-      <c r="K226" s="6" t="inlineStr"/>
-      <c r="L226" s="6" t="inlineStr">
-        <is>
-          <t>a.laune@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M226" s="6" t="inlineStr"/>
-    </row>
-    <row r="227" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A227" s="6" t="inlineStr"/>
-      <c r="B227" s="6" t="inlineStr"/>
-      <c r="C227" s="6" t="inlineStr"/>
-      <c r="D227" s="6" t="inlineStr"/>
-      <c r="E227" s="6" t="inlineStr"/>
-      <c r="F227" s="6" t="inlineStr"/>
-      <c r="G227" s="6" t="inlineStr"/>
-      <c r="H227" s="6" t="inlineStr"/>
-      <c r="I227" s="6" t="inlineStr">
-        <is>
-          <t>COMPTABILITÉ CLIENT (MARDI ET JEUDI DE 9H30 À 12H)</t>
-        </is>
-      </c>
-      <c r="J227" s="6" t="inlineStr"/>
-      <c r="K227" s="6" t="inlineStr">
+          <t>cdelobelle@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M225" s="6" t="inlineStr">
+        <is>
+          <t>SOPRASSISTANCE LILLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="15.9" customHeight="1">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>STAFF CLEAN 3D</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>FSST0123</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>STAFF CLEAN 3D</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="inlineStr">
+        <is>
+          <t>NUISIBLES</t>
+        </is>
+      </c>
+      <c r="F226" s="4" t="inlineStr">
+        <is>
+          <t>SUD EST</t>
+        </is>
+      </c>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>LA CIOTAT</t>
+        </is>
+      </c>
+      <c r="H226" s="4" t="inlineStr"/>
+      <c r="I226" s="4" t="inlineStr"/>
+      <c r="J226" s="4" t="inlineStr"/>
+      <c r="K226" s="4" t="inlineStr"/>
+      <c r="L226" s="4" t="inlineStr"/>
+      <c r="M226" s="4" t="inlineStr">
+        <is>
+          <t>AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="41.7" customHeight="1">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>TECH 9 ENERGIE</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>FSTE0082</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>TECH9 ENERGIE</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>CLIMATICIEN</t>
+        </is>
+      </c>
+      <c r="F227" s="4" t="inlineStr">
+        <is>
+          <t>SUD</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr">
+        <is>
+          <t>CLIMATICIEN ; NOTRE CONTACT CHEZ GROUPTECH9</t>
+        </is>
+      </c>
+      <c r="H227" s="4" t="inlineStr">
         <is>
           <t>04 12 04 09 56</t>
         </is>
       </c>
-      <c r="L227" s="6" t="inlineStr">
-        <is>
-          <t>fournisseurs@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M227" s="6" t="inlineStr"/>
-    </row>
-    <row r="228" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="I227" s="4" t="inlineStr"/>
+      <c r="J227" s="4" t="inlineStr"/>
+      <c r="K227" s="4" t="inlineStr"/>
+      <c r="L227" s="4" t="inlineStr"/>
+      <c r="M227" s="4" t="inlineStr">
+        <is>
+          <t>DOMAINE ABSENT DE LA SOURCE (« CLIMATICIEN » SAISI EN COLONNE CENTRE) : RÉTABLI LORS DE LA CONSOLIDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A228" s="6" t="inlineStr"/>
       <c r="B228" s="6" t="inlineStr"/>
       <c r="C228" s="6" t="inlineStr"/>
@@ -7943,50 +7979,62 @@
       <c r="H228" s="6" t="inlineStr"/>
       <c r="I228" s="6" t="inlineStr">
         <is>
-          <t>FRED</t>
+          <t>JEAN-PIERRE CAPPONI</t>
         </is>
       </c>
       <c r="J228" s="6" t="inlineStr">
         <is>
-          <t>TECHNICIEN MAINTENANCE</t>
+          <t>DIRECTION</t>
         </is>
       </c>
       <c r="K228" s="6" t="inlineStr">
         <is>
-          <t>07 83 70 87 89</t>
-        </is>
-      </c>
-      <c r="L228" s="6" t="inlineStr"/>
+          <t>04 90 50 33 59 / 06 20 76 44 06</t>
+        </is>
+      </c>
+      <c r="L228" s="6" t="inlineStr">
+        <is>
+          <t>jp.capponi@grouptech9.fr</t>
+        </is>
+      </c>
       <c r="M228" s="6" t="inlineStr"/>
     </row>
-    <row r="229" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="229" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A229" s="6" t="inlineStr"/>
       <c r="B229" s="6" t="inlineStr"/>
       <c r="C229" s="6" t="inlineStr"/>
       <c r="D229" s="6" t="inlineStr"/>
       <c r="E229" s="6" t="inlineStr"/>
       <c r="F229" s="6" t="inlineStr"/>
-      <c r="G229" s="6" t="inlineStr"/>
+      <c r="G229" s="6" t="inlineStr">
+        <is>
+          <t>NOTRE CONTACT CHEZ GROUPTECH9</t>
+        </is>
+      </c>
       <c r="H229" s="6" t="inlineStr"/>
       <c r="I229" s="6" t="inlineStr">
         <is>
-          <t>P. SANGIARDI</t>
+          <t>CHRISTOPHE LECOINTE</t>
         </is>
       </c>
       <c r="J229" s="6" t="inlineStr">
         <is>
-          <t>DIRECTION ICE</t>
-        </is>
-      </c>
-      <c r="K229" s="6" t="inlineStr"/>
+          <t>RESPONSABLE D’AFFAIRES TECH9</t>
+        </is>
+      </c>
+      <c r="K229" s="6" t="inlineStr">
+        <is>
+          <t>07 57 50 11 70</t>
+        </is>
+      </c>
       <c r="L229" s="6" t="inlineStr">
         <is>
-          <t>p.sangiardi@grouptech9.fr</t>
+          <t>c.lecointe@grouptech9.fr</t>
         </is>
       </c>
       <c r="M229" s="6" t="inlineStr"/>
     </row>
-    <row r="230" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="230" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A230" s="6" t="inlineStr"/>
       <c r="B230" s="6" t="inlineStr"/>
       <c r="C230" s="6" t="inlineStr"/>
@@ -7997,23 +8045,27 @@
       <c r="H230" s="6" t="inlineStr"/>
       <c r="I230" s="6" t="inlineStr">
         <is>
-          <t>JP. CAPPONI</t>
+          <t>MME V. ARCAMONE (GÈRE LA FACTURATION)</t>
         </is>
       </c>
       <c r="J230" s="6" t="inlineStr">
         <is>
-          <t>DIRECTION ICE</t>
-        </is>
-      </c>
-      <c r="K230" s="6" t="inlineStr"/>
+          <t>PRODUCTION (CHOIX 2)</t>
+        </is>
+      </c>
+      <c r="K230" s="6" t="inlineStr">
+        <is>
+          <t>04 90 50 33 59</t>
+        </is>
+      </c>
       <c r="L230" s="6" t="inlineStr">
         <is>
-          <t>jp.capponi@grouptech9.fr</t>
+          <t>v.arcamone@grouptech9.fr</t>
         </is>
       </c>
       <c r="M230" s="6" t="inlineStr"/>
     </row>
-    <row r="231" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="231" outlineLevel="1" ht="41.7" customHeight="1">
       <c r="A231" s="6" t="inlineStr"/>
       <c r="B231" s="6" t="inlineStr"/>
       <c r="C231" s="6" t="inlineStr"/>
@@ -8024,19 +8076,19 @@
       <c r="H231" s="6" t="inlineStr"/>
       <c r="I231" s="6" t="inlineStr">
         <is>
-          <t>TRAVAUX ET DÉPANNAGES ICE</t>
+          <t>MME MARIELLE LUCCINI (À METTRE EN COPIE CC EN CAS ABS MME ARCAMONE)</t>
         </is>
       </c>
       <c r="J231" s="6" t="inlineStr"/>
       <c r="K231" s="6" t="inlineStr"/>
       <c r="L231" s="6" t="inlineStr">
         <is>
-          <t>e.carasco@grouptech9.fr</t>
+          <t>m.luccini@grouptech9.fr</t>
         </is>
       </c>
       <c r="M231" s="6" t="inlineStr"/>
     </row>
-    <row r="232" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="232" outlineLevel="1" ht="41.7" customHeight="1">
       <c r="A232" s="6" t="inlineStr"/>
       <c r="B232" s="6" t="inlineStr"/>
       <c r="C232" s="6" t="inlineStr"/>
@@ -8047,64 +8099,48 @@
       <c r="H232" s="6" t="inlineStr"/>
       <c r="I232" s="6" t="inlineStr">
         <is>
-          <t>PEGGY CARRENO (FACTURES ICE)</t>
-        </is>
-      </c>
-      <c r="J232" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANTE, SERVICE COMPTABLE</t>
-        </is>
-      </c>
-      <c r="K232" s="6" t="inlineStr">
-        <is>
-          <t>04 42 50 69 89</t>
-        </is>
-      </c>
+          <t>M. VALENTIN FLEUREAU (EN CAS D'ABSENCE DE MME LUCCINI)</t>
+        </is>
+      </c>
+      <c r="J232" s="6" t="inlineStr"/>
+      <c r="K232" s="6" t="inlineStr"/>
       <c r="L232" s="6" t="inlineStr">
         <is>
-          <t>contact.ice@grouptech9.fr</t>
+          <t>f.fleureau@grouptech9.fr</t>
         </is>
       </c>
       <c r="M232" s="6" t="inlineStr"/>
     </row>
-    <row r="233" ht="28.8" customHeight="1">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B233" s="5" t="inlineStr">
-        <is>
-          <t>THIBAUT BOUISSON</t>
-        </is>
-      </c>
-      <c r="C233" s="5" t="inlineStr">
-        <is>
-          <t>FSBO0099</t>
-        </is>
-      </c>
-      <c r="D233" s="4" t="inlineStr">
-        <is>
-          <t>BOUISSON THIBAUT</t>
-        </is>
-      </c>
-      <c r="E233" s="4" t="inlineStr">
-        <is>
-          <t>ESPACES VERTS / PAYSAGISTE</t>
-        </is>
-      </c>
-      <c r="F233" s="4" t="inlineStr"/>
-      <c r="G233" s="4" t="inlineStr">
-        <is>
-          <t>MONTPELLIER AIGUELONGUE</t>
-        </is>
-      </c>
-      <c r="H233" s="4" t="inlineStr"/>
-      <c r="I233" s="4" t="inlineStr"/>
-      <c r="J233" s="4" t="inlineStr"/>
-      <c r="K233" s="4" t="inlineStr"/>
-      <c r="L233" s="4" t="inlineStr"/>
-      <c r="M233" s="4" t="inlineStr"/>
+    <row r="233" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A233" s="6" t="inlineStr"/>
+      <c r="B233" s="6" t="inlineStr"/>
+      <c r="C233" s="6" t="inlineStr"/>
+      <c r="D233" s="6" t="inlineStr"/>
+      <c r="E233" s="6" t="inlineStr"/>
+      <c r="F233" s="6" t="inlineStr"/>
+      <c r="G233" s="6" t="inlineStr"/>
+      <c r="H233" s="6" t="inlineStr"/>
+      <c r="I233" s="6" t="inlineStr">
+        <is>
+          <t>OLIVIER PARTAGE</t>
+        </is>
+      </c>
+      <c r="J233" s="6" t="inlineStr">
+        <is>
+          <t>GRANDS TRAVAUX</t>
+        </is>
+      </c>
+      <c r="K233" s="6" t="inlineStr">
+        <is>
+          <t>07 48 11 96 52</t>
+        </is>
+      </c>
+      <c r="L233" s="6" t="inlineStr">
+        <is>
+          <t>o.partage@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M233" s="6" t="inlineStr"/>
     </row>
     <row r="234" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A234" s="6" t="inlineStr"/>
@@ -8115,66 +8151,42 @@
       <c r="F234" s="6" t="inlineStr"/>
       <c r="G234" s="6" t="inlineStr"/>
       <c r="H234" s="6" t="inlineStr"/>
-      <c r="I234" s="6" t="inlineStr">
-        <is>
-          <t>THIBAUT BOUISSON</t>
-        </is>
-      </c>
-      <c r="J234" s="6" t="inlineStr">
-        <is>
-          <t>GÉRANT</t>
-        </is>
-      </c>
-      <c r="K234" s="6" t="inlineStr">
-        <is>
-          <t>06 42 78 88 91</t>
-        </is>
-      </c>
-      <c r="L234" s="6" t="inlineStr"/>
+      <c r="I234" s="6" t="inlineStr"/>
+      <c r="J234" s="6" t="inlineStr"/>
+      <c r="K234" s="6" t="inlineStr"/>
+      <c r="L234" s="6" t="inlineStr">
+        <is>
+          <t>a.laune@grouptech9.fr</t>
+        </is>
+      </c>
       <c r="M234" s="6" t="inlineStr"/>
     </row>
-    <row r="235" ht="15.9" customHeight="1">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B235" s="5" t="inlineStr">
-        <is>
-          <t>VERRE SOLUTIONS NANTES</t>
-        </is>
-      </c>
-      <c r="C235" s="5" t="inlineStr">
-        <is>
-          <t>FSVE0047</t>
-        </is>
-      </c>
-      <c r="D235" s="4" t="inlineStr">
-        <is>
-          <t>VERRE SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="E235" s="4" t="inlineStr">
-        <is>
-          <t>PORTE AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="F235" s="4" t="inlineStr">
-        <is>
-          <t>OUEST</t>
-        </is>
-      </c>
-      <c r="G235" s="4" t="inlineStr">
-        <is>
-          <t>LA BAULE PALMIERS</t>
-        </is>
-      </c>
-      <c r="H235" s="4" t="inlineStr"/>
-      <c r="I235" s="4" t="inlineStr"/>
-      <c r="J235" s="4" t="inlineStr"/>
-      <c r="K235" s="4" t="inlineStr"/>
-      <c r="L235" s="4" t="inlineStr"/>
-      <c r="M235" s="4" t="inlineStr"/>
+    <row r="235" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A235" s="6" t="inlineStr"/>
+      <c r="B235" s="6" t="inlineStr"/>
+      <c r="C235" s="6" t="inlineStr"/>
+      <c r="D235" s="6" t="inlineStr"/>
+      <c r="E235" s="6" t="inlineStr"/>
+      <c r="F235" s="6" t="inlineStr"/>
+      <c r="G235" s="6" t="inlineStr"/>
+      <c r="H235" s="6" t="inlineStr"/>
+      <c r="I235" s="6" t="inlineStr">
+        <is>
+          <t>COMPTABILITÉ CLIENT (MARDI ET JEUDI DE 9H30 À 12H)</t>
+        </is>
+      </c>
+      <c r="J235" s="6" t="inlineStr"/>
+      <c r="K235" s="6" t="inlineStr">
+        <is>
+          <t>04 12 04 09 56</t>
+        </is>
+      </c>
+      <c r="L235" s="6" t="inlineStr">
+        <is>
+          <t>fournisseurs@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M235" s="6" t="inlineStr"/>
     </row>
     <row r="236" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A236" s="6" t="inlineStr"/>
@@ -8187,52 +8199,48 @@
       <c r="H236" s="6" t="inlineStr"/>
       <c r="I236" s="6" t="inlineStr">
         <is>
-          <t>AUDREY COUSIN</t>
-        </is>
-      </c>
-      <c r="J236" s="6" t="inlineStr"/>
+          <t>FRED</t>
+        </is>
+      </c>
+      <c r="J236" s="6" t="inlineStr">
+        <is>
+          <t>TECHNICIEN MAINTENANCE</t>
+        </is>
+      </c>
       <c r="K236" s="6" t="inlineStr">
         <is>
-          <t>02 40 72 52 38</t>
+          <t>07 83 70 87 89</t>
         </is>
       </c>
       <c r="L236" s="6" t="inlineStr"/>
-      <c r="M236" s="6" t="inlineStr">
-        <is>
-          <t>10-12 RUE DES GRANDES BOSSES, 44220 COUËRON</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="41.7" customHeight="1">
-      <c r="A237" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B237" s="5" t="inlineStr">
-        <is>
-          <t>VERT BEAU BOIS</t>
-        </is>
-      </c>
-      <c r="C237" s="5" t="inlineStr"/>
-      <c r="D237" s="4" t="inlineStr"/>
-      <c r="E237" s="4" t="inlineStr">
-        <is>
-          <t>ESPACES VERTS / PAYSAGISTE</t>
-        </is>
-      </c>
-      <c r="F237" s="4" t="inlineStr"/>
-      <c r="G237" s="4" t="inlineStr"/>
-      <c r="H237" s="4" t="inlineStr"/>
-      <c r="I237" s="4" t="inlineStr"/>
-      <c r="J237" s="4" t="inlineStr"/>
-      <c r="K237" s="4" t="inlineStr"/>
-      <c r="L237" s="4" t="inlineStr"/>
-      <c r="M237" s="4" t="inlineStr">
-        <is>
-          <t>AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
-        </is>
-      </c>
+      <c r="M236" s="6" t="inlineStr"/>
+    </row>
+    <row r="237" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A237" s="6" t="inlineStr"/>
+      <c r="B237" s="6" t="inlineStr"/>
+      <c r="C237" s="6" t="inlineStr"/>
+      <c r="D237" s="6" t="inlineStr"/>
+      <c r="E237" s="6" t="inlineStr"/>
+      <c r="F237" s="6" t="inlineStr"/>
+      <c r="G237" s="6" t="inlineStr"/>
+      <c r="H237" s="6" t="inlineStr"/>
+      <c r="I237" s="6" t="inlineStr">
+        <is>
+          <t>P. SANGIARDI</t>
+        </is>
+      </c>
+      <c r="J237" s="6" t="inlineStr">
+        <is>
+          <t>DIRECTION ICE</t>
+        </is>
+      </c>
+      <c r="K237" s="6" t="inlineStr"/>
+      <c r="L237" s="6" t="inlineStr">
+        <is>
+          <t>p.sangiardi@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M237" s="6" t="inlineStr"/>
     </row>
     <row r="238" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A238" s="6" t="inlineStr"/>
@@ -8245,14 +8253,18 @@
       <c r="H238" s="6" t="inlineStr"/>
       <c r="I238" s="6" t="inlineStr">
         <is>
-          <t>GESTION CONTRAT, DEVIS</t>
-        </is>
-      </c>
-      <c r="J238" s="6" t="inlineStr"/>
+          <t>JP. CAPPONI</t>
+        </is>
+      </c>
+      <c r="J238" s="6" t="inlineStr">
+        <is>
+          <t>DIRECTION ICE</t>
+        </is>
+      </c>
       <c r="K238" s="6" t="inlineStr"/>
       <c r="L238" s="6" t="inlineStr">
         <is>
-          <t>contact@vertbeaubois.fr</t>
+          <t>jp.capponi@grouptech9.fr</t>
         </is>
       </c>
       <c r="M238" s="6" t="inlineStr"/>
@@ -8268,20 +8280,264 @@
       <c r="H239" s="6" t="inlineStr"/>
       <c r="I239" s="6" t="inlineStr">
         <is>
-          <t>COMPTABILITÉ</t>
+          <t>TRAVAUX ET DÉPANNAGES ICE</t>
         </is>
       </c>
       <c r="J239" s="6" t="inlineStr"/>
       <c r="K239" s="6" t="inlineStr"/>
       <c r="L239" s="6" t="inlineStr">
         <is>
+          <t>e.carasco@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M239" s="6" t="inlineStr"/>
+    </row>
+    <row r="240" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A240" s="6" t="inlineStr"/>
+      <c r="B240" s="6" t="inlineStr"/>
+      <c r="C240" s="6" t="inlineStr"/>
+      <c r="D240" s="6" t="inlineStr"/>
+      <c r="E240" s="6" t="inlineStr"/>
+      <c r="F240" s="6" t="inlineStr"/>
+      <c r="G240" s="6" t="inlineStr"/>
+      <c r="H240" s="6" t="inlineStr"/>
+      <c r="I240" s="6" t="inlineStr">
+        <is>
+          <t>PEGGY CARRENO (FACTURES ICE)</t>
+        </is>
+      </c>
+      <c r="J240" s="6" t="inlineStr">
+        <is>
+          <t>ASSISTANTE, SERVICE COMPTABLE</t>
+        </is>
+      </c>
+      <c r="K240" s="6" t="inlineStr">
+        <is>
+          <t>04 42 50 69 89</t>
+        </is>
+      </c>
+      <c r="L240" s="6" t="inlineStr">
+        <is>
+          <t>contact.ice@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M240" s="6" t="inlineStr"/>
+    </row>
+    <row r="241" ht="28.8" customHeight="1">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
+        <is>
+          <t>THIBAUT BOUISSON</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>FSBO0099</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>BOUISSON THIBAUT</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>ESPACES VERTS / PAYSAGISTE</t>
+        </is>
+      </c>
+      <c r="F241" s="4" t="inlineStr"/>
+      <c r="G241" s="4" t="inlineStr">
+        <is>
+          <t>MONTPELLIER AIGUELONGUE</t>
+        </is>
+      </c>
+      <c r="H241" s="4" t="inlineStr"/>
+      <c r="I241" s="4" t="inlineStr"/>
+      <c r="J241" s="4" t="inlineStr"/>
+      <c r="K241" s="4" t="inlineStr"/>
+      <c r="L241" s="4" t="inlineStr"/>
+      <c r="M241" s="4" t="inlineStr"/>
+    </row>
+    <row r="242" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A242" s="6" t="inlineStr"/>
+      <c r="B242" s="6" t="inlineStr"/>
+      <c r="C242" s="6" t="inlineStr"/>
+      <c r="D242" s="6" t="inlineStr"/>
+      <c r="E242" s="6" t="inlineStr"/>
+      <c r="F242" s="6" t="inlineStr"/>
+      <c r="G242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="inlineStr"/>
+      <c r="I242" s="6" t="inlineStr">
+        <is>
+          <t>THIBAUT BOUISSON</t>
+        </is>
+      </c>
+      <c r="J242" s="6" t="inlineStr">
+        <is>
+          <t>GÉRANT</t>
+        </is>
+      </c>
+      <c r="K242" s="6" t="inlineStr">
+        <is>
+          <t>06 42 78 88 91</t>
+        </is>
+      </c>
+      <c r="L242" s="6" t="inlineStr"/>
+      <c r="M242" s="6" t="inlineStr"/>
+    </row>
+    <row r="243" ht="15.9" customHeight="1">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>VERRE SOLUTIONS NANTES</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>FSVE0047</t>
+        </is>
+      </c>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>VERRE SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>PORTE AUTOMATIQUE</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>OUEST</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>LA BAULE PALMIERS</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="inlineStr"/>
+      <c r="I243" s="4" t="inlineStr"/>
+      <c r="J243" s="4" t="inlineStr"/>
+      <c r="K243" s="4" t="inlineStr"/>
+      <c r="L243" s="4" t="inlineStr"/>
+      <c r="M243" s="4" t="inlineStr"/>
+    </row>
+    <row r="244" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A244" s="6" t="inlineStr"/>
+      <c r="B244" s="6" t="inlineStr"/>
+      <c r="C244" s="6" t="inlineStr"/>
+      <c r="D244" s="6" t="inlineStr"/>
+      <c r="E244" s="6" t="inlineStr"/>
+      <c r="F244" s="6" t="inlineStr"/>
+      <c r="G244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="inlineStr"/>
+      <c r="I244" s="6" t="inlineStr">
+        <is>
+          <t>AUDREY COUSIN</t>
+        </is>
+      </c>
+      <c r="J244" s="6" t="inlineStr"/>
+      <c r="K244" s="6" t="inlineStr">
+        <is>
+          <t>02 40 72 52 38</t>
+        </is>
+      </c>
+      <c r="L244" s="6" t="inlineStr"/>
+      <c r="M244" s="6" t="inlineStr">
+        <is>
+          <t>10-12 RUE DES GRANDES BOSSES, 44220 COUËRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="41.7" customHeight="1">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B245" s="5" t="inlineStr">
+        <is>
+          <t>VERT BEAU BOIS</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="inlineStr"/>
+      <c r="D245" s="4" t="inlineStr"/>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>ESPACES VERTS / PAYSAGISTE</t>
+        </is>
+      </c>
+      <c r="F245" s="4" t="inlineStr"/>
+      <c r="G245" s="4" t="inlineStr"/>
+      <c r="H245" s="4" t="inlineStr"/>
+      <c r="I245" s="4" t="inlineStr"/>
+      <c r="J245" s="4" t="inlineStr"/>
+      <c r="K245" s="4" t="inlineStr"/>
+      <c r="L245" s="4" t="inlineStr"/>
+      <c r="M245" s="4" t="inlineStr">
+        <is>
+          <t>AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A246" s="6" t="inlineStr"/>
+      <c r="B246" s="6" t="inlineStr"/>
+      <c r="C246" s="6" t="inlineStr"/>
+      <c r="D246" s="6" t="inlineStr"/>
+      <c r="E246" s="6" t="inlineStr"/>
+      <c r="F246" s="6" t="inlineStr"/>
+      <c r="G246" s="6" t="inlineStr"/>
+      <c r="H246" s="6" t="inlineStr"/>
+      <c r="I246" s="6" t="inlineStr">
+        <is>
+          <t>GESTION CONTRAT, DEVIS</t>
+        </is>
+      </c>
+      <c r="J246" s="6" t="inlineStr"/>
+      <c r="K246" s="6" t="inlineStr"/>
+      <c r="L246" s="6" t="inlineStr">
+        <is>
+          <t>contact@vertbeaubois.fr</t>
+        </is>
+      </c>
+      <c r="M246" s="6" t="inlineStr"/>
+    </row>
+    <row r="247" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A247" s="6" t="inlineStr"/>
+      <c r="B247" s="6" t="inlineStr"/>
+      <c r="C247" s="6" t="inlineStr"/>
+      <c r="D247" s="6" t="inlineStr"/>
+      <c r="E247" s="6" t="inlineStr"/>
+      <c r="F247" s="6" t="inlineStr"/>
+      <c r="G247" s="6" t="inlineStr"/>
+      <c r="H247" s="6" t="inlineStr"/>
+      <c r="I247" s="6" t="inlineStr">
+        <is>
+          <t>COMPTABILITÉ</t>
+        </is>
+      </c>
+      <c r="J247" s="6" t="inlineStr"/>
+      <c r="K247" s="6" t="inlineStr"/>
+      <c r="L247" s="6" t="inlineStr">
+        <is>
           <t>compta@vertbeaubois.fr</t>
         </is>
       </c>
-      <c r="M239" s="6" t="inlineStr"/>
+      <c r="M247" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M239"/>
+  <autoFilter ref="A3:M247"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>

--- a/fournisseurs/Table_fournisseurs_consolidee.xlsx
+++ b/fournisseurs/Table_fournisseurs_consolidee.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Fournisseurs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fournisseurs'!$A$3:$M$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Fournisseurs'!$A$3:$M$261</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M247"/>
+  <dimension ref="A1:M261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3843,7 +3843,11 @@
           <t>aducre@eurofeu.r</t>
         </is>
       </c>
-      <c r="M102" s="6" t="inlineStr"/>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>EXTENSION DU COURRIEL INCOMPLÈTE DANS LA SOURCE, À VÉRIFIER</t>
+        </is>
+      </c>
     </row>
     <row r="103" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A103" s="6" t="inlineStr"/>
@@ -4422,7 +4426,7 @@
       </c>
       <c r="L120" s="6" t="inlineStr">
         <is>
-          <t>morgane.tressard@faactechnologies.com&gt;</t>
+          <t>morgane.tressard@faactechnologies.com</t>
         </is>
       </c>
       <c r="M120" s="6" t="inlineStr"/>
@@ -5371,7 +5375,7 @@
       </c>
       <c r="M148" s="6" t="inlineStr"/>
     </row>
-    <row r="149" ht="67.5" customHeight="1">
+    <row r="149" ht="54.6" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
@@ -5379,21 +5383,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>LUSTRAL</t>
+          <t>LORINIS</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr"/>
       <c r="D149" s="4" t="inlineStr"/>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>MÉNAGE</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>EST ; NORD</t>
-        </is>
-      </c>
+          <t>AGENT MULTI-SERVICE</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr"/>
       <c r="G149" s="4" t="inlineStr"/>
       <c r="H149" s="4" t="inlineStr"/>
       <c r="I149" s="4" t="inlineStr"/>
@@ -5402,52 +5402,32 @@
       <c r="L149" s="4" t="inlineStr"/>
       <c r="M149" s="4" t="inlineStr">
         <is>
-          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE SECTEURS EST ET NORD ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="15.9" customHeight="1">
-      <c r="A150" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B150" s="5" t="inlineStr">
-        <is>
-          <t>MATHIS&amp;PHILIP</t>
-        </is>
-      </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>FSMA0109</t>
-        </is>
-      </c>
-      <c r="D150" s="4" t="inlineStr">
-        <is>
-          <t>MATHIS &amp; PHILIP</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>CHAUFFAGISTE</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>EST</t>
-        </is>
-      </c>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>VITTEL</t>
-        </is>
-      </c>
-      <c r="H150" s="4" t="inlineStr"/>
-      <c r="I150" s="4" t="inlineStr"/>
-      <c r="J150" s="4" t="inlineStr"/>
-      <c r="K150" s="4" t="inlineStr"/>
-      <c r="L150" s="4" t="inlineStr"/>
-      <c r="M150" s="4" t="inlineStr"/>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PÔLE À CONFIRMER : PRESTATION À CARACTÈRE SIÈGE / SERVICES GÉNÉRAUX ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A150" s="6" t="inlineStr"/>
+      <c r="B150" s="6" t="inlineStr"/>
+      <c r="C150" s="6" t="inlineStr"/>
+      <c r="D150" s="6" t="inlineStr"/>
+      <c r="E150" s="6" t="inlineStr"/>
+      <c r="F150" s="6" t="inlineStr"/>
+      <c r="G150" s="6" t="inlineStr"/>
+      <c r="H150" s="6" t="inlineStr"/>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>ANTONIO</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="inlineStr"/>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>06 18 32 69 08</t>
+        </is>
+      </c>
+      <c r="L150" s="6" t="inlineStr"/>
+      <c r="M150" s="6" t="inlineStr"/>
     </row>
     <row r="151" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A151" s="6" t="inlineStr"/>
@@ -5460,20 +5440,16 @@
       <c r="H151" s="6" t="inlineStr"/>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>ISABELLE ANTOINE</t>
+          <t>WILLIAM</t>
         </is>
       </c>
       <c r="J151" s="6" t="inlineStr"/>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>03 29 08 01 02</t>
-        </is>
-      </c>
-      <c r="L151" s="6" t="inlineStr">
-        <is>
-          <t>i.antoine@mathisetphilip.com</t>
-        </is>
-      </c>
+          <t>06 58 02 41 68</t>
+        </is>
+      </c>
+      <c r="L151" s="6" t="inlineStr"/>
       <c r="M151" s="6" t="inlineStr"/>
     </row>
     <row r="152" ht="67.5" customHeight="1">
@@ -5484,90 +5460,110 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>MTE LOGISTIC</t>
+          <t>LUSTRAL</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr"/>
       <c r="D152" s="4" t="inlineStr"/>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>RIDEAU METALLIQUE ; MAINTENANCE</t>
+          <t>MÉNAGE</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>EST ; SUD OUEST</t>
-        </is>
-      </c>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>CHALON 2 ; BERGERAC, CHALON 2</t>
-        </is>
-      </c>
-      <c r="H152" s="4" t="inlineStr">
-        <is>
-          <t>04 74 45 56 46</t>
-        </is>
-      </c>
+          <t>EST ; NORD</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr"/>
+      <c r="H152" s="4" t="inlineStr"/>
       <c r="I152" s="4" t="inlineStr"/>
       <c r="J152" s="4" t="inlineStr"/>
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="4" t="inlineStr"/>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>SAISI 2 FOIS DANS LES SOURCES (« ANNUAIRE FRN CONTRATS » (RIDEAU METALLIQUE) + « ANNUAIRE FRN CONTRATS » (MAINTENANCE)) : LIGNES FUSIONNÉES, DOMAINES CUMULÉS ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A153" s="6" t="inlineStr"/>
-      <c r="B153" s="6" t="inlineStr"/>
-      <c r="C153" s="6" t="inlineStr"/>
-      <c r="D153" s="6" t="inlineStr"/>
-      <c r="E153" s="6" t="inlineStr"/>
-      <c r="F153" s="6" t="inlineStr"/>
-      <c r="G153" s="6" t="inlineStr"/>
-      <c r="H153" s="6" t="inlineStr"/>
-      <c r="I153" s="6" t="inlineStr">
-        <is>
-          <t>PATRICIA RAMAKERS</t>
-        </is>
-      </c>
-      <c r="J153" s="6" t="inlineStr">
-        <is>
-          <t>MANAGER</t>
-        </is>
-      </c>
-      <c r="K153" s="6" t="inlineStr"/>
-      <c r="L153" s="6" t="inlineStr">
-        <is>
-          <t>patricia.ramakers@mtelogistic.com</t>
-        </is>
-      </c>
-      <c r="M153" s="6" t="inlineStr"/>
-    </row>
-    <row r="154" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A154" s="6" t="inlineStr"/>
-      <c r="B154" s="6" t="inlineStr"/>
-      <c r="C154" s="6" t="inlineStr"/>
-      <c r="D154" s="6" t="inlineStr"/>
-      <c r="E154" s="6" t="inlineStr"/>
-      <c r="F154" s="6" t="inlineStr"/>
-      <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="6" t="inlineStr"/>
-      <c r="I154" s="6" t="inlineStr">
-        <is>
-          <t>AURORE NAPOLITANO</t>
-        </is>
-      </c>
-      <c r="J154" s="6" t="inlineStr"/>
-      <c r="K154" s="6" t="inlineStr"/>
-      <c r="L154" s="6" t="inlineStr">
-        <is>
-          <t>aurore.napolitano@mtelogistic.com</t>
-        </is>
-      </c>
-      <c r="M154" s="6" t="inlineStr"/>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE SECTEURS EST ET NORD ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="54.6" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>LYRECO</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr"/>
+      <c r="D153" s="4" t="inlineStr"/>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>FOURNITURES DE BUREAU</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr"/>
+      <c r="G153" s="4" t="inlineStr"/>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>08 25 09 08 07</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr"/>
+      <c r="J153" s="4" t="inlineStr"/>
+      <c r="K153" s="4" t="inlineStr"/>
+      <c r="L153" s="4" t="inlineStr"/>
+      <c r="M153" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PÔLE À CONFIRMER : PRESTATION À CARACTÈRE SIÈGE / SERVICES GÉNÉRAUX ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="15.9" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>MATHIS&amp;PHILIP</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>FSMA0109</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>MATHIS &amp; PHILIP</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>VITTEL</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr"/>
+      <c r="I154" s="4" t="inlineStr"/>
+      <c r="J154" s="4" t="inlineStr"/>
+      <c r="K154" s="4" t="inlineStr"/>
+      <c r="L154" s="4" t="inlineStr"/>
+      <c r="M154" s="4" t="inlineStr"/>
     </row>
     <row r="155" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A155" s="6" t="inlineStr"/>
@@ -5580,54 +5576,54 @@
       <c r="H155" s="6" t="inlineStr"/>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>CONTACT SAV DÉPANNAGES</t>
+          <t>ISABELLE ANTOINE</t>
         </is>
       </c>
       <c r="J155" s="6" t="inlineStr"/>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>04 74 45 56 46</t>
+          <t>03 29 08 01 02</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr">
         <is>
-          <t>contact@mtelogistic.com</t>
+          <t>i.antoine@mathisetphilip.com</t>
         </is>
       </c>
       <c r="M155" s="6" t="inlineStr"/>
     </row>
-    <row r="156" outlineLevel="1" ht="41.7" customHeight="1">
-      <c r="A156" s="6" t="inlineStr"/>
-      <c r="B156" s="6" t="inlineStr"/>
-      <c r="C156" s="6" t="inlineStr"/>
-      <c r="D156" s="6" t="inlineStr"/>
-      <c r="E156" s="6" t="inlineStr"/>
-      <c r="F156" s="6" t="inlineStr">
-        <is>
-          <t>SUD OUEST</t>
-        </is>
-      </c>
-      <c r="G156" s="6" t="inlineStr">
-        <is>
-          <t>BERGERAC, CHALON 2</t>
-        </is>
-      </c>
-      <c r="H156" s="6" t="inlineStr"/>
-      <c r="I156" s="6" t="inlineStr">
-        <is>
-          <t>BOÎTE GÉNÉRIQUE (À METTRE EN COPIE SYSTÉMATIQUE ET DESTINATAIRE)</t>
-        </is>
-      </c>
-      <c r="J156" s="6" t="inlineStr"/>
-      <c r="K156" s="6" t="inlineStr"/>
-      <c r="L156" s="6" t="inlineStr">
-        <is>
-          <t>contact@mtelogistic.com</t>
-        </is>
-      </c>
-      <c r="M156" s="6" t="inlineStr"/>
-    </row>
-    <row r="157" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="156" ht="93.3" customHeight="1">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>MÉNAGE</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr"/>
+      <c r="D156" s="4" t="inlineStr"/>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>PROPRETÉ DES LOCAUX</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr"/>
+      <c r="G156" s="4" t="inlineStr"/>
+      <c r="H156" s="4" t="inlineStr"/>
+      <c r="I156" s="4" t="inlineStr"/>
+      <c r="J156" s="4" t="inlineStr"/>
+      <c r="K156" s="4" t="inlineStr"/>
+      <c r="L156" s="4" t="inlineStr"/>
+      <c r="M156" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PÔLE À CONFIRMER : PRESTATION À CARACTÈRE SIÈGE / SERVICES GÉNÉRAUX ; RAISON SOCIALE NON PRÉCISÉE : S’AGIT-IL DU CONTACT CHEZ SNP, PRESTATAIRE MÉNAGE DU SIÈGE ? À CONFIRMER ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A157" s="6" t="inlineStr"/>
       <c r="B157" s="6" t="inlineStr"/>
       <c r="C157" s="6" t="inlineStr"/>
@@ -5638,48 +5634,60 @@
       <c r="H157" s="6" t="inlineStr"/>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>CYRIELLE GENTON</t>
+          <t>ALINE</t>
         </is>
       </c>
       <c r="J157" s="6" t="inlineStr"/>
-      <c r="K157" s="6" t="inlineStr"/>
-      <c r="L157" s="6" t="inlineStr">
-        <is>
-          <t>cyrielle.genton@mtelogistic.com</t>
-        </is>
-      </c>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>06 22 70 14 37</t>
+        </is>
+      </c>
+      <c r="L157" s="6" t="inlineStr"/>
       <c r="M157" s="6" t="inlineStr"/>
     </row>
-    <row r="158" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A158" s="6" t="inlineStr"/>
-      <c r="B158" s="6" t="inlineStr"/>
-      <c r="C158" s="6" t="inlineStr"/>
-      <c r="D158" s="6" t="inlineStr"/>
-      <c r="E158" s="6" t="inlineStr"/>
-      <c r="F158" s="6" t="inlineStr"/>
-      <c r="G158" s="6" t="inlineStr"/>
-      <c r="H158" s="6" t="inlineStr"/>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>ALINE ROSSET</t>
-        </is>
-      </c>
-      <c r="J158" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANTE COMMERCIALE</t>
-        </is>
-      </c>
-      <c r="K158" s="6" t="inlineStr">
-        <is>
-          <t>04 74 45 56 46 / 06 70 65 57 43</t>
-        </is>
-      </c>
-      <c r="L158" s="6" t="inlineStr">
-        <is>
-          <t>aline.rosset@mtelogistic.com</t>
-        </is>
-      </c>
-      <c r="M158" s="6" t="inlineStr"/>
+    <row r="158" ht="67.5" customHeight="1">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>MTE LOGISTIC</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr"/>
+      <c r="D158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>RIDEAU METALLIQUE ; MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>EST ; SUD OUEST</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>CHALON 2 ; BERGERAC, CHALON 2</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>04 74 45 56 46</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr"/>
+      <c r="J158" s="4" t="inlineStr"/>
+      <c r="K158" s="4" t="inlineStr"/>
+      <c r="L158" s="4" t="inlineStr"/>
+      <c r="M158" s="4" t="inlineStr">
+        <is>
+          <t>SAISI 2 FOIS DANS LES SOURCES (« ANNUAIRE FRN CONTRATS » (RIDEAU METALLIQUE) + « ANNUAIRE FRN CONTRATS » (MAINTENANCE)) : LIGNES FUSIONNÉES, DOMAINES CUMULÉS ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
+        </is>
+      </c>
     </row>
     <row r="159" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A159" s="6" t="inlineStr"/>
@@ -5697,14 +5705,10 @@
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>DIRIGEANTE</t>
-        </is>
-      </c>
-      <c r="K159" s="6" t="inlineStr">
-        <is>
-          <t>04 74 45 56 46 / 06 48 44 91 44</t>
-        </is>
-      </c>
+          <t>MANAGER</t>
+        </is>
+      </c>
+      <c r="K159" s="6" t="inlineStr"/>
       <c r="L159" s="6" t="inlineStr">
         <is>
           <t>patricia.ramakers@mtelogistic.com</t>
@@ -5712,161 +5716,109 @@
       </c>
       <c r="M159" s="6" t="inlineStr"/>
     </row>
-    <row r="160" ht="67.5" customHeight="1">
-      <c r="A160" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B160" s="5" t="inlineStr">
-        <is>
-          <t>NETIJY</t>
-        </is>
-      </c>
-      <c r="C160" s="5" t="inlineStr"/>
-      <c r="D160" s="4" t="inlineStr"/>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>MÉNAGE</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
-        <is>
-          <t>OUEST ; SUD OUEST</t>
-        </is>
-      </c>
-      <c r="G160" s="4" t="inlineStr"/>
-      <c r="H160" s="4" t="inlineStr"/>
-      <c r="I160" s="4" t="inlineStr"/>
-      <c r="J160" s="4" t="inlineStr"/>
-      <c r="K160" s="4" t="inlineStr"/>
-      <c r="L160" s="4" t="inlineStr"/>
-      <c r="M160" s="4" t="inlineStr">
-        <is>
-          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE SECTEURS OUEST ET SUD-OUEST ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="15.9" customHeight="1">
-      <c r="A161" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B161" s="5" t="inlineStr">
-        <is>
-          <t>NISSE FRERES</t>
-        </is>
-      </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>FSNI0015</t>
-        </is>
-      </c>
-      <c r="D161" s="4" t="inlineStr">
-        <is>
-          <t>NISSE FRERES</t>
-        </is>
-      </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>CHAUFFAGISTE</t>
-        </is>
-      </c>
-      <c r="F161" s="4" t="inlineStr">
-        <is>
-          <t>EST</t>
-        </is>
-      </c>
-      <c r="G161" s="4" t="inlineStr">
-        <is>
-          <t>SARREBOURG</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr"/>
-      <c r="I161" s="4" t="inlineStr"/>
-      <c r="J161" s="4" t="inlineStr"/>
-      <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="4" t="inlineStr"/>
-      <c r="M161" s="4" t="inlineStr"/>
-    </row>
-    <row r="162" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="160" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A160" s="6" t="inlineStr"/>
+      <c r="B160" s="6" t="inlineStr"/>
+      <c r="C160" s="6" t="inlineStr"/>
+      <c r="D160" s="6" t="inlineStr"/>
+      <c r="E160" s="6" t="inlineStr"/>
+      <c r="F160" s="6" t="inlineStr"/>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr"/>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>AURORE NAPOLITANO</t>
+        </is>
+      </c>
+      <c r="J160" s="6" t="inlineStr"/>
+      <c r="K160" s="6" t="inlineStr"/>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>aurore.napolitano@mtelogistic.com</t>
+        </is>
+      </c>
+      <c r="M160" s="6" t="inlineStr"/>
+    </row>
+    <row r="161" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A161" s="6" t="inlineStr"/>
+      <c r="B161" s="6" t="inlineStr"/>
+      <c r="C161" s="6" t="inlineStr"/>
+      <c r="D161" s="6" t="inlineStr"/>
+      <c r="E161" s="6" t="inlineStr"/>
+      <c r="F161" s="6" t="inlineStr"/>
+      <c r="G161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="inlineStr"/>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>CONTACT SAV DÉPANNAGES</t>
+        </is>
+      </c>
+      <c r="J161" s="6" t="inlineStr"/>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>04 74 45 56 46</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>contact@mtelogistic.com</t>
+        </is>
+      </c>
+      <c r="M161" s="6" t="inlineStr"/>
+    </row>
+    <row r="162" outlineLevel="1" ht="41.7" customHeight="1">
       <c r="A162" s="6" t="inlineStr"/>
       <c r="B162" s="6" t="inlineStr"/>
       <c r="C162" s="6" t="inlineStr"/>
       <c r="D162" s="6" t="inlineStr"/>
       <c r="E162" s="6" t="inlineStr"/>
-      <c r="F162" s="6" t="inlineStr"/>
-      <c r="G162" s="6" t="inlineStr"/>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>SUD OUEST</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>BERGERAC, CHALON 2</t>
+        </is>
+      </c>
       <c r="H162" s="6" t="inlineStr"/>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>JEAN-BERNARD KUHL</t>
-        </is>
-      </c>
-      <c r="J162" s="6" t="inlineStr">
-        <is>
-          <t>GÉRANT</t>
-        </is>
-      </c>
-      <c r="K162" s="6" t="inlineStr">
-        <is>
-          <t>03 87 03 17 15</t>
-        </is>
-      </c>
+          <t>BOÎTE GÉNÉRIQUE (À METTRE EN COPIE SYSTÉMATIQUE ET DESTINATAIRE)</t>
+        </is>
+      </c>
+      <c r="J162" s="6" t="inlineStr"/>
+      <c r="K162" s="6" t="inlineStr"/>
       <c r="L162" s="6" t="inlineStr">
         <is>
-          <t>info@nisse.fr</t>
+          <t>contact@mtelogistic.com</t>
         </is>
       </c>
       <c r="M162" s="6" t="inlineStr"/>
     </row>
-    <row r="163" ht="41.7" customHeight="1">
-      <c r="A163" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B163" s="5" t="inlineStr">
-        <is>
-          <t>OLEA SERVICES</t>
-        </is>
-      </c>
-      <c r="C163" s="5" t="inlineStr">
-        <is>
-          <t>FSOL0006</t>
-        </is>
-      </c>
-      <c r="D163" s="4" t="inlineStr">
-        <is>
-          <t>OLEA SERVICES</t>
-        </is>
-      </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>RIDEAU METALLIQUE ; BARRIERES AUTO PARKING</t>
-        </is>
-      </c>
-      <c r="F163" s="4" t="inlineStr">
-        <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G163" s="4" t="inlineStr">
-        <is>
-          <t>MARSEILLE SÉBASTOPOL ; BOURG EN BRESSE 2</t>
-        </is>
-      </c>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>02 49 62 09 24</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr"/>
-      <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="4" t="inlineStr"/>
-      <c r="M163" s="4" t="inlineStr"/>
+    <row r="163" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A163" s="6" t="inlineStr"/>
+      <c r="B163" s="6" t="inlineStr"/>
+      <c r="C163" s="6" t="inlineStr"/>
+      <c r="D163" s="6" t="inlineStr"/>
+      <c r="E163" s="6" t="inlineStr"/>
+      <c r="F163" s="6" t="inlineStr"/>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr"/>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>CYRIELLE GENTON</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr"/>
+      <c r="K163" s="6" t="inlineStr"/>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>cyrielle.genton@mtelogistic.com</t>
+        </is>
+      </c>
+      <c r="M163" s="6" t="inlineStr"/>
     </row>
     <row r="164" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A164" s="6" t="inlineStr"/>
@@ -5879,22 +5831,22 @@
       <c r="H164" s="6" t="inlineStr"/>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>STANDARD</t>
+          <t>ALINE ROSSET</t>
         </is>
       </c>
       <c r="J164" s="6" t="inlineStr">
         <is>
-          <t>PRÉCISER SITE, LOCALISATION, SI DÉPANNAGE OU DEVIS</t>
+          <t>ASSISTANTE COMMERCIALE</t>
         </is>
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>02 49 62 09 24</t>
+          <t>04 74 45 56 46 / 06 70 65 57 43</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr">
         <is>
-          <t>oleasav@olea-services.com</t>
+          <t>aline.rosset@mtelogistic.com</t>
         </is>
       </c>
       <c r="M164" s="6" t="inlineStr"/>
@@ -5906,27 +5858,31 @@
       <c r="D165" s="6" t="inlineStr"/>
       <c r="E165" s="6" t="inlineStr"/>
       <c r="F165" s="6" t="inlineStr"/>
-      <c r="G165" s="6" t="inlineStr">
-        <is>
-          <t>BOURG EN BRESSE 2</t>
-        </is>
-      </c>
+      <c r="G165" s="6" t="inlineStr"/>
       <c r="H165" s="6" t="inlineStr"/>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>NICOLAS THEOT</t>
+          <t>PATRICIA RAMAKERS</t>
         </is>
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>RESPONSABLE SERVICE CLIENTS &amp; PARTENARIATS</t>
-        </is>
-      </c>
-      <c r="K165" s="6" t="inlineStr"/>
-      <c r="L165" s="6" t="inlineStr"/>
+          <t>DIRIGEANTE</t>
+        </is>
+      </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>04 74 45 56 46 / 06 48 44 91 44</t>
+        </is>
+      </c>
+      <c r="L165" s="6" t="inlineStr">
+        <is>
+          <t>patricia.ramakers@mtelogistic.com</t>
+        </is>
+      </c>
       <c r="M165" s="6" t="inlineStr"/>
     </row>
-    <row r="166" ht="54.6" customHeight="1">
+    <row r="166" ht="67.5" customHeight="1">
       <c r="A166" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
@@ -5934,160 +5890,184 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>OOVOOM FLEET</t>
+          <t>NETIJY</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr"/>
       <c r="D166" s="4" t="inlineStr"/>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>GESTION DE FLOTTE</t>
-        </is>
-      </c>
-      <c r="F166" s="4" t="inlineStr"/>
+          <t>MÉNAGE</t>
+        </is>
+      </c>
+      <c r="F166" s="4" t="inlineStr">
+        <is>
+          <t>OUEST ; SUD OUEST</t>
+        </is>
+      </c>
       <c r="G166" s="4" t="inlineStr"/>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>01 80 82 44 44</t>
-        </is>
-      </c>
+      <c r="H166" s="4" t="inlineStr"/>
       <c r="I166" s="4" t="inlineStr"/>
       <c r="J166" s="4" t="inlineStr"/>
       <c r="K166" s="4" t="inlineStr"/>
       <c r="L166" s="4" t="inlineStr"/>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; 59 BOULEVARD EXELMANS, 75016 PARIS ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A167" s="6" t="inlineStr"/>
-      <c r="B167" s="6" t="inlineStr"/>
-      <c r="C167" s="6" t="inlineStr"/>
-      <c r="D167" s="6" t="inlineStr"/>
-      <c r="E167" s="6" t="inlineStr"/>
-      <c r="F167" s="6" t="inlineStr"/>
-      <c r="G167" s="6" t="inlineStr"/>
-      <c r="H167" s="6" t="inlineStr"/>
-      <c r="I167" s="6" t="inlineStr">
-        <is>
-          <t>SANDRA BIBAS</t>
-        </is>
-      </c>
-      <c r="J167" s="6" t="inlineStr"/>
-      <c r="K167" s="6" t="inlineStr">
-        <is>
-          <t>06 88 39 35 03</t>
-        </is>
-      </c>
-      <c r="L167" s="6" t="inlineStr"/>
-      <c r="M167" s="6" t="inlineStr"/>
-    </row>
-    <row r="168" ht="15.9" customHeight="1">
-      <c r="A168" s="4" t="inlineStr">
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE SECTEURS OUEST ET SUD-OUEST ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="15.9" customHeight="1">
+      <c r="A167" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
         </is>
       </c>
-      <c r="B168" s="5" t="inlineStr">
-        <is>
-          <t>PELTIER EURL (GROUPE CHAM)</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>FSPE0031</t>
-        </is>
-      </c>
-      <c r="D168" s="4" t="inlineStr">
-        <is>
-          <t>PELTIER EURL</t>
-        </is>
-      </c>
-      <c r="E168" s="4" t="inlineStr">
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>NISSE FRERES</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>FSNI0015</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>NISSE FRERES</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
         <is>
           <t>CHAUFFAGISTE</t>
         </is>
       </c>
-      <c r="F168" s="4" t="inlineStr">
-        <is>
-          <t>SUD OUEST</t>
-        </is>
-      </c>
-      <c r="G168" s="4" t="inlineStr">
-        <is>
-          <t>SAINT JEAN DE LUZ</t>
-        </is>
-      </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>05 59 54 01 32</t>
-        </is>
-      </c>
-      <c r="I168" s="4" t="inlineStr"/>
-      <c r="J168" s="4" t="inlineStr"/>
-      <c r="K168" s="4" t="inlineStr"/>
-      <c r="L168" s="4" t="inlineStr"/>
-      <c r="M168" s="4" t="inlineStr"/>
-    </row>
-    <row r="169" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A169" s="6" t="inlineStr"/>
-      <c r="B169" s="6" t="inlineStr"/>
-      <c r="C169" s="6" t="inlineStr"/>
-      <c r="D169" s="6" t="inlineStr"/>
-      <c r="E169" s="6" t="inlineStr"/>
-      <c r="F169" s="6" t="inlineStr"/>
-      <c r="G169" s="6" t="inlineStr"/>
-      <c r="H169" s="6" t="inlineStr"/>
-      <c r="I169" s="6" t="inlineStr">
+      <c r="F167" s="4" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>SARREBOURG</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr"/>
+      <c r="I167" s="4" t="inlineStr"/>
+      <c r="J167" s="4" t="inlineStr"/>
+      <c r="K167" s="4" t="inlineStr"/>
+      <c r="L167" s="4" t="inlineStr"/>
+      <c r="M167" s="4" t="inlineStr"/>
+    </row>
+    <row r="168" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A168" s="6" t="inlineStr"/>
+      <c r="B168" s="6" t="inlineStr"/>
+      <c r="C168" s="6" t="inlineStr"/>
+      <c r="D168" s="6" t="inlineStr"/>
+      <c r="E168" s="6" t="inlineStr"/>
+      <c r="F168" s="6" t="inlineStr"/>
+      <c r="G168" s="6" t="inlineStr"/>
+      <c r="H168" s="6" t="inlineStr"/>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>JEAN-BERNARD KUHL</t>
+        </is>
+      </c>
+      <c r="J168" s="6" t="inlineStr">
+        <is>
+          <t>GÉRANT</t>
+        </is>
+      </c>
+      <c r="K168" s="6" t="inlineStr">
+        <is>
+          <t>03 87 03 17 15</t>
+        </is>
+      </c>
+      <c r="L168" s="6" t="inlineStr">
+        <is>
+          <t>info@nisse.fr</t>
+        </is>
+      </c>
+      <c r="M168" s="6" t="inlineStr"/>
+    </row>
+    <row r="169" ht="41.7" customHeight="1">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>OLEA SERVICES</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>FSOL0006</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>OLEA SERVICES</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>RIDEAU METALLIQUE ; BARRIERES AUTO PARKING</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>SUD EST</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>MARSEILLE SÉBASTOPOL ; BOURG EN BRESSE 2</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>02 49 62 09 24</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr"/>
+      <c r="J169" s="4" t="inlineStr"/>
+      <c r="K169" s="4" t="inlineStr"/>
+      <c r="L169" s="4" t="inlineStr"/>
+      <c r="M169" s="4" t="inlineStr"/>
+    </row>
+    <row r="170" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A170" s="6" t="inlineStr"/>
+      <c r="B170" s="6" t="inlineStr"/>
+      <c r="C170" s="6" t="inlineStr"/>
+      <c r="D170" s="6" t="inlineStr"/>
+      <c r="E170" s="6" t="inlineStr"/>
+      <c r="F170" s="6" t="inlineStr"/>
+      <c r="G170" s="6" t="inlineStr"/>
+      <c r="H170" s="6" t="inlineStr"/>
+      <c r="I170" s="6" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="J169" s="6" t="inlineStr"/>
-      <c r="K169" s="6" t="inlineStr">
-        <is>
-          <t>05 59 54 01 32</t>
-        </is>
-      </c>
-      <c r="L169" s="6" t="inlineStr">
-        <is>
-          <t>contact@peltier64.fr</t>
-        </is>
-      </c>
-      <c r="M169" s="6" t="inlineStr"/>
-    </row>
-    <row r="170" ht="54.6" customHeight="1">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B170" s="5" t="inlineStr">
-        <is>
-          <t>PÉNÉLOPE GROUPE</t>
-        </is>
-      </c>
-      <c r="C170" s="5" t="inlineStr"/>
-      <c r="D170" s="4" t="inlineStr"/>
-      <c r="E170" s="4" t="inlineStr"/>
-      <c r="F170" s="4" t="inlineStr"/>
-      <c r="G170" s="4" t="inlineStr"/>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>01 42 09 10 00</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="inlineStr"/>
-      <c r="J170" s="4" t="inlineStr"/>
-      <c r="K170" s="4" t="inlineStr"/>
-      <c r="L170" s="4" t="inlineStr"/>
-      <c r="M170" s="4" t="inlineStr">
-        <is>
-          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; 52 RUE TAITBOUT, PARIS ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; DOMAINE D’ACTIVITÉ À PRÉCISER</t>
-        </is>
-      </c>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
+          <t>PRÉCISER SITE, LOCALISATION, SI DÉPANNAGE OU DEVIS</t>
+        </is>
+      </c>
+      <c r="K170" s="6" t="inlineStr">
+        <is>
+          <t>02 49 62 09 24</t>
+        </is>
+      </c>
+      <c r="L170" s="6" t="inlineStr">
+        <is>
+          <t>oleasav@olea-services.com</t>
+        </is>
+      </c>
+      <c r="M170" s="6" t="inlineStr"/>
     </row>
     <row r="171" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A171" s="6" t="inlineStr"/>
@@ -6096,27 +6076,27 @@
       <c r="D171" s="6" t="inlineStr"/>
       <c r="E171" s="6" t="inlineStr"/>
       <c r="F171" s="6" t="inlineStr"/>
-      <c r="G171" s="6" t="inlineStr"/>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>BOURG EN BRESSE 2</t>
+        </is>
+      </c>
       <c r="H171" s="6" t="inlineStr"/>
       <c r="I171" s="6" t="inlineStr">
         <is>
-          <t>O. KOJCIC</t>
-        </is>
-      </c>
-      <c r="J171" s="6" t="inlineStr"/>
+          <t>NICOLAS THEOT</t>
+        </is>
+      </c>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
+          <t>RESPONSABLE SERVICE CLIENTS &amp; PARTENARIATS</t>
+        </is>
+      </c>
       <c r="K171" s="6" t="inlineStr"/>
-      <c r="L171" s="6" t="inlineStr">
-        <is>
-          <t>o.kojcic@penelope.fr</t>
-        </is>
-      </c>
-      <c r="M171" s="6" t="inlineStr">
-        <is>
-          <t>NOM DÉDUIT DE L'ADRESSE COURRIEL, À CONFIRMER</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="54.6" customHeight="1">
+      <c r="L171" s="6" t="inlineStr"/>
+      <c r="M171" s="6" t="inlineStr"/>
+    </row>
+    <row r="172" ht="80.40000000000001" customHeight="1">
       <c r="A172" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
@@ -6124,44 +6104,32 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>PORTALP</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="inlineStr">
-        <is>
-          <t>FSPO0011</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>PORTALP</t>
-        </is>
-      </c>
+          <t>OOVOOM FLEET</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr"/>
+      <c r="D172" s="4" t="inlineStr"/>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>PORTE AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>FRANCE</t>
-        </is>
-      </c>
-      <c r="G172" s="4" t="inlineStr">
-        <is>
-          <t>PORTE : AUBAGNE, AUXERRE / PORTE+RIDEAU : VITRY LE FRANÇOIS, CHÂTEAUBRIANT</t>
-        </is>
-      </c>
+          <t>GESTION DE FLOTTE, CONTRAVENTIONS</t>
+        </is>
+      </c>
+      <c r="F172" s="4" t="inlineStr"/>
+      <c r="G172" s="4" t="inlineStr"/>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>08 00 50 02 00</t>
+          <t>01 80 82 44 44</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr"/>
       <c r="J172" s="4" t="inlineStr"/>
       <c r="K172" s="4" t="inlineStr"/>
       <c r="L172" s="4" t="inlineStr"/>
-      <c r="M172" s="4" t="inlineStr"/>
+      <c r="M172" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PÔLE À CONFIRMER : PRESTATION À CARACTÈRE SIÈGE / SERVICES GÉNÉRAUX ; 59 BOULEVARD EXELMANS, 75016 PARIS ; ÉGALEMENT DÉSIGNÉ « OOVOOM » DANS LES ÉCHANGES ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
+        </is>
+      </c>
     </row>
     <row r="173" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A173" s="6" t="inlineStr"/>
@@ -6174,23 +6142,19 @@
       <c r="H173" s="6" t="inlineStr"/>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t>PLATEFORME</t>
+          <t>SANDRA BIBAS</t>
         </is>
       </c>
       <c r="J173" s="6" t="inlineStr"/>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>08 00 50 02 00</t>
-        </is>
-      </c>
-      <c r="L173" s="6" t="inlineStr">
-        <is>
-          <t>callcenterportalp@portalp.fr</t>
-        </is>
-      </c>
+          <t>06 88 39 35 03</t>
+        </is>
+      </c>
+      <c r="L173" s="6" t="inlineStr"/>
       <c r="M173" s="6" t="inlineStr"/>
     </row>
-    <row r="174" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="174" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A174" s="6" t="inlineStr"/>
       <c r="B174" s="6" t="inlineStr"/>
       <c r="C174" s="6" t="inlineStr"/>
@@ -6201,42 +6165,74 @@
       <c r="H174" s="6" t="inlineStr"/>
       <c r="I174" s="6" t="inlineStr">
         <is>
-          <t>SAV FRANCE</t>
+          <t>SERVICE FLOTTE AUTOMOBILE ET CONTRAVENTIONS</t>
         </is>
       </c>
       <c r="J174" s="6" t="inlineStr"/>
-      <c r="K174" s="6" t="inlineStr"/>
+      <c r="K174" s="6" t="inlineStr">
+        <is>
+          <t>01 80 82 44 43</t>
+        </is>
+      </c>
       <c r="L174" s="6" t="inlineStr">
         <is>
-          <t>sav.france@portalp.com</t>
-        </is>
-      </c>
-      <c r="M174" s="6" t="inlineStr"/>
-    </row>
-    <row r="175" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A175" s="6" t="inlineStr"/>
-      <c r="B175" s="6" t="inlineStr"/>
-      <c r="C175" s="6" t="inlineStr"/>
-      <c r="D175" s="6" t="inlineStr"/>
-      <c r="E175" s="6" t="inlineStr"/>
-      <c r="F175" s="6" t="inlineStr"/>
-      <c r="G175" s="6" t="inlineStr"/>
-      <c r="H175" s="6" t="inlineStr"/>
-      <c r="I175" s="6" t="inlineStr">
-        <is>
-          <t>AGENCE CHAMPAGNE ARDENNE (VITRY-LE-FRANÇOIS)</t>
-        </is>
-      </c>
-      <c r="J175" s="6" t="inlineStr"/>
-      <c r="K175" s="6" t="inlineStr">
-        <is>
-          <t>03 26 97 25 40</t>
-        </is>
-      </c>
-      <c r="L175" s="6" t="inlineStr"/>
-      <c r="M175" s="6" t="inlineStr"/>
-    </row>
-    <row r="176" outlineLevel="1" ht="28.8" customHeight="1">
+          <t>auddika@oovoom.fr</t>
+        </is>
+      </c>
+      <c r="M174" s="6" t="inlineStr">
+        <is>
+          <t>ADRESSE SAISIE « AUDDIKA@ » AVEC DEUX D, À CONFIRMER</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="15.9" customHeight="1">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>PELTIER EURL (GROUPE CHAM)</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>FSPE0031</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>PELTIER EURL</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F175" s="4" t="inlineStr">
+        <is>
+          <t>SUD OUEST</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>SAINT JEAN DE LUZ</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>05 59 54 01 32</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr"/>
+      <c r="J175" s="4" t="inlineStr"/>
+      <c r="K175" s="4" t="inlineStr"/>
+      <c r="L175" s="4" t="inlineStr"/>
+      <c r="M175" s="4" t="inlineStr"/>
+    </row>
+    <row r="176" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A176" s="6" t="inlineStr"/>
       <c r="B176" s="6" t="inlineStr"/>
       <c r="C176" s="6" t="inlineStr"/>
@@ -6247,58 +6243,54 @@
       <c r="H176" s="6" t="inlineStr"/>
       <c r="I176" s="6" t="inlineStr">
         <is>
-          <t>EMILIE BEGHIN</t>
-        </is>
-      </c>
-      <c r="J176" s="6" t="inlineStr">
-        <is>
-          <t>CHARGÉE D'AFFAIRES CHAMPAGNE ARDENNES</t>
-        </is>
-      </c>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="J176" s="6" t="inlineStr"/>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>06 58 06 94 73</t>
+          <t>05 59 54 01 32</t>
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr">
         <is>
-          <t>e.beghin@portalp.com</t>
+          <t>contact@peltier64.fr</t>
         </is>
       </c>
       <c r="M176" s="6" t="inlineStr"/>
     </row>
-    <row r="177" outlineLevel="1" ht="41.7" customHeight="1">
-      <c r="A177" s="6" t="inlineStr"/>
-      <c r="B177" s="6" t="inlineStr"/>
-      <c r="C177" s="6" t="inlineStr"/>
-      <c r="D177" s="6" t="inlineStr"/>
-      <c r="E177" s="6" t="inlineStr"/>
-      <c r="F177" s="6" t="inlineStr"/>
-      <c r="G177" s="6" t="inlineStr"/>
-      <c r="H177" s="6" t="inlineStr"/>
-      <c r="I177" s="6" t="inlineStr">
-        <is>
-          <t>HÉLÈNE SERRE (AGENCE À AZAY LE BRULE 79, CTRE CHÂTEAUBRIANT)</t>
-        </is>
-      </c>
-      <c r="J177" s="6" t="inlineStr">
-        <is>
-          <t>CHARGÉE DE CLIENTÈLE</t>
-        </is>
-      </c>
-      <c r="K177" s="6" t="inlineStr">
-        <is>
-          <t>05 49 77 59 07 / 07 63 63 66 53</t>
-        </is>
-      </c>
-      <c r="L177" s="6" t="inlineStr">
-        <is>
-          <t>hserre@portalp.com</t>
-        </is>
-      </c>
-      <c r="M177" s="6" t="inlineStr"/>
-    </row>
-    <row r="178" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="177" ht="80.40000000000001" customHeight="1">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>PÉNÉLOPE GROUPE</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr"/>
+      <c r="D177" s="4" t="inlineStr"/>
+      <c r="E177" s="4" t="inlineStr"/>
+      <c r="F177" s="4" t="inlineStr"/>
+      <c r="G177" s="4" t="inlineStr"/>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>01 42 09 10 00</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr"/>
+      <c r="J177" s="4" t="inlineStr"/>
+      <c r="K177" s="4" t="inlineStr"/>
+      <c r="L177" s="4" t="inlineStr"/>
+      <c r="M177" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PÔLE À CONFIRMER : PRESTATION À CARACTÈRE SIÈGE / SERVICES GÉNÉRAUX ; 52 RUE TAITBOUT, PARIS ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; DOMAINE D’ACTIVITÉ À PRÉCISER</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A178" s="6" t="inlineStr"/>
       <c r="B178" s="6" t="inlineStr"/>
       <c r="C178" s="6" t="inlineStr"/>
@@ -6309,19 +6301,27 @@
       <c r="H178" s="6" t="inlineStr"/>
       <c r="I178" s="6" t="inlineStr">
         <is>
-          <t>AGENCE BORDEAUX (BAYONNE ST ESPRIT)</t>
-        </is>
-      </c>
-      <c r="J178" s="6" t="inlineStr"/>
+          <t>RAJA HELLARA</t>
+        </is>
+      </c>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
+          <t>DIRECTRICE RÉGIONALE</t>
+        </is>
+      </c>
       <c r="K178" s="6" t="inlineStr">
         <is>
-          <t>05 56 13 47 41</t>
-        </is>
-      </c>
-      <c r="L178" s="6" t="inlineStr"/>
+          <t>06 33 37 23 65</t>
+        </is>
+      </c>
+      <c r="L178" s="6" t="inlineStr">
+        <is>
+          <t>r.hellara@penelope.fr</t>
+        </is>
+      </c>
       <c r="M178" s="6" t="inlineStr"/>
     </row>
-    <row r="179" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="179" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A179" s="6" t="inlineStr"/>
       <c r="B179" s="6" t="inlineStr"/>
       <c r="C179" s="6" t="inlineStr"/>
@@ -6332,22 +6332,22 @@
       <c r="H179" s="6" t="inlineStr"/>
       <c r="I179" s="6" t="inlineStr">
         <is>
-          <t>SANDRA BRUNETEAU (BAYONNE ST ESPRIT)</t>
+          <t>OLIVERA KOJCIC</t>
         </is>
       </c>
       <c r="J179" s="6" t="inlineStr">
         <is>
-          <t>CHARGÉE DE CLIENTÈLE (AGENCE BORDEAUX MÉRIGNAC)</t>
+          <t>RESPONSABLE D’AGENCE</t>
         </is>
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>05 56 13 47 46 / 06 68 96 54 40</t>
+          <t>06 83 82 70 78</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr">
         <is>
-          <t>sbruneteau@portalp.com</t>
+          <t>o.kojcic@penelope.fr</t>
         </is>
       </c>
       <c r="M179" s="6" t="inlineStr"/>
@@ -6363,95 +6363,103 @@
       <c r="H180" s="6" t="inlineStr"/>
       <c r="I180" s="6" t="inlineStr">
         <is>
-          <t>ANTOINE ZEUD</t>
+          <t>SARAH BENKHALIFA</t>
         </is>
       </c>
       <c r="J180" s="6" t="inlineStr">
         <is>
-          <t>CHARGÉ D'AFFAIRES BORDEAUX</t>
+          <t>RESPONSABLE PLANNING</t>
         </is>
       </c>
       <c r="K180" s="6" t="inlineStr">
         <is>
-          <t>06 66 33 41 58</t>
-        </is>
-      </c>
-      <c r="L180" s="6" t="inlineStr"/>
+          <t>06 02 04 51 05</t>
+        </is>
+      </c>
+      <c r="L180" s="6" t="inlineStr">
+        <is>
+          <t>s.benkhalifa@penelope.fr</t>
+        </is>
+      </c>
       <c r="M180" s="6" t="inlineStr"/>
     </row>
-    <row r="181" ht="15.9" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
+    <row r="181" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A181" s="6" t="inlineStr"/>
+      <c r="B181" s="6" t="inlineStr"/>
+      <c r="C181" s="6" t="inlineStr"/>
+      <c r="D181" s="6" t="inlineStr"/>
+      <c r="E181" s="6" t="inlineStr"/>
+      <c r="F181" s="6" t="inlineStr"/>
+      <c r="G181" s="6" t="inlineStr"/>
+      <c r="H181" s="6" t="inlineStr"/>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>SVETLANA CAUTIK</t>
+        </is>
+      </c>
+      <c r="J181" s="6" t="inlineStr">
+        <is>
+          <t>RESPONSABLE CONTRÔLE QUALITÉ</t>
+        </is>
+      </c>
+      <c r="K181" s="6" t="inlineStr">
+        <is>
+          <t>06 88 08 82 22</t>
+        </is>
+      </c>
+      <c r="L181" s="6" t="inlineStr">
+        <is>
+          <t>s.cautik@penelope.fr</t>
+        </is>
+      </c>
+      <c r="M181" s="6" t="inlineStr"/>
+    </row>
+    <row r="182" ht="54.6" customHeight="1">
+      <c r="A182" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
         </is>
       </c>
-      <c r="B181" s="5" t="inlineStr">
-        <is>
-          <t>PROXI GAZ ABITIBI</t>
-        </is>
-      </c>
-      <c r="C181" s="5" t="inlineStr">
-        <is>
-          <t>FSPR0042</t>
-        </is>
-      </c>
-      <c r="D181" s="4" t="inlineStr">
-        <is>
-          <t>PROXI GAZ SERVICE</t>
-        </is>
-      </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>CHAUFFAGISTE</t>
-        </is>
-      </c>
-      <c r="F181" s="4" t="inlineStr">
-        <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G181" s="4" t="inlineStr">
-        <is>
-          <t>LYON VENDÔME</t>
-        </is>
-      </c>
-      <c r="H181" s="4" t="inlineStr">
-        <is>
-          <t>04 78 17 20 13</t>
-        </is>
-      </c>
-      <c r="I181" s="4" t="inlineStr"/>
-      <c r="J181" s="4" t="inlineStr"/>
-      <c r="K181" s="4" t="inlineStr"/>
-      <c r="L181" s="4" t="inlineStr"/>
-      <c r="M181" s="4" t="inlineStr"/>
-    </row>
-    <row r="182" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A182" s="6" t="inlineStr"/>
-      <c r="B182" s="6" t="inlineStr"/>
-      <c r="C182" s="6" t="inlineStr"/>
-      <c r="D182" s="6" t="inlineStr"/>
-      <c r="E182" s="6" t="inlineStr"/>
-      <c r="F182" s="6" t="inlineStr"/>
-      <c r="G182" s="6" t="inlineStr"/>
-      <c r="H182" s="6" t="inlineStr"/>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="J182" s="6" t="inlineStr"/>
-      <c r="K182" s="6" t="inlineStr">
-        <is>
-          <t>04 78 17 20 13</t>
-        </is>
-      </c>
-      <c r="L182" s="6" t="inlineStr">
-        <is>
-          <t>contact@proxigazservice.fr</t>
-        </is>
-      </c>
-      <c r="M182" s="6" t="inlineStr"/>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>PORTALP</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>FSPO0011</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>PORTALP</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>PORTE AUTOMATIQUE</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>FRANCE</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>PORTE : AUBAGNE, AUXERRE / PORTE+RIDEAU : VITRY LE FRANÇOIS, CHÂTEAUBRIANT</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>08 00 50 02 00</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr"/>
+      <c r="J182" s="4" t="inlineStr"/>
+      <c r="K182" s="4" t="inlineStr"/>
+      <c r="L182" s="4" t="inlineStr"/>
+      <c r="M182" s="4" t="inlineStr"/>
     </row>
     <row r="183" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A183" s="6" t="inlineStr"/>
@@ -6464,70 +6472,46 @@
       <c r="H183" s="6" t="inlineStr"/>
       <c r="I183" s="6" t="inlineStr">
         <is>
-          <t>NATHALIE</t>
-        </is>
-      </c>
-      <c r="J183" s="6" t="inlineStr">
-        <is>
-          <t>SAV ABITIBI</t>
-        </is>
-      </c>
+          <t>PLATEFORME</t>
+        </is>
+      </c>
+      <c r="J183" s="6" t="inlineStr"/>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>04 78 37 42 72</t>
+          <t>08 00 50 02 00</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr">
         <is>
-          <t>sav@abitibi.fr</t>
+          <t>callcenterportalp@portalp.fr</t>
         </is>
       </c>
       <c r="M183" s="6" t="inlineStr"/>
     </row>
-    <row r="184" ht="15.9" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
-        <is>
-          <t>RATAUD ASSAINISSEMENT</t>
-        </is>
-      </c>
-      <c r="C184" s="5" t="inlineStr">
-        <is>
-          <t>V000112</t>
-        </is>
-      </c>
-      <c r="D184" s="4" t="inlineStr">
-        <is>
-          <t>ASSAINISSEMENTS RATAUD</t>
-        </is>
-      </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>CANALISATIONS EU</t>
-        </is>
-      </c>
-      <c r="F184" s="4" t="inlineStr">
-        <is>
-          <t>OUEST</t>
-        </is>
-      </c>
-      <c r="G184" s="4" t="inlineStr">
-        <is>
-          <t>ST GILLES CROIX DE VIE</t>
-        </is>
-      </c>
-      <c r="H184" s="4" t="inlineStr"/>
-      <c r="I184" s="4" t="inlineStr"/>
-      <c r="J184" s="4" t="inlineStr"/>
-      <c r="K184" s="4" t="inlineStr"/>
-      <c r="L184" s="4" t="inlineStr"/>
-      <c r="M184" s="4" t="inlineStr"/>
-    </row>
-    <row r="185" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="184" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A184" s="6" t="inlineStr"/>
+      <c r="B184" s="6" t="inlineStr"/>
+      <c r="C184" s="6" t="inlineStr"/>
+      <c r="D184" s="6" t="inlineStr"/>
+      <c r="E184" s="6" t="inlineStr"/>
+      <c r="F184" s="6" t="inlineStr"/>
+      <c r="G184" s="6" t="inlineStr"/>
+      <c r="H184" s="6" t="inlineStr"/>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>SAV FRANCE</t>
+        </is>
+      </c>
+      <c r="J184" s="6" t="inlineStr"/>
+      <c r="K184" s="6" t="inlineStr"/>
+      <c r="L184" s="6" t="inlineStr">
+        <is>
+          <t>sav.france@portalp.com</t>
+        </is>
+      </c>
+      <c r="M184" s="6" t="inlineStr"/>
+    </row>
+    <row r="185" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A185" s="6" t="inlineStr"/>
       <c r="B185" s="6" t="inlineStr"/>
       <c r="C185" s="6" t="inlineStr"/>
@@ -6538,70 +6522,50 @@
       <c r="H185" s="6" t="inlineStr"/>
       <c r="I185" s="6" t="inlineStr">
         <is>
-          <t>JULIE RATAUD</t>
+          <t>AGENCE CHAMPAGNE ARDENNE (VITRY-LE-FRANÇOIS)</t>
         </is>
       </c>
       <c r="J185" s="6" t="inlineStr"/>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>02 51 55 86 44</t>
-        </is>
-      </c>
-      <c r="L185" s="6" t="inlineStr">
-        <is>
-          <t>sarlrataud@gmail.com</t>
-        </is>
-      </c>
+          <t>03 26 97 25 40</t>
+        </is>
+      </c>
+      <c r="L185" s="6" t="inlineStr"/>
       <c r="M185" s="6" t="inlineStr"/>
     </row>
-    <row r="186" ht="41.7" customHeight="1">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
-        <is>
-          <t>RECORD</t>
-        </is>
-      </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>FSRE0051</t>
-        </is>
-      </c>
-      <c r="D186" s="4" t="inlineStr">
-        <is>
-          <t>RECORD PORTES AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>PORTE AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>BRIEY, BRON, CHALON2, CLAMECY, JONZAC, ST RÉMY, VALENCIENNES LUÇON</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr">
-        <is>
-          <t>08 09 10 01 22</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="inlineStr"/>
-      <c r="J186" s="4" t="inlineStr"/>
-      <c r="K186" s="4" t="inlineStr"/>
-      <c r="L186" s="4" t="inlineStr"/>
-      <c r="M186" s="4" t="inlineStr"/>
-    </row>
-    <row r="187" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="186" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A186" s="6" t="inlineStr"/>
+      <c r="B186" s="6" t="inlineStr"/>
+      <c r="C186" s="6" t="inlineStr"/>
+      <c r="D186" s="6" t="inlineStr"/>
+      <c r="E186" s="6" t="inlineStr"/>
+      <c r="F186" s="6" t="inlineStr"/>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr"/>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>EMILIE BEGHIN</t>
+        </is>
+      </c>
+      <c r="J186" s="6" t="inlineStr">
+        <is>
+          <t>CHARGÉE D'AFFAIRES CHAMPAGNE ARDENNES</t>
+        </is>
+      </c>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t>06 58 06 94 73</t>
+        </is>
+      </c>
+      <c r="L186" s="6" t="inlineStr">
+        <is>
+          <t>e.beghin@portalp.com</t>
+        </is>
+      </c>
+      <c r="M186" s="6" t="inlineStr"/>
+    </row>
+    <row r="187" outlineLevel="1" ht="41.7" customHeight="1">
       <c r="A187" s="6" t="inlineStr"/>
       <c r="B187" s="6" t="inlineStr"/>
       <c r="C187" s="6" t="inlineStr"/>
@@ -6612,22 +6576,22 @@
       <c r="H187" s="6" t="inlineStr"/>
       <c r="I187" s="6" t="inlineStr">
         <is>
-          <t>SERVICE FRONT OFFICE</t>
+          <t>HÉLÈNE SERRE (AGENCE À AZAY LE BRULE 79, CTRE CHÂTEAUBRIANT)</t>
         </is>
       </c>
       <c r="J187" s="6" t="inlineStr">
         <is>
-          <t>RENSEIGNEMENT VISITES D'ENTRETIEN ET DÉPANNAGES</t>
+          <t>CHARGÉE DE CLIENTÈLE</t>
         </is>
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>08 09 10 01 22</t>
+          <t>05 49 77 59 07 / 07 63 63 66 53</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr">
         <is>
-          <t>maintenance.sudest@record.fr</t>
+          <t>hserre@portalp.com</t>
         </is>
       </c>
       <c r="M187" s="6" t="inlineStr"/>
@@ -6643,24 +6607,16 @@
       <c r="H188" s="6" t="inlineStr"/>
       <c r="I188" s="6" t="inlineStr">
         <is>
-          <t>SERVICE BACK OFFICE</t>
-        </is>
-      </c>
-      <c r="J188" s="6" t="inlineStr">
-        <is>
-          <t>QUESTIONS FACTURATION, DEVIS, CONTRAT</t>
-        </is>
-      </c>
+          <t>AGENCE BORDEAUX (BAYONNE ST ESPRIT)</t>
+        </is>
+      </c>
+      <c r="J188" s="6" t="inlineStr"/>
       <c r="K188" s="6" t="inlineStr">
         <is>
-          <t>09 79 98 08 60</t>
-        </is>
-      </c>
-      <c r="L188" s="6" t="inlineStr">
-        <is>
-          <t>maintenance.sudest@record.fr</t>
-        </is>
-      </c>
+          <t>05 56 13 47 41</t>
+        </is>
+      </c>
+      <c r="L188" s="6" t="inlineStr"/>
       <c r="M188" s="6" t="inlineStr"/>
     </row>
     <row r="189" outlineLevel="1" ht="28.8" customHeight="1">
@@ -6674,22 +6630,22 @@
       <c r="H189" s="6" t="inlineStr"/>
       <c r="I189" s="6" t="inlineStr">
         <is>
-          <t>PÔLE CONTRATS SUD EST</t>
+          <t>SANDRA BRUNETEAU (BAYONNE ST ESPRIT)</t>
         </is>
       </c>
       <c r="J189" s="6" t="inlineStr">
         <is>
-          <t>CONTRATS</t>
+          <t>CHARGÉE DE CLIENTÈLE (AGENCE BORDEAUX MÉRIGNAC)</t>
         </is>
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>04 79 52 09 73</t>
+          <t>05 56 13 47 46 / 06 68 96 54 40</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr">
         <is>
-          <t>contrats.maintenance.sudest@record.fr</t>
+          <t>sbruneteau@portalp.com</t>
         </is>
       </c>
       <c r="M189" s="6" t="inlineStr"/>
@@ -6705,54 +6661,54 @@
       <c r="H190" s="6" t="inlineStr"/>
       <c r="I190" s="6" t="inlineStr">
         <is>
-          <t>FLORENT RIVAILLIER</t>
+          <t>ANTOINE ZEUD</t>
         </is>
       </c>
       <c r="J190" s="6" t="inlineStr">
         <is>
-          <t>INTERLOCUTEUR CONTRAT CLAMECY</t>
+          <t>CHARGÉ D'AFFAIRES BORDEAUX</t>
         </is>
       </c>
       <c r="K190" s="6" t="inlineStr">
         <is>
-          <t>09 79 98 08 60</t>
-        </is>
-      </c>
-      <c r="L190" s="6" t="inlineStr">
-        <is>
-          <t>maintenance.sudest@record.fr</t>
-        </is>
-      </c>
+          <t>06 66 33 41 58</t>
+        </is>
+      </c>
+      <c r="L190" s="6" t="inlineStr"/>
       <c r="M190" s="6" t="inlineStr"/>
     </row>
-    <row r="191" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A191" s="6" t="inlineStr"/>
-      <c r="B191" s="6" t="inlineStr"/>
-      <c r="C191" s="6" t="inlineStr"/>
-      <c r="D191" s="6" t="inlineStr"/>
-      <c r="E191" s="6" t="inlineStr"/>
-      <c r="F191" s="6" t="inlineStr"/>
-      <c r="G191" s="6" t="inlineStr"/>
-      <c r="H191" s="6" t="inlineStr"/>
-      <c r="I191" s="6" t="inlineStr">
-        <is>
-          <t>ISABELLE VALLET</t>
-        </is>
-      </c>
-      <c r="J191" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANTE MAINTENANCE (BRON)</t>
-        </is>
-      </c>
-      <c r="K191" s="6" t="inlineStr">
-        <is>
-          <t>09 79 98 09 93</t>
-        </is>
-      </c>
-      <c r="L191" s="6" t="inlineStr"/>
-      <c r="M191" s="6" t="inlineStr"/>
-    </row>
-    <row r="192" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="191" ht="67.5" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>PRODITION</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr"/>
+      <c r="D191" s="4" t="inlineStr"/>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>LOGISTIQUE</t>
+        </is>
+      </c>
+      <c r="F191" s="4" t="inlineStr"/>
+      <c r="G191" s="4" t="inlineStr"/>
+      <c r="H191" s="4" t="inlineStr"/>
+      <c r="I191" s="4" t="inlineStr"/>
+      <c r="J191" s="4" t="inlineStr"/>
+      <c r="K191" s="4" t="inlineStr"/>
+      <c r="L191" s="4" t="inlineStr"/>
+      <c r="M191" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PÔLE À CONFIRMER : PRESTATION À CARACTÈRE SIÈGE / SERVICES GÉNÉRAUX ; CENTRE LOGISTIQUE AUDIKA ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A192" s="6" t="inlineStr"/>
       <c r="B192" s="6" t="inlineStr"/>
       <c r="C192" s="6" t="inlineStr"/>
@@ -6763,54 +6719,66 @@
       <c r="H192" s="6" t="inlineStr"/>
       <c r="I192" s="6" t="inlineStr">
         <is>
-          <t>JULIETTE BOURBON</t>
-        </is>
-      </c>
-      <c r="J192" s="6" t="inlineStr">
-        <is>
-          <t>COMMERCIALE SÉDENTAIRE MAINTENANCE SUD-EST</t>
-        </is>
-      </c>
+          <t>VERONIQUE</t>
+        </is>
+      </c>
+      <c r="J192" s="6" t="inlineStr"/>
       <c r="K192" s="6" t="inlineStr">
         <is>
-          <t>04 79 52 09 76</t>
-        </is>
-      </c>
-      <c r="L192" s="6" t="inlineStr">
-        <is>
-          <t>juliette.bourbon@record.fr</t>
-        </is>
-      </c>
+          <t>01 41 27 28 66</t>
+        </is>
+      </c>
+      <c r="L192" s="6" t="inlineStr"/>
       <c r="M192" s="6" t="inlineStr"/>
     </row>
-    <row r="193" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A193" s="6" t="inlineStr"/>
-      <c r="B193" s="6" t="inlineStr"/>
-      <c r="C193" s="6" t="inlineStr"/>
-      <c r="D193" s="6" t="inlineStr"/>
-      <c r="E193" s="6" t="inlineStr"/>
-      <c r="F193" s="6" t="inlineStr"/>
-      <c r="G193" s="6" t="inlineStr"/>
-      <c r="H193" s="6" t="inlineStr"/>
-      <c r="I193" s="6" t="inlineStr">
-        <is>
-          <t>MAINTENANCE OUEST</t>
-        </is>
-      </c>
-      <c r="J193" s="6" t="inlineStr"/>
-      <c r="K193" s="6" t="inlineStr">
-        <is>
-          <t>08 09 10 01 22</t>
-        </is>
-      </c>
-      <c r="L193" s="6" t="inlineStr">
-        <is>
-          <t>maintenance.ouest@record.fr</t>
-        </is>
-      </c>
-      <c r="M193" s="6" t="inlineStr"/>
-    </row>
-    <row r="194" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="193" ht="15.9" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>PROXI GAZ ABITIBI</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>FSPR0042</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>PROXI GAZ SERVICE</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F193" s="4" t="inlineStr">
+        <is>
+          <t>SUD EST</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr">
+        <is>
+          <t>LYON VENDÔME</t>
+        </is>
+      </c>
+      <c r="H193" s="4" t="inlineStr">
+        <is>
+          <t>04 78 17 20 13</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="inlineStr"/>
+      <c r="J193" s="4" t="inlineStr"/>
+      <c r="K193" s="4" t="inlineStr"/>
+      <c r="L193" s="4" t="inlineStr"/>
+      <c r="M193" s="4" t="inlineStr"/>
+    </row>
+    <row r="194" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A194" s="6" t="inlineStr"/>
       <c r="B194" s="6" t="inlineStr"/>
       <c r="C194" s="6" t="inlineStr"/>
@@ -6821,19 +6789,23 @@
       <c r="H194" s="6" t="inlineStr"/>
       <c r="I194" s="6" t="inlineStr">
         <is>
-          <t>PÔLE CONTRATS OUEST</t>
+          <t>STANDARD</t>
         </is>
       </c>
       <c r="J194" s="6" t="inlineStr"/>
-      <c r="K194" s="6" t="inlineStr"/>
+      <c r="K194" s="6" t="inlineStr">
+        <is>
+          <t>04 78 17 20 13</t>
+        </is>
+      </c>
       <c r="L194" s="6" t="inlineStr">
         <is>
-          <t>contrats.maintenanceouest@record.fr</t>
+          <t>contact@proxigazservice.fr</t>
         </is>
       </c>
       <c r="M194" s="6" t="inlineStr"/>
     </row>
-    <row r="195" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="195" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A195" s="6" t="inlineStr"/>
       <c r="B195" s="6" t="inlineStr"/>
       <c r="C195" s="6" t="inlineStr"/>
@@ -6844,22 +6816,22 @@
       <c r="H195" s="6" t="inlineStr"/>
       <c r="I195" s="6" t="inlineStr">
         <is>
-          <t>AURÉLIE GUIRCHOUN</t>
+          <t>NATHALIE</t>
         </is>
       </c>
       <c r="J195" s="6" t="inlineStr">
         <is>
-          <t>COMMERCIALE SÉDENTAIRE MAINTENANCE OUEST</t>
+          <t>SAV ABITIBI</t>
         </is>
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>09 79 98 08 74</t>
+          <t>04 78 37 42 72</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr">
         <is>
-          <t>aurelie.guirchoun@record.fr</t>
+          <t>sav@abitibi.fr</t>
         </is>
       </c>
       <c r="M195" s="6" t="inlineStr"/>
@@ -6872,28 +6844,32 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>REMI GIRARD</t>
+          <t>RATAUD ASSAINISSEMENT</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>FSRE0151</t>
+          <t>V000112</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>REMI GIRARD</t>
+          <t>ASSAINISSEMENTS RATAUD</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>NUISIBLES</t>
-        </is>
-      </c>
-      <c r="F196" s="4" t="inlineStr"/>
+          <t>CANALISATIONS EU</t>
+        </is>
+      </c>
+      <c r="F196" s="4" t="inlineStr">
+        <is>
+          <t>OUEST</t>
+        </is>
+      </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>CHAMPAGNOLE</t>
+          <t>ST GILLES CROIX DE VIE</t>
         </is>
       </c>
       <c r="H196" s="4" t="inlineStr"/>
@@ -6914,23 +6890,23 @@
       <c r="H197" s="6" t="inlineStr"/>
       <c r="I197" s="6" t="inlineStr">
         <is>
-          <t>RÉMI GIRARD</t>
+          <t>JULIE RATAUD</t>
         </is>
       </c>
       <c r="J197" s="6" t="inlineStr"/>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>06 02 23 02 87</t>
+          <t>02 51 55 86 44</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr">
         <is>
-          <t>rem14117@gmail.com</t>
+          <t>sarlrataud@gmail.com</t>
         </is>
       </c>
       <c r="M197" s="6" t="inlineStr"/>
     </row>
-    <row r="198" ht="28.8" customHeight="1">
+    <row r="198" ht="41.7" customHeight="1">
       <c r="A198" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
@@ -6938,37 +6914,37 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>SCARAVELLI &amp; FILS, INZA GROUPE</t>
+          <t>RECORD</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>FSSC0096</t>
+          <t>FSRE0051</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>SCARAVELLI ET FILS</t>
+          <t>RECORD PORTES AUTOMATIQUE</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>CHAUFFAGISTE</t>
+          <t>PORTE AUTOMATIQUE</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>SUD OUEST</t>
+          <t>SUD EST</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>NÉRAC</t>
+          <t>BRIEY, BRON, CHALON2, CLAMECY, JONZAC, ST RÉMY, VALENCIENNES LUÇON</t>
         </is>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
-          <t>06 12 13 28 85</t>
+          <t>08 09 10 01 22</t>
         </is>
       </c>
       <c r="I198" s="4" t="inlineStr"/>
@@ -6988,105 +6964,89 @@
       <c r="H199" s="6" t="inlineStr"/>
       <c r="I199" s="6" t="inlineStr">
         <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="J199" s="6" t="inlineStr"/>
+          <t>SERVICE FRONT OFFICE</t>
+        </is>
+      </c>
+      <c r="J199" s="6" t="inlineStr">
+        <is>
+          <t>RENSEIGNEMENT VISITES D'ENTRETIEN ET DÉPANNAGES</t>
+        </is>
+      </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>06 12 13 28 85</t>
+          <t>08 09 10 01 22</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr">
         <is>
-          <t>scaravelli.chauffagiste@orange.fr</t>
+          <t>maintenance.sudest@record.fr</t>
         </is>
       </c>
       <c r="M199" s="6" t="inlineStr"/>
     </row>
-    <row r="200" ht="54.6" customHeight="1">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>SIÈGE</t>
-        </is>
-      </c>
-      <c r="B200" s="5" t="inlineStr">
-        <is>
-          <t>SNP</t>
-        </is>
-      </c>
-      <c r="C200" s="5" t="inlineStr"/>
-      <c r="D200" s="4" t="inlineStr"/>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>MÉNAGE</t>
-        </is>
-      </c>
-      <c r="F200" s="4" t="inlineStr"/>
-      <c r="G200" s="4" t="inlineStr">
-        <is>
-          <t>SIÈGE</t>
-        </is>
-      </c>
-      <c r="H200" s="4" t="inlineStr"/>
-      <c r="I200" s="4" t="inlineStr"/>
-      <c r="J200" s="4" t="inlineStr"/>
-      <c r="K200" s="4" t="inlineStr"/>
-      <c r="L200" s="4" t="inlineStr"/>
-      <c r="M200" s="4" t="inlineStr">
-        <is>
-          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE DU SIÈGE ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="28.8" customHeight="1">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B201" s="5" t="inlineStr">
-        <is>
-          <t>SOCIETE NOUVELLE H. CONRAUX</t>
-        </is>
-      </c>
-      <c r="C201" s="5" t="inlineStr">
-        <is>
-          <t>FSCO0034</t>
-        </is>
-      </c>
-      <c r="D201" s="4" t="inlineStr">
-        <is>
-          <t>CONRAUX H SAS</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>CHAUFFAGISTE</t>
-        </is>
-      </c>
-      <c r="F201" s="4" t="inlineStr">
-        <is>
-          <t>EST</t>
-        </is>
-      </c>
-      <c r="G201" s="4" t="inlineStr">
-        <is>
-          <t>REIMS PARIS</t>
-        </is>
-      </c>
-      <c r="H201" s="4" t="inlineStr">
-        <is>
-          <t>03 26 65 40 40</t>
-        </is>
-      </c>
-      <c r="I201" s="4" t="inlineStr"/>
-      <c r="J201" s="4" t="inlineStr"/>
-      <c r="K201" s="4" t="inlineStr"/>
-      <c r="L201" s="4" t="inlineStr"/>
-      <c r="M201" s="4" t="inlineStr"/>
-    </row>
-    <row r="202" outlineLevel="1" ht="41.7" customHeight="1">
+    <row r="200" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A200" s="6" t="inlineStr"/>
+      <c r="B200" s="6" t="inlineStr"/>
+      <c r="C200" s="6" t="inlineStr"/>
+      <c r="D200" s="6" t="inlineStr"/>
+      <c r="E200" s="6" t="inlineStr"/>
+      <c r="F200" s="6" t="inlineStr"/>
+      <c r="G200" s="6" t="inlineStr"/>
+      <c r="H200" s="6" t="inlineStr"/>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>SERVICE BACK OFFICE</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="inlineStr">
+        <is>
+          <t>QUESTIONS FACTURATION, DEVIS, CONTRAT</t>
+        </is>
+      </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t>09 79 98 08 60</t>
+        </is>
+      </c>
+      <c r="L200" s="6" t="inlineStr">
+        <is>
+          <t>maintenance.sudest@record.fr</t>
+        </is>
+      </c>
+      <c r="M200" s="6" t="inlineStr"/>
+    </row>
+    <row r="201" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A201" s="6" t="inlineStr"/>
+      <c r="B201" s="6" t="inlineStr"/>
+      <c r="C201" s="6" t="inlineStr"/>
+      <c r="D201" s="6" t="inlineStr"/>
+      <c r="E201" s="6" t="inlineStr"/>
+      <c r="F201" s="6" t="inlineStr"/>
+      <c r="G201" s="6" t="inlineStr"/>
+      <c r="H201" s="6" t="inlineStr"/>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>PÔLE CONTRATS SUD EST</t>
+        </is>
+      </c>
+      <c r="J201" s="6" t="inlineStr">
+        <is>
+          <t>CONTRATS</t>
+        </is>
+      </c>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>04 79 52 09 73</t>
+        </is>
+      </c>
+      <c r="L201" s="6" t="inlineStr">
+        <is>
+          <t>contrats.maintenance.sudest@record.fr</t>
+        </is>
+      </c>
+      <c r="M201" s="6" t="inlineStr"/>
+    </row>
+    <row r="202" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A202" s="6" t="inlineStr"/>
       <c r="B202" s="6" t="inlineStr"/>
       <c r="C202" s="6" t="inlineStr"/>
@@ -7097,25 +7057,25 @@
       <c r="H202" s="6" t="inlineStr"/>
       <c r="I202" s="6" t="inlineStr">
         <is>
-          <t>SAV</t>
-        </is>
-      </c>
-      <c r="J202" s="6" t="inlineStr"/>
+          <t>FLORENT RIVAILLIER</t>
+        </is>
+      </c>
+      <c r="J202" s="6" t="inlineStr">
+        <is>
+          <t>INTERLOCUTEUR CONTRAT CLAMECY</t>
+        </is>
+      </c>
       <c r="K202" s="6" t="inlineStr">
         <is>
-          <t>03 26 65 40 40</t>
+          <t>09 79 98 08 60</t>
         </is>
       </c>
       <c r="L202" s="6" t="inlineStr">
         <is>
-          <t>sav.anquetil@anquetil.fr</t>
-        </is>
-      </c>
-      <c r="M202" s="6" t="inlineStr">
-        <is>
-          <t>STÉ NOUVELLE H. CONRAUX TRAVAILLE EN PARTENARIAT AVEC ANQUETIL, ÉGALEMENT FILIALE SPIE, POUR LA MAINTENANCE ; CHOIX 2</t>
-        </is>
-      </c>
+          <t>maintenance.sudest@record.fr</t>
+        </is>
+      </c>
+      <c r="M202" s="6" t="inlineStr"/>
     </row>
     <row r="203" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A203" s="6" t="inlineStr"/>
@@ -7128,27 +7088,23 @@
       <c r="H203" s="6" t="inlineStr"/>
       <c r="I203" s="6" t="inlineStr">
         <is>
-          <t>JORICK MAILLARD</t>
+          <t>ISABELLE VALLET</t>
         </is>
       </c>
       <c r="J203" s="6" t="inlineStr">
         <is>
-          <t>TECHNICIEN D'ETUDE</t>
+          <t>ASSISTANTE MAINTENANCE (BRON)</t>
         </is>
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>06 15 62 53 79</t>
-        </is>
-      </c>
-      <c r="L203" s="6" t="inlineStr">
-        <is>
-          <t>jorick.maillard@spie.com</t>
-        </is>
-      </c>
+          <t>09 79 98 09 93</t>
+        </is>
+      </c>
+      <c r="L203" s="6" t="inlineStr"/>
       <c r="M203" s="6" t="inlineStr"/>
     </row>
-    <row r="204" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="204" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A204" s="6" t="inlineStr"/>
       <c r="B204" s="6" t="inlineStr"/>
       <c r="C204" s="6" t="inlineStr"/>
@@ -7159,14 +7115,22 @@
       <c r="H204" s="6" t="inlineStr"/>
       <c r="I204" s="6" t="inlineStr">
         <is>
-          <t>KEVIN MOREAUX</t>
-        </is>
-      </c>
-      <c r="J204" s="6" t="inlineStr"/>
-      <c r="K204" s="6" t="inlineStr"/>
+          <t>JULIETTE BOURBON</t>
+        </is>
+      </c>
+      <c r="J204" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCIALE SÉDENTAIRE MAINTENANCE SUD-EST</t>
+        </is>
+      </c>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t>04 79 52 09 76</t>
+        </is>
+      </c>
       <c r="L204" s="6" t="inlineStr">
         <is>
-          <t>kevin.moreaux@spie.com</t>
+          <t>juliette.bourbon@record.fr</t>
         </is>
       </c>
       <c r="M204" s="6" t="inlineStr"/>
@@ -7182,19 +7146,23 @@
       <c r="H205" s="6" t="inlineStr"/>
       <c r="I205" s="6" t="inlineStr">
         <is>
-          <t>DJAMILA BENSEGHIR</t>
+          <t>MAINTENANCE OUEST</t>
         </is>
       </c>
       <c r="J205" s="6" t="inlineStr"/>
-      <c r="K205" s="6" t="inlineStr"/>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>08 09 10 01 22</t>
+        </is>
+      </c>
       <c r="L205" s="6" t="inlineStr">
         <is>
-          <t>djamila.benseghir@spie.com</t>
+          <t>maintenance.ouest@record.fr</t>
         </is>
       </c>
       <c r="M205" s="6" t="inlineStr"/>
     </row>
-    <row r="206" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="206" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A206" s="6" t="inlineStr"/>
       <c r="B206" s="6" t="inlineStr"/>
       <c r="C206" s="6" t="inlineStr"/>
@@ -7205,105 +7173,89 @@
       <c r="H206" s="6" t="inlineStr"/>
       <c r="I206" s="6" t="inlineStr">
         <is>
-          <t>ISABELLE BAILLARD</t>
-        </is>
-      </c>
-      <c r="J206" s="6" t="inlineStr">
-        <is>
-          <t>COMPTABLE</t>
-        </is>
-      </c>
-      <c r="K206" s="6" t="inlineStr">
-        <is>
-          <t>03 80 60 61 19</t>
-        </is>
-      </c>
+          <t>PÔLE CONTRATS OUEST</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="inlineStr"/>
+      <c r="K206" s="6" t="inlineStr"/>
       <c r="L206" s="6" t="inlineStr">
         <is>
-          <t>isabelle.baillard@spie.com</t>
+          <t>contrats.maintenanceouest@record.fr</t>
         </is>
       </c>
       <c r="M206" s="6" t="inlineStr"/>
     </row>
-    <row r="207" ht="15.9" customHeight="1">
-      <c r="A207" s="4" t="inlineStr">
+    <row r="207" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A207" s="6" t="inlineStr"/>
+      <c r="B207" s="6" t="inlineStr"/>
+      <c r="C207" s="6" t="inlineStr"/>
+      <c r="D207" s="6" t="inlineStr"/>
+      <c r="E207" s="6" t="inlineStr"/>
+      <c r="F207" s="6" t="inlineStr"/>
+      <c r="G207" s="6" t="inlineStr"/>
+      <c r="H207" s="6" t="inlineStr"/>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>AURÉLIE GUIRCHOUN</t>
+        </is>
+      </c>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCIALE SÉDENTAIRE MAINTENANCE OUEST</t>
+        </is>
+      </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>09 79 98 08 74</t>
+        </is>
+      </c>
+      <c r="L207" s="6" t="inlineStr">
+        <is>
+          <t>aurelie.guirchoun@record.fr</t>
+        </is>
+      </c>
+      <c r="M207" s="6" t="inlineStr"/>
+    </row>
+    <row r="208" ht="15.9" customHeight="1">
+      <c r="A208" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
         </is>
       </c>
-      <c r="B207" s="5" t="inlineStr">
-        <is>
-          <t>SOFTICA</t>
-        </is>
-      </c>
-      <c r="C207" s="5" t="inlineStr">
-        <is>
-          <t>FSSO0157</t>
-        </is>
-      </c>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>SOFTICA</t>
-        </is>
-      </c>
-      <c r="E207" s="4" t="inlineStr">
-        <is>
-          <t>PORTE AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>DRUMETTAZ, GRÉSY-SUR-AIX</t>
-        </is>
-      </c>
-      <c r="H207" s="4" t="inlineStr">
-        <is>
-          <t>04 79 63 14 89</t>
-        </is>
-      </c>
-      <c r="I207" s="4" t="inlineStr"/>
-      <c r="J207" s="4" t="inlineStr"/>
-      <c r="K207" s="4" t="inlineStr"/>
-      <c r="L207" s="4" t="inlineStr"/>
-      <c r="M207" s="4" t="inlineStr"/>
-    </row>
-    <row r="208" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A208" s="6" t="inlineStr"/>
-      <c r="B208" s="6" t="inlineStr"/>
-      <c r="C208" s="6" t="inlineStr"/>
-      <c r="D208" s="6" t="inlineStr"/>
-      <c r="E208" s="6" t="inlineStr"/>
-      <c r="F208" s="6" t="inlineStr"/>
-      <c r="G208" s="6" t="inlineStr"/>
-      <c r="H208" s="6" t="inlineStr"/>
-      <c r="I208" s="6" t="inlineStr">
-        <is>
-          <t>SAV, DÉPANNAGES</t>
-        </is>
-      </c>
-      <c r="J208" s="6" t="inlineStr"/>
-      <c r="K208" s="6" t="inlineStr">
-        <is>
-          <t>04 79 63 14 89</t>
-        </is>
-      </c>
-      <c r="L208" s="6" t="inlineStr">
-        <is>
-          <t>maintenance@softica.fr</t>
-        </is>
-      </c>
-      <c r="M208" s="6" t="inlineStr">
-        <is>
-          <t>AGENCE CHAMBÉRY - ALPES</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>REMI GIRARD</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>FSRE0151</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>REMI GIRARD</t>
+        </is>
+      </c>
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>NUISIBLES</t>
+        </is>
+      </c>
+      <c r="F208" s="4" t="inlineStr"/>
+      <c r="G208" s="4" t="inlineStr">
+        <is>
+          <t>CHAMPAGNOLE</t>
+        </is>
+      </c>
+      <c r="H208" s="4" t="inlineStr"/>
+      <c r="I208" s="4" t="inlineStr"/>
+      <c r="J208" s="4" t="inlineStr"/>
+      <c r="K208" s="4" t="inlineStr"/>
+      <c r="L208" s="4" t="inlineStr"/>
+      <c r="M208" s="4" t="inlineStr"/>
+    </row>
+    <row r="209" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A209" s="6" t="inlineStr"/>
       <c r="B209" s="6" t="inlineStr"/>
       <c r="C209" s="6" t="inlineStr"/>
@@ -7314,163 +7266,179 @@
       <c r="H209" s="6" t="inlineStr"/>
       <c r="I209" s="6" t="inlineStr">
         <is>
-          <t>DEMANDES D'INTERVENTION</t>
-        </is>
-      </c>
-      <c r="J209" s="6" t="inlineStr">
-        <is>
-          <t>À UTILISER POUR TOUTES LES DEMANDES MAINT, PRÉV</t>
-        </is>
-      </c>
+          <t>RÉMI GIRARD</t>
+        </is>
+      </c>
+      <c r="J209" s="6" t="inlineStr"/>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>04 79 34 54 17</t>
+          <t>06 02 23 02 87</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr">
         <is>
-          <t>intervention@softica.fr</t>
+          <t>rem14117@gmail.com</t>
         </is>
       </c>
       <c r="M209" s="6" t="inlineStr"/>
     </row>
-    <row r="210" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A210" s="6" t="inlineStr"/>
-      <c r="B210" s="6" t="inlineStr"/>
-      <c r="C210" s="6" t="inlineStr"/>
-      <c r="D210" s="6" t="inlineStr"/>
-      <c r="E210" s="6" t="inlineStr"/>
-      <c r="F210" s="6" t="inlineStr"/>
-      <c r="G210" s="6" t="inlineStr"/>
-      <c r="H210" s="6" t="inlineStr"/>
-      <c r="I210" s="6" t="inlineStr">
-        <is>
-          <t>LAËTITIA MICHELLIER</t>
-        </is>
-      </c>
-      <c r="J210" s="6" t="inlineStr">
-        <is>
-          <t>COMMERCIALE SAV CONTRAT</t>
-        </is>
-      </c>
-      <c r="K210" s="6" t="inlineStr">
-        <is>
-          <t>04 79 63 78 35</t>
-        </is>
-      </c>
-      <c r="L210" s="6" t="inlineStr">
-        <is>
-          <t>lmichellier@softica.fr</t>
-        </is>
-      </c>
-      <c r="M210" s="6" t="inlineStr">
-        <is>
-          <t>SAVOIE HEXAPOLE, 55 IMPASSE DES IRIS 73420 MÉRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="80.40000000000001" customHeight="1">
-      <c r="A211" s="4" t="inlineStr">
+    <row r="210" ht="28.8" customHeight="1">
+      <c r="A210" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
         </is>
       </c>
-      <c r="B211" s="5" t="inlineStr">
-        <is>
-          <t>SOPREMA (SOPRASSISTANCE)</t>
-        </is>
-      </c>
-      <c r="C211" s="5" t="inlineStr">
-        <is>
-          <t>FSSO0114</t>
-        </is>
-      </c>
-      <c r="D211" s="4" t="inlineStr">
-        <is>
-          <t>SOPRASSISTANCE</t>
-        </is>
-      </c>
-      <c r="E211" s="4" t="inlineStr">
-        <is>
-          <t>TOITURES, CHENEAUX</t>
-        </is>
-      </c>
-      <c r="F211" s="4" t="inlineStr">
-        <is>
-          <t>FRANCE</t>
-        </is>
-      </c>
-      <c r="G211" s="4" t="inlineStr">
-        <is>
-          <t>ST GERMAIN EN LAYE ; LISIEUX ; BREST PASTEUR ; ST GILLES CROIX DE VIE ET ; LA ROCHE SUR YON 2 ; VENDÉE ; ORANGE ; DOUAI ; LA MADELEINE</t>
-        </is>
-      </c>
-      <c r="H211" s="4" t="inlineStr">
-        <is>
-          <t>02 98 41 03 40</t>
-        </is>
-      </c>
-      <c r="I211" s="4" t="inlineStr"/>
-      <c r="J211" s="4" t="inlineStr"/>
-      <c r="K211" s="4" t="inlineStr"/>
-      <c r="L211" s="4" t="inlineStr"/>
-      <c r="M211" s="4" t="inlineStr"/>
-    </row>
-    <row r="212" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A212" s="6" t="inlineStr"/>
-      <c r="B212" s="6" t="inlineStr"/>
-      <c r="C212" s="6" t="inlineStr"/>
-      <c r="D212" s="6" t="inlineStr"/>
-      <c r="E212" s="6" t="inlineStr"/>
-      <c r="F212" s="6" t="inlineStr"/>
-      <c r="G212" s="6" t="inlineStr"/>
-      <c r="H212" s="6" t="inlineStr"/>
-      <c r="I212" s="6" t="inlineStr">
-        <is>
-          <t>ADRESSE GÉNÉRIQUE</t>
-        </is>
-      </c>
-      <c r="J212" s="6" t="inlineStr"/>
-      <c r="K212" s="6" t="inlineStr"/>
-      <c r="L212" s="6" t="inlineStr">
-        <is>
-          <t>contact@soprema-entreprises.fr</t>
-        </is>
-      </c>
-      <c r="M212" s="6" t="inlineStr"/>
-    </row>
-    <row r="213" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A213" s="6" t="inlineStr"/>
-      <c r="B213" s="6" t="inlineStr"/>
-      <c r="C213" s="6" t="inlineStr"/>
-      <c r="D213" s="6" t="inlineStr"/>
-      <c r="E213" s="6" t="inlineStr"/>
-      <c r="F213" s="6" t="inlineStr"/>
-      <c r="G213" s="6" t="inlineStr"/>
-      <c r="H213" s="6" t="inlineStr"/>
-      <c r="I213" s="6" t="inlineStr">
-        <is>
-          <t>ANTHONY GAUDOIN</t>
-        </is>
-      </c>
-      <c r="J213" s="6" t="inlineStr"/>
-      <c r="K213" s="6" t="inlineStr">
-        <is>
-          <t>01 55 46 10 80 / 06 74 25 92 39</t>
-        </is>
-      </c>
-      <c r="L213" s="6" t="inlineStr">
-        <is>
-          <t>agaudoin@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M213" s="6" t="inlineStr">
-        <is>
-          <t>ZAC DES LOUVRESSES, 16 AV. DES LOUVRESSES 92230 GENNEVILLIERS</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>SCARAVELLI &amp; FILS, INZA GROUPE</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>FSSC0096</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>SCARAVELLI ET FILS</t>
+        </is>
+      </c>
+      <c r="E210" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F210" s="4" t="inlineStr">
+        <is>
+          <t>SUD OUEST</t>
+        </is>
+      </c>
+      <c r="G210" s="4" t="inlineStr">
+        <is>
+          <t>NÉRAC</t>
+        </is>
+      </c>
+      <c r="H210" s="4" t="inlineStr">
+        <is>
+          <t>06 12 13 28 85</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="inlineStr"/>
+      <c r="J210" s="4" t="inlineStr"/>
+      <c r="K210" s="4" t="inlineStr"/>
+      <c r="L210" s="4" t="inlineStr"/>
+      <c r="M210" s="4" t="inlineStr"/>
+    </row>
+    <row r="211" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A211" s="6" t="inlineStr"/>
+      <c r="B211" s="6" t="inlineStr"/>
+      <c r="C211" s="6" t="inlineStr"/>
+      <c r="D211" s="6" t="inlineStr"/>
+      <c r="E211" s="6" t="inlineStr"/>
+      <c r="F211" s="6" t="inlineStr"/>
+      <c r="G211" s="6" t="inlineStr"/>
+      <c r="H211" s="6" t="inlineStr"/>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="J211" s="6" t="inlineStr"/>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>06 12 13 28 85</t>
+        </is>
+      </c>
+      <c r="L211" s="6" t="inlineStr">
+        <is>
+          <t>scaravelli.chauffagiste@orange.fr</t>
+        </is>
+      </c>
+      <c r="M211" s="6" t="inlineStr"/>
+    </row>
+    <row r="212" ht="54.6" customHeight="1">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>SIÈGE</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>SNP</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr"/>
+      <c r="D212" s="4" t="inlineStr"/>
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>MÉNAGE</t>
+        </is>
+      </c>
+      <c r="F212" s="4" t="inlineStr"/>
+      <c r="G212" s="4" t="inlineStr">
+        <is>
+          <t>SIÈGE</t>
+        </is>
+      </c>
+      <c r="H212" s="4" t="inlineStr"/>
+      <c r="I212" s="4" t="inlineStr"/>
+      <c r="J212" s="4" t="inlineStr"/>
+      <c r="K212" s="4" t="inlineStr"/>
+      <c r="L212" s="4" t="inlineStr"/>
+      <c r="M212" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE MÉNAGE DU SIÈGE ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="28.8" customHeight="1">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>SOCIETE NOUVELLE H. CONRAUX</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>FSCO0034</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>CONRAUX H SAS</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>CHAUFFAGISTE</t>
+        </is>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t>REIMS PARIS</t>
+        </is>
+      </c>
+      <c r="H213" s="4" t="inlineStr">
+        <is>
+          <t>03 26 65 40 40</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="inlineStr"/>
+      <c r="J213" s="4" t="inlineStr"/>
+      <c r="K213" s="4" t="inlineStr"/>
+      <c r="L213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="inlineStr"/>
+    </row>
+    <row r="214" outlineLevel="1" ht="41.7" customHeight="1">
       <c r="A214" s="6" t="inlineStr"/>
       <c r="B214" s="6" t="inlineStr"/>
       <c r="C214" s="6" t="inlineStr"/>
@@ -7481,25 +7449,25 @@
       <c r="H214" s="6" t="inlineStr"/>
       <c r="I214" s="6" t="inlineStr">
         <is>
-          <t>FLORENCE ESCUER</t>
-        </is>
-      </c>
-      <c r="J214" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANTE</t>
-        </is>
-      </c>
+          <t>SAV</t>
+        </is>
+      </c>
+      <c r="J214" s="6" t="inlineStr"/>
       <c r="K214" s="6" t="inlineStr">
         <is>
-          <t>01 55 46 00 82</t>
+          <t>03 26 65 40 40</t>
         </is>
       </c>
       <c r="L214" s="6" t="inlineStr">
         <is>
-          <t>fescuer@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M214" s="6" t="inlineStr"/>
+          <t>sav.anquetil@anquetil.fr</t>
+        </is>
+      </c>
+      <c r="M214" s="6" t="inlineStr">
+        <is>
+          <t>STÉ NOUVELLE H. CONRAUX TRAVAILLE EN PARTENARIAT AVEC ANQUETIL, ÉGALEMENT FILIALE SPIE, POUR LA MAINTENANCE ; CHOIX 2</t>
+        </is>
+      </c>
     </row>
     <row r="215" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A215" s="6" t="inlineStr"/>
@@ -7508,24 +7476,28 @@
       <c r="D215" s="6" t="inlineStr"/>
       <c r="E215" s="6" t="inlineStr"/>
       <c r="F215" s="6" t="inlineStr"/>
-      <c r="G215" s="6" t="inlineStr">
-        <is>
-          <t>LISIEUX</t>
-        </is>
-      </c>
+      <c r="G215" s="6" t="inlineStr"/>
       <c r="H215" s="6" t="inlineStr"/>
       <c r="I215" s="6" t="inlineStr">
         <is>
-          <t>AGENCE VAL-DE-REUIL</t>
-        </is>
-      </c>
-      <c r="J215" s="6" t="inlineStr"/>
+          <t>JORICK MAILLARD</t>
+        </is>
+      </c>
+      <c r="J215" s="6" t="inlineStr">
+        <is>
+          <t>TECHNICIEN D'ETUDE</t>
+        </is>
+      </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>02 32 40 22 98</t>
-        </is>
-      </c>
-      <c r="L215" s="6" t="inlineStr"/>
+          <t>06 15 62 53 79</t>
+        </is>
+      </c>
+      <c r="L215" s="6" t="inlineStr">
+        <is>
+          <t>jorick.maillard@spie.com</t>
+        </is>
+      </c>
       <c r="M215" s="6" t="inlineStr"/>
     </row>
     <row r="216" outlineLevel="1" ht="15.9" customHeight="1">
@@ -7535,64 +7507,44 @@
       <c r="D216" s="6" t="inlineStr"/>
       <c r="E216" s="6" t="inlineStr"/>
       <c r="F216" s="6" t="inlineStr"/>
-      <c r="G216" s="6" t="inlineStr">
-        <is>
-          <t>BREST PASTEUR</t>
-        </is>
-      </c>
+      <c r="G216" s="6" t="inlineStr"/>
       <c r="H216" s="6" t="inlineStr"/>
       <c r="I216" s="6" t="inlineStr">
         <is>
-          <t>STANDARD</t>
+          <t>KEVIN MOREAUX</t>
         </is>
       </c>
       <c r="J216" s="6" t="inlineStr"/>
-      <c r="K216" s="6" t="inlineStr">
-        <is>
-          <t>02 98 41 03 40</t>
-        </is>
-      </c>
-      <c r="L216" s="6" t="inlineStr"/>
+      <c r="K216" s="6" t="inlineStr"/>
+      <c r="L216" s="6" t="inlineStr">
+        <is>
+          <t>kevin.moreaux@spie.com</t>
+        </is>
+      </c>
       <c r="M216" s="6" t="inlineStr"/>
     </row>
-    <row r="217" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="217" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A217" s="6" t="inlineStr"/>
       <c r="B217" s="6" t="inlineStr"/>
       <c r="C217" s="6" t="inlineStr"/>
       <c r="D217" s="6" t="inlineStr"/>
       <c r="E217" s="6" t="inlineStr"/>
       <c r="F217" s="6" t="inlineStr"/>
-      <c r="G217" s="6" t="inlineStr">
-        <is>
-          <t>BREST PASTEUR</t>
-        </is>
-      </c>
+      <c r="G217" s="6" t="inlineStr"/>
       <c r="H217" s="6" t="inlineStr"/>
       <c r="I217" s="6" t="inlineStr">
         <is>
-          <t>LUCILE PRIGENT</t>
-        </is>
-      </c>
-      <c r="J217" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANTE &amp; GESTIONNAIRE COMMUNICATION</t>
-        </is>
-      </c>
-      <c r="K217" s="6" t="inlineStr">
-        <is>
-          <t>02 98 41 17 24</t>
-        </is>
-      </c>
+          <t>DJAMILA BENSEGHIR</t>
+        </is>
+      </c>
+      <c r="J217" s="6" t="inlineStr"/>
+      <c r="K217" s="6" t="inlineStr"/>
       <c r="L217" s="6" t="inlineStr">
         <is>
-          <t>lprigent@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M217" s="6" t="inlineStr">
-        <is>
-          <t>PLOUDANIEL (29260)</t>
-        </is>
-      </c>
+          <t>djamila.benseghir@spie.com</t>
+        </is>
+      </c>
+      <c r="M217" s="6" t="inlineStr"/>
     </row>
     <row r="218" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A218" s="6" t="inlineStr"/>
@@ -7601,87 +7553,107 @@
       <c r="D218" s="6" t="inlineStr"/>
       <c r="E218" s="6" t="inlineStr"/>
       <c r="F218" s="6" t="inlineStr"/>
-      <c r="G218" s="6" t="inlineStr">
-        <is>
-          <t>BREST PASTEUR</t>
-        </is>
-      </c>
+      <c r="G218" s="6" t="inlineStr"/>
       <c r="H218" s="6" t="inlineStr"/>
       <c r="I218" s="6" t="inlineStr">
         <is>
-          <t>SOLÈNE CORRE</t>
+          <t>ISABELLE BAILLARD</t>
         </is>
       </c>
       <c r="J218" s="6" t="inlineStr">
         <is>
-          <t>CONDUCTEUR DE TRAVAUX</t>
-        </is>
-      </c>
-      <c r="K218" s="6" t="inlineStr"/>
+          <t>COMPTABLE</t>
+        </is>
+      </c>
+      <c r="K218" s="6" t="inlineStr">
+        <is>
+          <t>03 80 60 61 19</t>
+        </is>
+      </c>
       <c r="L218" s="6" t="inlineStr">
         <is>
-          <t>scorre@soprema.fr</t>
+          <t>isabelle.baillard@spie.com</t>
         </is>
       </c>
       <c r="M218" s="6" t="inlineStr"/>
     </row>
-    <row r="219" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A219" s="6" t="inlineStr"/>
-      <c r="B219" s="6" t="inlineStr"/>
-      <c r="C219" s="6" t="inlineStr"/>
-      <c r="D219" s="6" t="inlineStr"/>
-      <c r="E219" s="6" t="inlineStr"/>
-      <c r="F219" s="6" t="inlineStr"/>
-      <c r="G219" s="6" t="inlineStr">
-        <is>
-          <t>BREST PASTEUR</t>
-        </is>
-      </c>
-      <c r="H219" s="6" t="inlineStr"/>
-      <c r="I219" s="6" t="inlineStr">
-        <is>
-          <t>COURRIEL GÉNÉRIQUE AGENCE BREST</t>
-        </is>
-      </c>
-      <c r="J219" s="6" t="inlineStr"/>
-      <c r="K219" s="6" t="inlineStr"/>
-      <c r="L219" s="6" t="inlineStr">
-        <is>
-          <t>soprassistance-brest@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M219" s="6" t="inlineStr"/>
-    </row>
-    <row r="220" outlineLevel="1" ht="28.8" customHeight="1">
+    <row r="219" ht="15.9" customHeight="1">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>SOFTICA</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>FSSO0157</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>SOFTICA</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>PORTE AUTOMATIQUE</t>
+        </is>
+      </c>
+      <c r="F219" s="4" t="inlineStr">
+        <is>
+          <t>SUD EST</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr">
+        <is>
+          <t>DRUMETTAZ, GRÉSY-SUR-AIX</t>
+        </is>
+      </c>
+      <c r="H219" s="4" t="inlineStr">
+        <is>
+          <t>04 79 63 14 89</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="inlineStr"/>
+      <c r="J219" s="4" t="inlineStr"/>
+      <c r="K219" s="4" t="inlineStr"/>
+      <c r="L219" s="4" t="inlineStr"/>
+      <c r="M219" s="4" t="inlineStr"/>
+    </row>
+    <row r="220" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A220" s="6" t="inlineStr"/>
       <c r="B220" s="6" t="inlineStr"/>
       <c r="C220" s="6" t="inlineStr"/>
       <c r="D220" s="6" t="inlineStr"/>
       <c r="E220" s="6" t="inlineStr"/>
       <c r="F220" s="6" t="inlineStr"/>
-      <c r="G220" s="6" t="inlineStr">
-        <is>
-          <t>ST GILLES CROIX DE VIE ET</t>
-        </is>
-      </c>
+      <c r="G220" s="6" t="inlineStr"/>
       <c r="H220" s="6" t="inlineStr"/>
       <c r="I220" s="6" t="inlineStr">
         <is>
-          <t>ASSISTANTE D'AGENCE VENDÉE</t>
+          <t>SAV, DÉPANNAGES</t>
         </is>
       </c>
       <c r="J220" s="6" t="inlineStr"/>
       <c r="K220" s="6" t="inlineStr">
         <is>
-          <t>02 28 97 72 31</t>
+          <t>04 79 63 14 89</t>
         </is>
       </c>
       <c r="L220" s="6" t="inlineStr">
         <is>
-          <t>soprassistance-vendee@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M220" s="6" t="inlineStr"/>
+          <t>maintenance@softica.fr</t>
+        </is>
+      </c>
+      <c r="M220" s="6" t="inlineStr">
+        <is>
+          <t>AGENCE CHAMBÉRY - ALPES</t>
+        </is>
+      </c>
     </row>
     <row r="221" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A221" s="6" t="inlineStr"/>
@@ -7690,37 +7662,29 @@
       <c r="D221" s="6" t="inlineStr"/>
       <c r="E221" s="6" t="inlineStr"/>
       <c r="F221" s="6" t="inlineStr"/>
-      <c r="G221" s="6" t="inlineStr">
-        <is>
-          <t>VENDÉE</t>
-        </is>
-      </c>
+      <c r="G221" s="6" t="inlineStr"/>
       <c r="H221" s="6" t="inlineStr"/>
       <c r="I221" s="6" t="inlineStr">
         <is>
-          <t>DAVID VINCENT</t>
+          <t>DEMANDES D'INTERVENTION</t>
         </is>
       </c>
       <c r="J221" s="6" t="inlineStr">
         <is>
-          <t>RESPONSABLE D'AGENCE VENDÉE</t>
+          <t>À UTILISER POUR TOUTES LES DEMANDES MAINT, PRÉV</t>
         </is>
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>02 28 97 72 31 / 06 47 85 97 52</t>
+          <t>04 79 34 54 17</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr">
         <is>
-          <t>davincent@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M221" s="6" t="inlineStr">
-        <is>
-          <t>9 RUE AMPÈRE, BP3, 85170 LE POIRÉ-SUR-VIE</t>
-        </is>
-      </c>
+          <t>intervention@softica.fr</t>
+        </is>
+      </c>
+      <c r="M221" s="6" t="inlineStr"/>
     </row>
     <row r="222" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A222" s="6" t="inlineStr"/>
@@ -7729,68 +7693,80 @@
       <c r="D222" s="6" t="inlineStr"/>
       <c r="E222" s="6" t="inlineStr"/>
       <c r="F222" s="6" t="inlineStr"/>
-      <c r="G222" s="6" t="inlineStr">
-        <is>
-          <t>ORANGE</t>
-        </is>
-      </c>
+      <c r="G222" s="6" t="inlineStr"/>
       <c r="H222" s="6" t="inlineStr"/>
       <c r="I222" s="6" t="inlineStr">
         <is>
-          <t>OLIVIER BECKER</t>
-        </is>
-      </c>
-      <c r="J222" s="6" t="inlineStr"/>
+          <t>LAËTITIA MICHELLIER</t>
+        </is>
+      </c>
+      <c r="J222" s="6" t="inlineStr">
+        <is>
+          <t>COMMERCIALE SAV CONTRAT</t>
+        </is>
+      </c>
       <c r="K222" s="6" t="inlineStr">
         <is>
-          <t>04 90 14 89 27 / 06 87 56 73 32</t>
+          <t>04 79 63 78 35</t>
         </is>
       </c>
       <c r="L222" s="6" t="inlineStr">
         <is>
-          <t>obecker@soprema.fr</t>
+          <t>lmichellier@softica.fr</t>
         </is>
       </c>
       <c r="M222" s="6" t="inlineStr">
         <is>
-          <t>125, RUE DES QUATRE GENDARMES D'OUVÉA 84000 AVIGNON</t>
-        </is>
-      </c>
-    </row>
-    <row r="223" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A223" s="6" t="inlineStr"/>
-      <c r="B223" s="6" t="inlineStr"/>
-      <c r="C223" s="6" t="inlineStr"/>
-      <c r="D223" s="6" t="inlineStr"/>
-      <c r="E223" s="6" t="inlineStr"/>
-      <c r="F223" s="6" t="inlineStr"/>
-      <c r="G223" s="6" t="inlineStr">
-        <is>
-          <t>DOUAI</t>
-        </is>
-      </c>
-      <c r="H223" s="6" t="inlineStr"/>
-      <c r="I223" s="6" t="inlineStr">
-        <is>
-          <t>YOHAN FRERE</t>
-        </is>
-      </c>
-      <c r="J223" s="6" t="inlineStr"/>
-      <c r="K223" s="6" t="inlineStr">
-        <is>
-          <t>03 20 86 27 69 / 06 08 14 70 57</t>
-        </is>
-      </c>
-      <c r="L223" s="6" t="inlineStr">
-        <is>
-          <t>yfrere@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M223" s="6" t="inlineStr">
-        <is>
-          <t>208 RUE DES BOULEAUX 59860 BRUAY-SUR-L'ESCAUT</t>
-        </is>
-      </c>
+          <t>SAVOIE HEXAPOLE, 55 IMPASSE DES IRIS 73420 MÉRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="80.40000000000001" customHeight="1">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>SOPREMA (SOPRASSISTANCE)</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>FSSO0114</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>SOPRASSISTANCE</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>TOITURES, CHENEAUX</t>
+        </is>
+      </c>
+      <c r="F223" s="4" t="inlineStr">
+        <is>
+          <t>FRANCE</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr">
+        <is>
+          <t>ST GERMAIN EN LAYE ; LISIEUX ; BREST PASTEUR ; ST GILLES CROIX DE VIE ET ; LA ROCHE SUR YON 2 ; VENDÉE ; ORANGE ; DOUAI ; LA MADELEINE</t>
+        </is>
+      </c>
+      <c r="H223" s="4" t="inlineStr">
+        <is>
+          <t>02 98 41 03 40</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="inlineStr"/>
+      <c r="J223" s="4" t="inlineStr"/>
+      <c r="K223" s="4" t="inlineStr"/>
+      <c r="L223" s="4" t="inlineStr"/>
+      <c r="M223" s="4" t="inlineStr"/>
     </row>
     <row r="224" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A224" s="6" t="inlineStr"/>
@@ -7799,204 +7775,136 @@
       <c r="D224" s="6" t="inlineStr"/>
       <c r="E224" s="6" t="inlineStr"/>
       <c r="F224" s="6" t="inlineStr"/>
-      <c r="G224" s="6" t="inlineStr">
-        <is>
-          <t>LA MADELEINE</t>
-        </is>
-      </c>
+      <c r="G224" s="6" t="inlineStr"/>
       <c r="H224" s="6" t="inlineStr"/>
       <c r="I224" s="6" t="inlineStr">
         <is>
-          <t>ANTOINE FRANÇOIS</t>
-        </is>
-      </c>
-      <c r="J224" s="6" t="inlineStr">
-        <is>
-          <t>CONDUCTEUR DE TRAVAUX</t>
-        </is>
-      </c>
-      <c r="K224" s="6" t="inlineStr">
-        <is>
-          <t>03 28 82 99 34 / 06 07 63 80 74</t>
-        </is>
-      </c>
+          <t>ADRESSE GÉNÉRIQUE</t>
+        </is>
+      </c>
+      <c r="J224" s="6" t="inlineStr"/>
+      <c r="K224" s="6" t="inlineStr"/>
       <c r="L224" s="6" t="inlineStr">
         <is>
-          <t>afrancois@soprema.fr</t>
-        </is>
-      </c>
-      <c r="M224" s="6" t="inlineStr">
-        <is>
-          <t>851 RUE DU CHEMIN VERT FRETIN CRT 3 - BP104 59810 LESQUIN CEDEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" outlineLevel="1" ht="15.9" customHeight="1">
+          <t>contact@soprema-entreprises.fr</t>
+        </is>
+      </c>
+      <c r="M224" s="6" t="inlineStr"/>
+    </row>
+    <row r="225" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A225" s="6" t="inlineStr"/>
       <c r="B225" s="6" t="inlineStr"/>
       <c r="C225" s="6" t="inlineStr"/>
       <c r="D225" s="6" t="inlineStr"/>
       <c r="E225" s="6" t="inlineStr"/>
       <c r="F225" s="6" t="inlineStr"/>
-      <c r="G225" s="6" t="inlineStr">
-        <is>
-          <t>LA MADELEINE</t>
-        </is>
-      </c>
+      <c r="G225" s="6" t="inlineStr"/>
       <c r="H225" s="6" t="inlineStr"/>
       <c r="I225" s="6" t="inlineStr">
         <is>
-          <t>CHARLES DELOBELLE</t>
-        </is>
-      </c>
-      <c r="J225" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANT</t>
-        </is>
-      </c>
+          <t>ANTHONY GAUDOIN</t>
+        </is>
+      </c>
+      <c r="J225" s="6" t="inlineStr"/>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>03 28 82 99 31</t>
+          <t>01 55 46 10 80 / 06 74 25 92 39</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr">
         <is>
-          <t>cdelobelle@soprema.fr</t>
+          <t>agaudoin@soprema.fr</t>
         </is>
       </c>
       <c r="M225" s="6" t="inlineStr">
         <is>
-          <t>SOPRASSISTANCE LILLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="226" ht="15.9" customHeight="1">
-      <c r="A226" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B226" s="5" t="inlineStr">
-        <is>
-          <t>STAFF CLEAN 3D</t>
-        </is>
-      </c>
-      <c r="C226" s="5" t="inlineStr">
-        <is>
-          <t>FSST0123</t>
-        </is>
-      </c>
-      <c r="D226" s="4" t="inlineStr">
-        <is>
-          <t>STAFF CLEAN 3D</t>
-        </is>
-      </c>
-      <c r="E226" s="4" t="inlineStr">
-        <is>
-          <t>NUISIBLES</t>
-        </is>
-      </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>SUD EST</t>
-        </is>
-      </c>
-      <c r="G226" s="4" t="inlineStr">
-        <is>
-          <t>LA CIOTAT</t>
-        </is>
-      </c>
-      <c r="H226" s="4" t="inlineStr"/>
-      <c r="I226" s="4" t="inlineStr"/>
-      <c r="J226" s="4" t="inlineStr"/>
-      <c r="K226" s="4" t="inlineStr"/>
-      <c r="L226" s="4" t="inlineStr"/>
-      <c r="M226" s="4" t="inlineStr">
-        <is>
-          <t>AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="227" ht="41.7" customHeight="1">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B227" s="5" t="inlineStr">
-        <is>
-          <t>TECH 9 ENERGIE</t>
-        </is>
-      </c>
-      <c r="C227" s="5" t="inlineStr">
-        <is>
-          <t>FSTE0082</t>
-        </is>
-      </c>
-      <c r="D227" s="4" t="inlineStr">
-        <is>
-          <t>TECH9 ENERGIE</t>
-        </is>
-      </c>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>CLIMATICIEN</t>
-        </is>
-      </c>
-      <c r="F227" s="4" t="inlineStr">
-        <is>
-          <t>SUD</t>
-        </is>
-      </c>
-      <c r="G227" s="4" t="inlineStr">
-        <is>
-          <t>CLIMATICIEN ; NOTRE CONTACT CHEZ GROUPTECH9</t>
-        </is>
-      </c>
-      <c r="H227" s="4" t="inlineStr">
-        <is>
-          <t>04 12 04 09 56</t>
-        </is>
-      </c>
-      <c r="I227" s="4" t="inlineStr"/>
-      <c r="J227" s="4" t="inlineStr"/>
-      <c r="K227" s="4" t="inlineStr"/>
-      <c r="L227" s="4" t="inlineStr"/>
-      <c r="M227" s="4" t="inlineStr">
-        <is>
-          <t>DOMAINE ABSENT DE LA SOURCE (« CLIMATICIEN » SAISI EN COLONNE CENTRE) : RÉTABLI LORS DE LA CONSOLIDATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="228" outlineLevel="1" ht="28.8" customHeight="1">
+          <t>ZAC DES LOUVRESSES, 16 AV. DES LOUVRESSES 92230 GENNEVILLIERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A226" s="6" t="inlineStr"/>
+      <c r="B226" s="6" t="inlineStr"/>
+      <c r="C226" s="6" t="inlineStr"/>
+      <c r="D226" s="6" t="inlineStr"/>
+      <c r="E226" s="6" t="inlineStr"/>
+      <c r="F226" s="6" t="inlineStr"/>
+      <c r="G226" s="6" t="inlineStr"/>
+      <c r="H226" s="6" t="inlineStr"/>
+      <c r="I226" s="6" t="inlineStr">
+        <is>
+          <t>FLORENCE ESCUER</t>
+        </is>
+      </c>
+      <c r="J226" s="6" t="inlineStr">
+        <is>
+          <t>ASSISTANTE</t>
+        </is>
+      </c>
+      <c r="K226" s="6" t="inlineStr">
+        <is>
+          <t>01 55 46 00 82</t>
+        </is>
+      </c>
+      <c r="L226" s="6" t="inlineStr">
+        <is>
+          <t>fescuer@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M226" s="6" t="inlineStr"/>
+    </row>
+    <row r="227" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A227" s="6" t="inlineStr"/>
+      <c r="B227" s="6" t="inlineStr"/>
+      <c r="C227" s="6" t="inlineStr"/>
+      <c r="D227" s="6" t="inlineStr"/>
+      <c r="E227" s="6" t="inlineStr"/>
+      <c r="F227" s="6" t="inlineStr"/>
+      <c r="G227" s="6" t="inlineStr">
+        <is>
+          <t>LISIEUX</t>
+        </is>
+      </c>
+      <c r="H227" s="6" t="inlineStr"/>
+      <c r="I227" s="6" t="inlineStr">
+        <is>
+          <t>AGENCE VAL-DE-REUIL</t>
+        </is>
+      </c>
+      <c r="J227" s="6" t="inlineStr"/>
+      <c r="K227" s="6" t="inlineStr">
+        <is>
+          <t>02 32 40 22 98</t>
+        </is>
+      </c>
+      <c r="L227" s="6" t="inlineStr"/>
+      <c r="M227" s="6" t="inlineStr"/>
+    </row>
+    <row r="228" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A228" s="6" t="inlineStr"/>
       <c r="B228" s="6" t="inlineStr"/>
       <c r="C228" s="6" t="inlineStr"/>
       <c r="D228" s="6" t="inlineStr"/>
       <c r="E228" s="6" t="inlineStr"/>
       <c r="F228" s="6" t="inlineStr"/>
-      <c r="G228" s="6" t="inlineStr"/>
+      <c r="G228" s="6" t="inlineStr">
+        <is>
+          <t>BREST PASTEUR</t>
+        </is>
+      </c>
       <c r="H228" s="6" t="inlineStr"/>
       <c r="I228" s="6" t="inlineStr">
         <is>
-          <t>JEAN-PIERRE CAPPONI</t>
-        </is>
-      </c>
-      <c r="J228" s="6" t="inlineStr">
-        <is>
-          <t>DIRECTION</t>
-        </is>
-      </c>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="J228" s="6" t="inlineStr"/>
       <c r="K228" s="6" t="inlineStr">
         <is>
-          <t>04 90 50 33 59 / 06 20 76 44 06</t>
-        </is>
-      </c>
-      <c r="L228" s="6" t="inlineStr">
-        <is>
-          <t>jp.capponi@grouptech9.fr</t>
-        </is>
-      </c>
+          <t>02 98 41 03 40</t>
+        </is>
+      </c>
+      <c r="L228" s="6" t="inlineStr"/>
       <c r="M228" s="6" t="inlineStr"/>
     </row>
     <row r="229" outlineLevel="1" ht="28.8" customHeight="1">
@@ -8008,158 +7916,198 @@
       <c r="F229" s="6" t="inlineStr"/>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t>NOTRE CONTACT CHEZ GROUPTECH9</t>
+          <t>BREST PASTEUR</t>
         </is>
       </c>
       <c r="H229" s="6" t="inlineStr"/>
       <c r="I229" s="6" t="inlineStr">
         <is>
-          <t>CHRISTOPHE LECOINTE</t>
+          <t>LUCILE PRIGENT</t>
         </is>
       </c>
       <c r="J229" s="6" t="inlineStr">
         <is>
-          <t>RESPONSABLE D’AFFAIRES TECH9</t>
+          <t>ASSISTANTE &amp; GESTIONNAIRE COMMUNICATION</t>
         </is>
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>07 57 50 11 70</t>
+          <t>02 98 41 17 24</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr">
         <is>
-          <t>c.lecointe@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M229" s="6" t="inlineStr"/>
-    </row>
-    <row r="230" outlineLevel="1" ht="28.8" customHeight="1">
+          <t>lprigent@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M229" s="6" t="inlineStr">
+        <is>
+          <t>PLOUDANIEL (29260)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A230" s="6" t="inlineStr"/>
       <c r="B230" s="6" t="inlineStr"/>
       <c r="C230" s="6" t="inlineStr"/>
       <c r="D230" s="6" t="inlineStr"/>
       <c r="E230" s="6" t="inlineStr"/>
       <c r="F230" s="6" t="inlineStr"/>
-      <c r="G230" s="6" t="inlineStr"/>
+      <c r="G230" s="6" t="inlineStr">
+        <is>
+          <t>BREST PASTEUR</t>
+        </is>
+      </c>
       <c r="H230" s="6" t="inlineStr"/>
       <c r="I230" s="6" t="inlineStr">
         <is>
-          <t>MME V. ARCAMONE (GÈRE LA FACTURATION)</t>
+          <t>SOLÈNE CORRE</t>
         </is>
       </c>
       <c r="J230" s="6" t="inlineStr">
         <is>
-          <t>PRODUCTION (CHOIX 2)</t>
-        </is>
-      </c>
-      <c r="K230" s="6" t="inlineStr">
-        <is>
-          <t>04 90 50 33 59</t>
-        </is>
-      </c>
+          <t>CONDUCTEUR DE TRAVAUX</t>
+        </is>
+      </c>
+      <c r="K230" s="6" t="inlineStr"/>
       <c r="L230" s="6" t="inlineStr">
         <is>
-          <t>v.arcamone@grouptech9.fr</t>
+          <t>scorre@soprema.fr</t>
         </is>
       </c>
       <c r="M230" s="6" t="inlineStr"/>
     </row>
-    <row r="231" outlineLevel="1" ht="41.7" customHeight="1">
+    <row r="231" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A231" s="6" t="inlineStr"/>
       <c r="B231" s="6" t="inlineStr"/>
       <c r="C231" s="6" t="inlineStr"/>
       <c r="D231" s="6" t="inlineStr"/>
       <c r="E231" s="6" t="inlineStr"/>
       <c r="F231" s="6" t="inlineStr"/>
-      <c r="G231" s="6" t="inlineStr"/>
+      <c r="G231" s="6" t="inlineStr">
+        <is>
+          <t>BREST PASTEUR</t>
+        </is>
+      </c>
       <c r="H231" s="6" t="inlineStr"/>
       <c r="I231" s="6" t="inlineStr">
         <is>
-          <t>MME MARIELLE LUCCINI (À METTRE EN COPIE CC EN CAS ABS MME ARCAMONE)</t>
+          <t>COURRIEL GÉNÉRIQUE AGENCE BREST</t>
         </is>
       </c>
       <c r="J231" s="6" t="inlineStr"/>
       <c r="K231" s="6" t="inlineStr"/>
       <c r="L231" s="6" t="inlineStr">
         <is>
-          <t>m.luccini@grouptech9.fr</t>
+          <t>soprassistance-brest@soprema.fr</t>
         </is>
       </c>
       <c r="M231" s="6" t="inlineStr"/>
     </row>
-    <row r="232" outlineLevel="1" ht="41.7" customHeight="1">
+    <row r="232" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A232" s="6" t="inlineStr"/>
       <c r="B232" s="6" t="inlineStr"/>
       <c r="C232" s="6" t="inlineStr"/>
       <c r="D232" s="6" t="inlineStr"/>
       <c r="E232" s="6" t="inlineStr"/>
       <c r="F232" s="6" t="inlineStr"/>
-      <c r="G232" s="6" t="inlineStr"/>
+      <c r="G232" s="6" t="inlineStr">
+        <is>
+          <t>ST GILLES CROIX DE VIE ET</t>
+        </is>
+      </c>
       <c r="H232" s="6" t="inlineStr"/>
       <c r="I232" s="6" t="inlineStr">
         <is>
-          <t>M. VALENTIN FLEUREAU (EN CAS D'ABSENCE DE MME LUCCINI)</t>
+          <t>ASSISTANTE D'AGENCE VENDÉE</t>
         </is>
       </c>
       <c r="J232" s="6" t="inlineStr"/>
-      <c r="K232" s="6" t="inlineStr"/>
+      <c r="K232" s="6" t="inlineStr">
+        <is>
+          <t>02 28 97 72 31</t>
+        </is>
+      </c>
       <c r="L232" s="6" t="inlineStr">
         <is>
-          <t>f.fleureau@grouptech9.fr</t>
+          <t>soprassistance-vendee@soprema.fr</t>
         </is>
       </c>
       <c r="M232" s="6" t="inlineStr"/>
     </row>
-    <row r="233" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="233" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A233" s="6" t="inlineStr"/>
       <c r="B233" s="6" t="inlineStr"/>
       <c r="C233" s="6" t="inlineStr"/>
       <c r="D233" s="6" t="inlineStr"/>
       <c r="E233" s="6" t="inlineStr"/>
       <c r="F233" s="6" t="inlineStr"/>
-      <c r="G233" s="6" t="inlineStr"/>
+      <c r="G233" s="6" t="inlineStr">
+        <is>
+          <t>VENDÉE</t>
+        </is>
+      </c>
       <c r="H233" s="6" t="inlineStr"/>
       <c r="I233" s="6" t="inlineStr">
         <is>
-          <t>OLIVIER PARTAGE</t>
+          <t>DAVID VINCENT</t>
         </is>
       </c>
       <c r="J233" s="6" t="inlineStr">
         <is>
-          <t>GRANDS TRAVAUX</t>
+          <t>RESPONSABLE D'AGENCE VENDÉE</t>
         </is>
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>07 48 11 96 52</t>
+          <t>02 28 97 72 31 / 06 47 85 97 52</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr">
         <is>
-          <t>o.partage@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M233" s="6" t="inlineStr"/>
-    </row>
-    <row r="234" outlineLevel="1" ht="15.9" customHeight="1">
+          <t>davincent@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M233" s="6" t="inlineStr">
+        <is>
+          <t>9 RUE AMPÈRE, BP3, 85170 LE POIRÉ-SUR-VIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A234" s="6" t="inlineStr"/>
       <c r="B234" s="6" t="inlineStr"/>
       <c r="C234" s="6" t="inlineStr"/>
       <c r="D234" s="6" t="inlineStr"/>
       <c r="E234" s="6" t="inlineStr"/>
       <c r="F234" s="6" t="inlineStr"/>
-      <c r="G234" s="6" t="inlineStr"/>
+      <c r="G234" s="6" t="inlineStr">
+        <is>
+          <t>ORANGE</t>
+        </is>
+      </c>
       <c r="H234" s="6" t="inlineStr"/>
-      <c r="I234" s="6" t="inlineStr"/>
+      <c r="I234" s="6" t="inlineStr">
+        <is>
+          <t>OLIVIER BECKER</t>
+        </is>
+      </c>
       <c r="J234" s="6" t="inlineStr"/>
-      <c r="K234" s="6" t="inlineStr"/>
+      <c r="K234" s="6" t="inlineStr">
+        <is>
+          <t>04 90 14 89 27 / 06 87 56 73 32</t>
+        </is>
+      </c>
       <c r="L234" s="6" t="inlineStr">
         <is>
-          <t>a.laune@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M234" s="6" t="inlineStr"/>
+          <t>obecker@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M234" s="6" t="inlineStr">
+        <is>
+          <t>125, RUE DES QUATRE GENDARMES D'OUVÉA 84000 AVIGNON</t>
+        </is>
+      </c>
     </row>
     <row r="235" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A235" s="6" t="inlineStr"/>
@@ -8168,52 +8116,72 @@
       <c r="D235" s="6" t="inlineStr"/>
       <c r="E235" s="6" t="inlineStr"/>
       <c r="F235" s="6" t="inlineStr"/>
-      <c r="G235" s="6" t="inlineStr"/>
+      <c r="G235" s="6" t="inlineStr">
+        <is>
+          <t>DOUAI</t>
+        </is>
+      </c>
       <c r="H235" s="6" t="inlineStr"/>
       <c r="I235" s="6" t="inlineStr">
         <is>
-          <t>COMPTABILITÉ CLIENT (MARDI ET JEUDI DE 9H30 À 12H)</t>
+          <t>YOHAN FRERE</t>
         </is>
       </c>
       <c r="J235" s="6" t="inlineStr"/>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>04 12 04 09 56</t>
+          <t>03 20 86 27 69 / 06 08 14 70 57</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr">
         <is>
-          <t>fournisseurs@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M235" s="6" t="inlineStr"/>
-    </row>
-    <row r="236" outlineLevel="1" ht="15.9" customHeight="1">
+          <t>yfrere@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M235" s="6" t="inlineStr">
+        <is>
+          <t>208 RUE DES BOULEAUX 59860 BRUAY-SUR-L'ESCAUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A236" s="6" t="inlineStr"/>
       <c r="B236" s="6" t="inlineStr"/>
       <c r="C236" s="6" t="inlineStr"/>
       <c r="D236" s="6" t="inlineStr"/>
       <c r="E236" s="6" t="inlineStr"/>
       <c r="F236" s="6" t="inlineStr"/>
-      <c r="G236" s="6" t="inlineStr"/>
+      <c r="G236" s="6" t="inlineStr">
+        <is>
+          <t>LA MADELEINE</t>
+        </is>
+      </c>
       <c r="H236" s="6" t="inlineStr"/>
       <c r="I236" s="6" t="inlineStr">
         <is>
-          <t>FRED</t>
+          <t>ANTOINE FRANÇOIS</t>
         </is>
       </c>
       <c r="J236" s="6" t="inlineStr">
         <is>
-          <t>TECHNICIEN MAINTENANCE</t>
+          <t>CONDUCTEUR DE TRAVAUX</t>
         </is>
       </c>
       <c r="K236" s="6" t="inlineStr">
         <is>
-          <t>07 83 70 87 89</t>
-        </is>
-      </c>
-      <c r="L236" s="6" t="inlineStr"/>
-      <c r="M236" s="6" t="inlineStr"/>
+          <t>03 28 82 99 34 / 06 07 63 80 74</t>
+        </is>
+      </c>
+      <c r="L236" s="6" t="inlineStr">
+        <is>
+          <t>afrancois@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M236" s="6" t="inlineStr">
+        <is>
+          <t>851 RUE DU CHEMIN VERT FRETIN CRT 3 - BP104 59810 LESQUIN CEDEX</t>
+        </is>
+      </c>
     </row>
     <row r="237" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A237" s="6" t="inlineStr"/>
@@ -8222,52 +8190,76 @@
       <c r="D237" s="6" t="inlineStr"/>
       <c r="E237" s="6" t="inlineStr"/>
       <c r="F237" s="6" t="inlineStr"/>
-      <c r="G237" s="6" t="inlineStr"/>
+      <c r="G237" s="6" t="inlineStr">
+        <is>
+          <t>LA MADELEINE</t>
+        </is>
+      </c>
       <c r="H237" s="6" t="inlineStr"/>
       <c r="I237" s="6" t="inlineStr">
         <is>
-          <t>P. SANGIARDI</t>
+          <t>CHARLES DELOBELLE</t>
         </is>
       </c>
       <c r="J237" s="6" t="inlineStr">
         <is>
-          <t>DIRECTION ICE</t>
-        </is>
-      </c>
-      <c r="K237" s="6" t="inlineStr"/>
+          <t>ASSISTANT</t>
+        </is>
+      </c>
+      <c r="K237" s="6" t="inlineStr">
+        <is>
+          <t>03 28 82 99 31</t>
+        </is>
+      </c>
       <c r="L237" s="6" t="inlineStr">
         <is>
-          <t>p.sangiardi@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M237" s="6" t="inlineStr"/>
-    </row>
-    <row r="238" outlineLevel="1" ht="15.9" customHeight="1">
-      <c r="A238" s="6" t="inlineStr"/>
-      <c r="B238" s="6" t="inlineStr"/>
-      <c r="C238" s="6" t="inlineStr"/>
-      <c r="D238" s="6" t="inlineStr"/>
-      <c r="E238" s="6" t="inlineStr"/>
-      <c r="F238" s="6" t="inlineStr"/>
-      <c r="G238" s="6" t="inlineStr"/>
-      <c r="H238" s="6" t="inlineStr"/>
-      <c r="I238" s="6" t="inlineStr">
-        <is>
-          <t>JP. CAPPONI</t>
-        </is>
-      </c>
-      <c r="J238" s="6" t="inlineStr">
-        <is>
-          <t>DIRECTION ICE</t>
-        </is>
-      </c>
-      <c r="K238" s="6" t="inlineStr"/>
-      <c r="L238" s="6" t="inlineStr">
-        <is>
-          <t>jp.capponi@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M238" s="6" t="inlineStr"/>
+          <t>cdelobelle@soprema.fr</t>
+        </is>
+      </c>
+      <c r="M237" s="6" t="inlineStr">
+        <is>
+          <t>SOPRASSISTANCE LILLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="54.6" customHeight="1">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>SIÈGE</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>SOVEDIS</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr"/>
+      <c r="D238" s="4" t="inlineStr"/>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>ENTRETIEN DES MACHINES À CAFÉ</t>
+        </is>
+      </c>
+      <c r="F238" s="4" t="inlineStr"/>
+      <c r="G238" s="4" t="inlineStr">
+        <is>
+          <t>SIÈGE</t>
+        </is>
+      </c>
+      <c r="H238" s="4" t="inlineStr">
+        <is>
+          <t>06 52 97 88 52</t>
+        </is>
+      </c>
+      <c r="I238" s="4" t="inlineStr"/>
+      <c r="J238" s="4" t="inlineStr"/>
+      <c r="K238" s="4" t="inlineStr"/>
+      <c r="L238" s="4" t="inlineStr"/>
+      <c r="M238" s="4" t="inlineStr">
+        <is>
+          <t>AJOUT HORS ANNUAIRE FRN (TRANSMIS LE 09/09/2026) ; PRESTATAIRE DU SIÈGE ; SEUL NUMÉRO COMMUNIQUÉ, SUR UN PORTABLE ; AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE</t>
+        </is>
+      </c>
     </row>
     <row r="239" outlineLevel="1" ht="15.9" customHeight="1">
       <c r="A239" s="6" t="inlineStr"/>
@@ -8280,50 +8272,66 @@
       <c r="H239" s="6" t="inlineStr"/>
       <c r="I239" s="6" t="inlineStr">
         <is>
-          <t>TRAVAUX ET DÉPANNAGES ICE</t>
+          <t>PANNE ET INTERVENTION</t>
         </is>
       </c>
       <c r="J239" s="6" t="inlineStr"/>
-      <c r="K239" s="6" t="inlineStr"/>
-      <c r="L239" s="6" t="inlineStr">
-        <is>
-          <t>e.carasco@grouptech9.fr</t>
-        </is>
-      </c>
+      <c r="K239" s="6" t="inlineStr">
+        <is>
+          <t>06 52 97 88 52</t>
+        </is>
+      </c>
+      <c r="L239" s="6" t="inlineStr"/>
       <c r="M239" s="6" t="inlineStr"/>
     </row>
-    <row r="240" outlineLevel="1" ht="28.8" customHeight="1">
-      <c r="A240" s="6" t="inlineStr"/>
-      <c r="B240" s="6" t="inlineStr"/>
-      <c r="C240" s="6" t="inlineStr"/>
-      <c r="D240" s="6" t="inlineStr"/>
-      <c r="E240" s="6" t="inlineStr"/>
-      <c r="F240" s="6" t="inlineStr"/>
-      <c r="G240" s="6" t="inlineStr"/>
-      <c r="H240" s="6" t="inlineStr"/>
-      <c r="I240" s="6" t="inlineStr">
-        <is>
-          <t>PEGGY CARRENO (FACTURES ICE)</t>
-        </is>
-      </c>
-      <c r="J240" s="6" t="inlineStr">
-        <is>
-          <t>ASSISTANTE, SERVICE COMPTABLE</t>
-        </is>
-      </c>
-      <c r="K240" s="6" t="inlineStr">
-        <is>
-          <t>04 42 50 69 89</t>
-        </is>
-      </c>
-      <c r="L240" s="6" t="inlineStr">
-        <is>
-          <t>contact.ice@grouptech9.fr</t>
-        </is>
-      </c>
-      <c r="M240" s="6" t="inlineStr"/>
-    </row>
-    <row r="241" ht="28.8" customHeight="1">
+    <row r="240" ht="15.9" customHeight="1">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
+        <is>
+          <t>STAFF CLEAN 3D</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>FSST0123</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>STAFF CLEAN 3D</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>NUISIBLES</t>
+        </is>
+      </c>
+      <c r="F240" s="4" t="inlineStr">
+        <is>
+          <t>SUD EST</t>
+        </is>
+      </c>
+      <c r="G240" s="4" t="inlineStr">
+        <is>
+          <t>LA CIOTAT</t>
+        </is>
+      </c>
+      <c r="H240" s="4" t="inlineStr"/>
+      <c r="I240" s="4" t="inlineStr"/>
+      <c r="J240" s="4" t="inlineStr"/>
+      <c r="K240" s="4" t="inlineStr"/>
+      <c r="L240" s="4" t="inlineStr"/>
+      <c r="M240" s="4" t="inlineStr">
+        <is>
+          <t>AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="41.7" customHeight="1">
       <c r="A241" s="4" t="inlineStr">
         <is>
           <t>SGX RÉSEAU</t>
@@ -8331,38 +8339,50 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>THIBAUT BOUISSON</t>
+          <t>TECH 9 ENERGIE</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>FSBO0099</t>
+          <t>FSTE0082</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>BOUISSON THIBAUT</t>
+          <t>TECH9 ENERGIE</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>ESPACES VERTS / PAYSAGISTE</t>
-        </is>
-      </c>
-      <c r="F241" s="4" t="inlineStr"/>
+          <t>CLIMATICIEN</t>
+        </is>
+      </c>
+      <c r="F241" s="4" t="inlineStr">
+        <is>
+          <t>SUD</t>
+        </is>
+      </c>
       <c r="G241" s="4" t="inlineStr">
         <is>
-          <t>MONTPELLIER AIGUELONGUE</t>
-        </is>
-      </c>
-      <c r="H241" s="4" t="inlineStr"/>
+          <t>CLIMATICIEN ; NOTRE CONTACT CHEZ GROUPTECH9</t>
+        </is>
+      </c>
+      <c r="H241" s="4" t="inlineStr">
+        <is>
+          <t>04 12 04 09 56</t>
+        </is>
+      </c>
       <c r="I241" s="4" t="inlineStr"/>
       <c r="J241" s="4" t="inlineStr"/>
       <c r="K241" s="4" t="inlineStr"/>
       <c r="L241" s="4" t="inlineStr"/>
-      <c r="M241" s="4" t="inlineStr"/>
-    </row>
-    <row r="242" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="M241" s="4" t="inlineStr">
+        <is>
+          <t>DOMAINE ABSENT DE LA SOURCE (« CLIMATICIEN » SAISI EN COLONNE CENTRE) : RÉTABLI LORS DE LA CONSOLIDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A242" s="6" t="inlineStr"/>
       <c r="B242" s="6" t="inlineStr"/>
       <c r="C242" s="6" t="inlineStr"/>
@@ -8373,66 +8393,62 @@
       <c r="H242" s="6" t="inlineStr"/>
       <c r="I242" s="6" t="inlineStr">
         <is>
-          <t>THIBAUT BOUISSON</t>
+          <t>JEAN-PIERRE CAPPONI</t>
         </is>
       </c>
       <c r="J242" s="6" t="inlineStr">
         <is>
-          <t>GÉRANT</t>
+          <t>DIRECTION</t>
         </is>
       </c>
       <c r="K242" s="6" t="inlineStr">
         <is>
-          <t>06 42 78 88 91</t>
-        </is>
-      </c>
-      <c r="L242" s="6" t="inlineStr"/>
+          <t>04 90 50 33 59 / 06 20 76 44 06</t>
+        </is>
+      </c>
+      <c r="L242" s="6" t="inlineStr">
+        <is>
+          <t>jp.capponi@grouptech9.fr</t>
+        </is>
+      </c>
       <c r="M242" s="6" t="inlineStr"/>
     </row>
-    <row r="243" ht="15.9" customHeight="1">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
-        <is>
-          <t>VERRE SOLUTIONS NANTES</t>
-        </is>
-      </c>
-      <c r="C243" s="5" t="inlineStr">
-        <is>
-          <t>FSVE0047</t>
-        </is>
-      </c>
-      <c r="D243" s="4" t="inlineStr">
-        <is>
-          <t>VERRE SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="E243" s="4" t="inlineStr">
-        <is>
-          <t>PORTE AUTOMATIQUE</t>
-        </is>
-      </c>
-      <c r="F243" s="4" t="inlineStr">
-        <is>
-          <t>OUEST</t>
-        </is>
-      </c>
-      <c r="G243" s="4" t="inlineStr">
-        <is>
-          <t>LA BAULE PALMIERS</t>
-        </is>
-      </c>
-      <c r="H243" s="4" t="inlineStr"/>
-      <c r="I243" s="4" t="inlineStr"/>
-      <c r="J243" s="4" t="inlineStr"/>
-      <c r="K243" s="4" t="inlineStr"/>
-      <c r="L243" s="4" t="inlineStr"/>
-      <c r="M243" s="4" t="inlineStr"/>
-    </row>
-    <row r="244" outlineLevel="1" ht="15.9" customHeight="1">
+    <row r="243" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A243" s="6" t="inlineStr"/>
+      <c r="B243" s="6" t="inlineStr"/>
+      <c r="C243" s="6" t="inlineStr"/>
+      <c r="D243" s="6" t="inlineStr"/>
+      <c r="E243" s="6" t="inlineStr"/>
+      <c r="F243" s="6" t="inlineStr"/>
+      <c r="G243" s="6" t="inlineStr">
+        <is>
+          <t>NOTRE CONTACT CHEZ GROUPTECH9</t>
+        </is>
+      </c>
+      <c r="H243" s="6" t="inlineStr"/>
+      <c r="I243" s="6" t="inlineStr">
+        <is>
+          <t>CHRISTOPHE LECOINTE</t>
+        </is>
+      </c>
+      <c r="J243" s="6" t="inlineStr">
+        <is>
+          <t>RESPONSABLE D’AFFAIRES TECH9</t>
+        </is>
+      </c>
+      <c r="K243" s="6" t="inlineStr">
+        <is>
+          <t>07 57 50 11 70</t>
+        </is>
+      </c>
+      <c r="L243" s="6" t="inlineStr">
+        <is>
+          <t>c.lecointe@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M243" s="6" t="inlineStr"/>
+    </row>
+    <row r="244" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A244" s="6" t="inlineStr"/>
       <c r="B244" s="6" t="inlineStr"/>
       <c r="C244" s="6" t="inlineStr"/>
@@ -8443,54 +8459,50 @@
       <c r="H244" s="6" t="inlineStr"/>
       <c r="I244" s="6" t="inlineStr">
         <is>
-          <t>AUDREY COUSIN</t>
-        </is>
-      </c>
-      <c r="J244" s="6" t="inlineStr"/>
+          <t>MME V. ARCAMONE (GÈRE LA FACTURATION)</t>
+        </is>
+      </c>
+      <c r="J244" s="6" t="inlineStr">
+        <is>
+          <t>PRODUCTION (CHOIX 2)</t>
+        </is>
+      </c>
       <c r="K244" s="6" t="inlineStr">
         <is>
-          <t>02 40 72 52 38</t>
-        </is>
-      </c>
-      <c r="L244" s="6" t="inlineStr"/>
-      <c r="M244" s="6" t="inlineStr">
-        <is>
-          <t>10-12 RUE DES GRANDES BOSSES, 44220 COUËRON</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="41.7" customHeight="1">
-      <c r="A245" s="4" t="inlineStr">
-        <is>
-          <t>SGX RÉSEAU</t>
-        </is>
-      </c>
-      <c r="B245" s="5" t="inlineStr">
-        <is>
-          <t>VERT BEAU BOIS</t>
-        </is>
-      </c>
-      <c r="C245" s="5" t="inlineStr"/>
-      <c r="D245" s="4" t="inlineStr"/>
-      <c r="E245" s="4" t="inlineStr">
-        <is>
-          <t>ESPACES VERTS / PAYSAGISTE</t>
-        </is>
-      </c>
-      <c r="F245" s="4" t="inlineStr"/>
-      <c r="G245" s="4" t="inlineStr"/>
-      <c r="H245" s="4" t="inlineStr"/>
-      <c r="I245" s="4" t="inlineStr"/>
-      <c r="J245" s="4" t="inlineStr"/>
-      <c r="K245" s="4" t="inlineStr"/>
-      <c r="L245" s="4" t="inlineStr"/>
-      <c r="M245" s="4" t="inlineStr">
-        <is>
-          <t>AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" outlineLevel="1" ht="15.9" customHeight="1">
+          <t>04 90 50 33 59</t>
+        </is>
+      </c>
+      <c r="L244" s="6" t="inlineStr">
+        <is>
+          <t>v.arcamone@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M244" s="6" t="inlineStr"/>
+    </row>
+    <row r="245" outlineLevel="1" ht="41.7" customHeight="1">
+      <c r="A245" s="6" t="inlineStr"/>
+      <c r="B245" s="6" t="inlineStr"/>
+      <c r="C245" s="6" t="inlineStr"/>
+      <c r="D245" s="6" t="inlineStr"/>
+      <c r="E245" s="6" t="inlineStr"/>
+      <c r="F245" s="6" t="inlineStr"/>
+      <c r="G245" s="6" t="inlineStr"/>
+      <c r="H245" s="6" t="inlineStr"/>
+      <c r="I245" s="6" t="inlineStr">
+        <is>
+          <t>MME MARIELLE LUCCINI (À METTRE EN COPIE CC EN CAS ABS MME ARCAMONE)</t>
+        </is>
+      </c>
+      <c r="J245" s="6" t="inlineStr"/>
+      <c r="K245" s="6" t="inlineStr"/>
+      <c r="L245" s="6" t="inlineStr">
+        <is>
+          <t>m.luccini@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M245" s="6" t="inlineStr"/>
+    </row>
+    <row r="246" outlineLevel="1" ht="41.7" customHeight="1">
       <c r="A246" s="6" t="inlineStr"/>
       <c r="B246" s="6" t="inlineStr"/>
       <c r="C246" s="6" t="inlineStr"/>
@@ -8501,14 +8513,14 @@
       <c r="H246" s="6" t="inlineStr"/>
       <c r="I246" s="6" t="inlineStr">
         <is>
-          <t>GESTION CONTRAT, DEVIS</t>
+          <t>M. VALENTIN FLEUREAU (EN CAS D'ABSENCE DE MME LUCCINI)</t>
         </is>
       </c>
       <c r="J246" s="6" t="inlineStr"/>
       <c r="K246" s="6" t="inlineStr"/>
       <c r="L246" s="6" t="inlineStr">
         <is>
-          <t>contact@vertbeaubois.fr</t>
+          <t>f.fleureau@grouptech9.fr</t>
         </is>
       </c>
       <c r="M246" s="6" t="inlineStr"/>
@@ -8524,20 +8536,422 @@
       <c r="H247" s="6" t="inlineStr"/>
       <c r="I247" s="6" t="inlineStr">
         <is>
+          <t>OLIVIER PARTAGE</t>
+        </is>
+      </c>
+      <c r="J247" s="6" t="inlineStr">
+        <is>
+          <t>GRANDS TRAVAUX</t>
+        </is>
+      </c>
+      <c r="K247" s="6" t="inlineStr">
+        <is>
+          <t>07 48 11 96 52</t>
+        </is>
+      </c>
+      <c r="L247" s="6" t="inlineStr">
+        <is>
+          <t>o.partage@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M247" s="6" t="inlineStr"/>
+    </row>
+    <row r="248" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A248" s="6" t="inlineStr"/>
+      <c r="B248" s="6" t="inlineStr"/>
+      <c r="C248" s="6" t="inlineStr"/>
+      <c r="D248" s="6" t="inlineStr"/>
+      <c r="E248" s="6" t="inlineStr"/>
+      <c r="F248" s="6" t="inlineStr"/>
+      <c r="G248" s="6" t="inlineStr"/>
+      <c r="H248" s="6" t="inlineStr"/>
+      <c r="I248" s="6" t="inlineStr"/>
+      <c r="J248" s="6" t="inlineStr"/>
+      <c r="K248" s="6" t="inlineStr"/>
+      <c r="L248" s="6" t="inlineStr">
+        <is>
+          <t>a.laune@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M248" s="6" t="inlineStr"/>
+    </row>
+    <row r="249" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A249" s="6" t="inlineStr"/>
+      <c r="B249" s="6" t="inlineStr"/>
+      <c r="C249" s="6" t="inlineStr"/>
+      <c r="D249" s="6" t="inlineStr"/>
+      <c r="E249" s="6" t="inlineStr"/>
+      <c r="F249" s="6" t="inlineStr"/>
+      <c r="G249" s="6" t="inlineStr"/>
+      <c r="H249" s="6" t="inlineStr"/>
+      <c r="I249" s="6" t="inlineStr">
+        <is>
+          <t>COMPTABILITÉ CLIENT (MARDI ET JEUDI DE 9H30 À 12H)</t>
+        </is>
+      </c>
+      <c r="J249" s="6" t="inlineStr"/>
+      <c r="K249" s="6" t="inlineStr">
+        <is>
+          <t>04 12 04 09 56</t>
+        </is>
+      </c>
+      <c r="L249" s="6" t="inlineStr">
+        <is>
+          <t>fournisseurs@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M249" s="6" t="inlineStr"/>
+    </row>
+    <row r="250" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A250" s="6" t="inlineStr"/>
+      <c r="B250" s="6" t="inlineStr"/>
+      <c r="C250" s="6" t="inlineStr"/>
+      <c r="D250" s="6" t="inlineStr"/>
+      <c r="E250" s="6" t="inlineStr"/>
+      <c r="F250" s="6" t="inlineStr"/>
+      <c r="G250" s="6" t="inlineStr"/>
+      <c r="H250" s="6" t="inlineStr"/>
+      <c r="I250" s="6" t="inlineStr">
+        <is>
+          <t>FRED</t>
+        </is>
+      </c>
+      <c r="J250" s="6" t="inlineStr">
+        <is>
+          <t>TECHNICIEN MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="K250" s="6" t="inlineStr">
+        <is>
+          <t>07 83 70 87 89</t>
+        </is>
+      </c>
+      <c r="L250" s="6" t="inlineStr"/>
+      <c r="M250" s="6" t="inlineStr"/>
+    </row>
+    <row r="251" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A251" s="6" t="inlineStr"/>
+      <c r="B251" s="6" t="inlineStr"/>
+      <c r="C251" s="6" t="inlineStr"/>
+      <c r="D251" s="6" t="inlineStr"/>
+      <c r="E251" s="6" t="inlineStr"/>
+      <c r="F251" s="6" t="inlineStr"/>
+      <c r="G251" s="6" t="inlineStr"/>
+      <c r="H251" s="6" t="inlineStr"/>
+      <c r="I251" s="6" t="inlineStr">
+        <is>
+          <t>P. SANGIARDI</t>
+        </is>
+      </c>
+      <c r="J251" s="6" t="inlineStr">
+        <is>
+          <t>DIRECTION ICE</t>
+        </is>
+      </c>
+      <c r="K251" s="6" t="inlineStr"/>
+      <c r="L251" s="6" t="inlineStr">
+        <is>
+          <t>p.sangiardi@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M251" s="6" t="inlineStr"/>
+    </row>
+    <row r="252" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A252" s="6" t="inlineStr"/>
+      <c r="B252" s="6" t="inlineStr"/>
+      <c r="C252" s="6" t="inlineStr"/>
+      <c r="D252" s="6" t="inlineStr"/>
+      <c r="E252" s="6" t="inlineStr"/>
+      <c r="F252" s="6" t="inlineStr"/>
+      <c r="G252" s="6" t="inlineStr"/>
+      <c r="H252" s="6" t="inlineStr"/>
+      <c r="I252" s="6" t="inlineStr">
+        <is>
+          <t>JP. CAPPONI</t>
+        </is>
+      </c>
+      <c r="J252" s="6" t="inlineStr">
+        <is>
+          <t>DIRECTION ICE</t>
+        </is>
+      </c>
+      <c r="K252" s="6" t="inlineStr"/>
+      <c r="L252" s="6" t="inlineStr">
+        <is>
+          <t>jp.capponi@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M252" s="6" t="inlineStr"/>
+    </row>
+    <row r="253" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A253" s="6" t="inlineStr"/>
+      <c r="B253" s="6" t="inlineStr"/>
+      <c r="C253" s="6" t="inlineStr"/>
+      <c r="D253" s="6" t="inlineStr"/>
+      <c r="E253" s="6" t="inlineStr"/>
+      <c r="F253" s="6" t="inlineStr"/>
+      <c r="G253" s="6" t="inlineStr"/>
+      <c r="H253" s="6" t="inlineStr"/>
+      <c r="I253" s="6" t="inlineStr">
+        <is>
+          <t>TRAVAUX ET DÉPANNAGES ICE</t>
+        </is>
+      </c>
+      <c r="J253" s="6" t="inlineStr"/>
+      <c r="K253" s="6" t="inlineStr"/>
+      <c r="L253" s="6" t="inlineStr">
+        <is>
+          <t>e.carasco@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M253" s="6" t="inlineStr"/>
+    </row>
+    <row r="254" outlineLevel="1" ht="28.8" customHeight="1">
+      <c r="A254" s="6" t="inlineStr"/>
+      <c r="B254" s="6" t="inlineStr"/>
+      <c r="C254" s="6" t="inlineStr"/>
+      <c r="D254" s="6" t="inlineStr"/>
+      <c r="E254" s="6" t="inlineStr"/>
+      <c r="F254" s="6" t="inlineStr"/>
+      <c r="G254" s="6" t="inlineStr"/>
+      <c r="H254" s="6" t="inlineStr"/>
+      <c r="I254" s="6" t="inlineStr">
+        <is>
+          <t>PEGGY CARRENO (FACTURES ICE)</t>
+        </is>
+      </c>
+      <c r="J254" s="6" t="inlineStr">
+        <is>
+          <t>ASSISTANTE, SERVICE COMPTABLE</t>
+        </is>
+      </c>
+      <c r="K254" s="6" t="inlineStr">
+        <is>
+          <t>04 42 50 69 89</t>
+        </is>
+      </c>
+      <c r="L254" s="6" t="inlineStr">
+        <is>
+          <t>contact.ice@grouptech9.fr</t>
+        </is>
+      </c>
+      <c r="M254" s="6" t="inlineStr"/>
+    </row>
+    <row r="255" ht="28.8" customHeight="1">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="inlineStr">
+        <is>
+          <t>THIBAUT BOUISSON</t>
+        </is>
+      </c>
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t>FSBO0099</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr">
+        <is>
+          <t>BOUISSON THIBAUT</t>
+        </is>
+      </c>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>ESPACES VERTS / PAYSAGISTE</t>
+        </is>
+      </c>
+      <c r="F255" s="4" t="inlineStr"/>
+      <c r="G255" s="4" t="inlineStr">
+        <is>
+          <t>MONTPELLIER AIGUELONGUE</t>
+        </is>
+      </c>
+      <c r="H255" s="4" t="inlineStr"/>
+      <c r="I255" s="4" t="inlineStr"/>
+      <c r="J255" s="4" t="inlineStr"/>
+      <c r="K255" s="4" t="inlineStr"/>
+      <c r="L255" s="4" t="inlineStr"/>
+      <c r="M255" s="4" t="inlineStr"/>
+    </row>
+    <row r="256" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A256" s="6" t="inlineStr"/>
+      <c r="B256" s="6" t="inlineStr"/>
+      <c r="C256" s="6" t="inlineStr"/>
+      <c r="D256" s="6" t="inlineStr"/>
+      <c r="E256" s="6" t="inlineStr"/>
+      <c r="F256" s="6" t="inlineStr"/>
+      <c r="G256" s="6" t="inlineStr"/>
+      <c r="H256" s="6" t="inlineStr"/>
+      <c r="I256" s="6" t="inlineStr">
+        <is>
+          <t>THIBAUT BOUISSON</t>
+        </is>
+      </c>
+      <c r="J256" s="6" t="inlineStr">
+        <is>
+          <t>GÉRANT</t>
+        </is>
+      </c>
+      <c r="K256" s="6" t="inlineStr">
+        <is>
+          <t>06 42 78 88 91</t>
+        </is>
+      </c>
+      <c r="L256" s="6" t="inlineStr"/>
+      <c r="M256" s="6" t="inlineStr"/>
+    </row>
+    <row r="257" ht="15.9" customHeight="1">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>VERRE SOLUTIONS NANTES</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>FSVE0047</t>
+        </is>
+      </c>
+      <c r="D257" s="4" t="inlineStr">
+        <is>
+          <t>VERRE SOLUTIONS</t>
+        </is>
+      </c>
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>PORTE AUTOMATIQUE</t>
+        </is>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
+        <is>
+          <t>OUEST</t>
+        </is>
+      </c>
+      <c r="G257" s="4" t="inlineStr">
+        <is>
+          <t>LA BAULE PALMIERS</t>
+        </is>
+      </c>
+      <c r="H257" s="4" t="inlineStr"/>
+      <c r="I257" s="4" t="inlineStr"/>
+      <c r="J257" s="4" t="inlineStr"/>
+      <c r="K257" s="4" t="inlineStr"/>
+      <c r="L257" s="4" t="inlineStr"/>
+      <c r="M257" s="4" t="inlineStr"/>
+    </row>
+    <row r="258" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A258" s="6" t="inlineStr"/>
+      <c r="B258" s="6" t="inlineStr"/>
+      <c r="C258" s="6" t="inlineStr"/>
+      <c r="D258" s="6" t="inlineStr"/>
+      <c r="E258" s="6" t="inlineStr"/>
+      <c r="F258" s="6" t="inlineStr"/>
+      <c r="G258" s="6" t="inlineStr"/>
+      <c r="H258" s="6" t="inlineStr"/>
+      <c r="I258" s="6" t="inlineStr">
+        <is>
+          <t>AUDREY COUSIN</t>
+        </is>
+      </c>
+      <c r="J258" s="6" t="inlineStr"/>
+      <c r="K258" s="6" t="inlineStr">
+        <is>
+          <t>02 40 72 52 38</t>
+        </is>
+      </c>
+      <c r="L258" s="6" t="inlineStr"/>
+      <c r="M258" s="6" t="inlineStr">
+        <is>
+          <t>10-12 RUE DES GRANDES BOSSES, 44220 COUËRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="41.7" customHeight="1">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>SGX RÉSEAU</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>VERT BEAU BOIS</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr"/>
+      <c r="D259" s="4" t="inlineStr"/>
+      <c r="E259" s="4" t="inlineStr">
+        <is>
+          <t>ESPACES VERTS / PAYSAGISTE</t>
+        </is>
+      </c>
+      <c r="F259" s="4" t="inlineStr"/>
+      <c r="G259" s="4" t="inlineStr"/>
+      <c r="H259" s="4" t="inlineStr"/>
+      <c r="I259" s="4" t="inlineStr"/>
+      <c r="J259" s="4" t="inlineStr"/>
+      <c r="K259" s="4" t="inlineStr"/>
+      <c r="L259" s="4" t="inlineStr"/>
+      <c r="M259" s="4" t="inlineStr">
+        <is>
+          <t>AUCUN N° DE COMPTE FOURNISSEUR AUDIKA DANS LA SOURCE ; AUCUN NUMÉRO DE TÉLÉPHONE DANS LA SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A260" s="6" t="inlineStr"/>
+      <c r="B260" s="6" t="inlineStr"/>
+      <c r="C260" s="6" t="inlineStr"/>
+      <c r="D260" s="6" t="inlineStr"/>
+      <c r="E260" s="6" t="inlineStr"/>
+      <c r="F260" s="6" t="inlineStr"/>
+      <c r="G260" s="6" t="inlineStr"/>
+      <c r="H260" s="6" t="inlineStr"/>
+      <c r="I260" s="6" t="inlineStr">
+        <is>
+          <t>GESTION CONTRAT, DEVIS</t>
+        </is>
+      </c>
+      <c r="J260" s="6" t="inlineStr"/>
+      <c r="K260" s="6" t="inlineStr"/>
+      <c r="L260" s="6" t="inlineStr">
+        <is>
+          <t>contact@vertbeaubois.fr</t>
+        </is>
+      </c>
+      <c r="M260" s="6" t="inlineStr"/>
+    </row>
+    <row r="261" outlineLevel="1" ht="15.9" customHeight="1">
+      <c r="A261" s="6" t="inlineStr"/>
+      <c r="B261" s="6" t="inlineStr"/>
+      <c r="C261" s="6" t="inlineStr"/>
+      <c r="D261" s="6" t="inlineStr"/>
+      <c r="E261" s="6" t="inlineStr"/>
+      <c r="F261" s="6" t="inlineStr"/>
+      <c r="G261" s="6" t="inlineStr"/>
+      <c r="H261" s="6" t="inlineStr"/>
+      <c r="I261" s="6" t="inlineStr">
+        <is>
           <t>COMPTABILITÉ</t>
         </is>
       </c>
-      <c r="J247" s="6" t="inlineStr"/>
-      <c r="K247" s="6" t="inlineStr"/>
-      <c r="L247" s="6" t="inlineStr">
+      <c r="J261" s="6" t="inlineStr"/>
+      <c r="K261" s="6" t="inlineStr"/>
+      <c r="L261" s="6" t="inlineStr">
         <is>
           <t>compta@vertbeaubois.fr</t>
         </is>
       </c>
-      <c r="M247" s="6" t="inlineStr"/>
+      <c r="M261" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M247"/>
+  <autoFilter ref="A3:M261"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
